--- a/docs/downloads/2026-10-07/bursa-report-2026-10-07.xlsx
+++ b/docs/downloads/2026-10-07/bursa-report-2026-10-07.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-07" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-07'!$A$1:$M$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-07'!$A$1:$M$75</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -35,13 +35,13 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
+      <color rgb="000CA30C"/>
+    </font>
+    <font>
       <color rgb="00898781"/>
     </font>
     <font>
       <color rgb="00D03B3B"/>
-    </font>
-    <font>
-      <color rgb="000CA30C"/>
     </font>
   </fonts>
   <fills count="3">
@@ -69,7 +69,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -78,12 +78,13 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -449,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -542,39 +543,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.09</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0</v>
+        <v>0.06860000000000001</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>7243300</v>
+        <v>81712800</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.01</v>
+        <v>1.48</v>
       </c>
       <c r="H2" t="n">
-        <v>21.78</v>
+        <v>77.87</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.195</v>
+        <v>0.773</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.413</v>
+        <v>0.704</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" s="7" t="inlineStr"/>
@@ -587,39 +588,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>0043</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>MTRONIC</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.895</v>
+        <v>0.005</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>0.0229</v>
+        <v>0</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>4720500</v>
+        <v>64189800</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.09</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>74.95</v>
+        <v>47.04</v>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.769</v>
+        <v>0.007</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.703</v>
+        <v>0.006</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" s="7" t="inlineStr"/>
@@ -632,39 +633,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E4" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E4" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>3950000</v>
+        <v>45362000</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="H4" t="n">
-        <v>68.56999999999999</v>
+        <v>21.78</v>
       </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.349</v>
+        <v>0.195</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.227</v>
+        <v>0.413</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
@@ -677,39 +678,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.305</v>
+        <v>0.5</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1660800</v>
+        <v>28772000</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.27</v>
+        <v>1.27</v>
       </c>
       <c r="H5" t="n">
-        <v>71.65000000000001</v>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
+        <v>74.92</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.288</v>
+        <v>0.409</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.273</v>
+        <v>0.343</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -722,39 +723,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1.12</v>
+        <v>0.34</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0</v>
+        <v>0.0303</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1020100</v>
+        <v>17826600</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.08</v>
+        <v>0.36</v>
       </c>
       <c r="H6" t="n">
-        <v>58.74</v>
+        <v>79.56</v>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.077</v>
+        <v>0.267</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>1.034</v>
+        <v>0.24</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
@@ -767,45 +768,3096 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>0.016</v>
+        <v>0.36</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>-0.04</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>871800</v>
+        <v>17075600</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.09</v>
+        <v>0.41</v>
       </c>
       <c r="H7" t="n">
-        <v>65.45999999999999</v>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
+        <v>61.99</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.175</v>
+        <v>0.348</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>1.119</v>
+        <v>0.227</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0476</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SLGC Berhad</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>14628200</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>9393</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ITRONIC</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>-0.1667</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>14254600</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>11.59</v>
+      </c>
+      <c r="H9" t="n">
+        <v>37.04</v>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0163</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CAREPLS</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>12469100</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H10" t="n">
+        <v>64.26000000000001</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>5168</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>HARTA</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0.0446</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>10193600</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H11" t="n">
+        <v>64.48999999999999</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>1.082</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>1.035</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>7192</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>GIIB</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>-0.0083</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>7775400</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>68.69</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>7153</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>KOSSAN</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>7396800</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="H13" t="n">
+        <v>65.45999999999999</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>1.119</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>7191</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ADVENTA</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0.09089999999999999</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>7356700</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="H14" t="n">
+        <v>77.04000000000001</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0193</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>KINERGY</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>6707000</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H15" t="n">
+        <v>38.38</v>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>7803</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>HEXCARE</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>5898500</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="H16" t="n">
+        <v>63.59</v>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>5311</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CEB</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>4759400</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="H17" t="n">
+        <v>71.65000000000001</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CIMB</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>-0.0325</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>4004100</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H18" t="n">
+        <v>36.54</v>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>7.736</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>7.752</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2127</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>COMFORT</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0.0571</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>3960600</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="H19" t="n">
+        <v>71.83</v>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CYPARK</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>3651600</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H20" t="n">
+        <v>66.81999999999999</v>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>0.764</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0459</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0.03700000000000001</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>3565100</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H21" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>0.654</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>4456</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>DNEX</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>3263100</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H22" t="n">
+        <v>61.53</v>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>0.477</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2429</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>TANCO</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>3224500</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H23" t="n">
+        <v>30.36</v>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>0.204</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>3174</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>L&amp;G</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>3091200</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H24" t="n">
+        <v>54.23</v>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>5238</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AAGB</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>-0.0101</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>2868600</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H25" t="n">
+        <v>28.04</v>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0345</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>SUNLOGY</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>-0.0105</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>2676700</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H26" t="n">
+        <v>56.29</v>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0270</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NATGATE</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>2646000</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H27" t="n">
+        <v>62.39</v>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>1.775</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>1.616</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>5142</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>WASCO</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>0.0915</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>2560800</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H28" t="n">
+        <v>61.84</v>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0248</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>YEWLEE</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>0.0164</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>2384600</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H29" t="n">
+        <v>55.75</v>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>5115</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ALAM</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>2328700</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="H30" t="n">
+        <v>53.85</v>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>0.242</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>4324</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>HENGYUAN</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>0.0434</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>2284100</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H31" t="n">
+        <v>54.81</v>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>3.582</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>2.669</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>7121</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>2066500</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H32" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>0.8070000000000001</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>7081</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>0.0151</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>1757800</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H33" t="n">
+        <v>33.03</v>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>1.066</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>5161</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>JCY</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>1745700</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H34" t="n">
+        <v>65.61</v>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>1699100</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H35" t="n">
+        <v>62.47</v>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>5.696</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>5.761</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0450</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>MFGROUP</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>1676900</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="H36" t="n">
+        <v>45.51</v>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0251</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SFPTECH</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0.0169</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>1668300</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H37" t="n">
+        <v>59.64</v>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0455</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>BUSCAP</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>-0.0061</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>1639100</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="H38" t="n">
+        <v>81.56</v>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>0.584</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ALPHA</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>-0.0175</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>1634100</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="H39" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" s="7" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>5151</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>HEXTAR</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>1590800</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H40" t="n">
+        <v>53.14</v>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" s="7" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0359</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>HKB</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>0.0672</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>1510200</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="H41" t="n">
+        <v>71.61</v>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>0.613</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" s="7" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0457</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>PENTECH</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>1444500</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H42" t="n">
+        <v>66</v>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0146</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>JFTECH</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>0.0064</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>1443400</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H43" t="n">
+        <v>69.79000000000001</v>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>0.699</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>0.6860000000000001</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>4677</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>YTL</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>1431500</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H44" t="n">
+        <v>43.79</v>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>2.248</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>2.223</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" s="7" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0262</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SUNVIEW</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>1422400</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H45" t="n">
+        <v>72.51000000000001</v>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" s="7" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0292</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>JTGROUP</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>0.0515</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>1319100</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H46" t="n">
+        <v>80.78</v>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>1.208</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" s="7" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0469</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>GTA</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>1248400</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H47" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="K47" s="2" t="n"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" s="7" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>5162</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>VSTECS</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>0.0231</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>1237700</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H48" t="n">
+        <v>63.95</v>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>1.657</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>1.679</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" s="7" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>MAYBANK</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>1200700</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H49" t="n">
+        <v>37.54</v>
+      </c>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>10.078</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>10.235</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" s="7" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>5555</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SUNMED</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>1192200</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H50" t="n">
+        <v>49.12</v>
+      </c>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>2.098</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>2.078</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" s="7" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>5327</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>MEGAFB</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>0.0036</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>1155900</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H51" t="n">
+        <v>70.62</v>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>2.591</v>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" s="7" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0353</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>WESTRVR</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>1146000</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H52" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" s="7" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>5398</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>GAMUDA</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>1063900</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H53" t="n">
+        <v>60.39</v>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>4.896</v>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>4.627</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" s="7" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>5337</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ECOSHOP</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>-0.0068</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>1052500</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H54" t="n">
+        <v>44.42</v>
+      </c>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>1.465</v>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>1.469</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" s="7" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>LGMS</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>1048100</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H55" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>0.514</v>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" s="7" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0236</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>RAMSSOL</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>1005000</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H56" t="n">
+        <v>55.54</v>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" s="7" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0181</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>AEMULUS</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E57" s="10" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>1002200</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H57" t="n">
+        <v>60.94</v>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" s="7" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0318</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ELRIDGE</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E58" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>974300</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H58" t="n">
+        <v>64.02</v>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" s="7" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>7204</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>D&amp;O</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>936200</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H59" t="n">
+        <v>58.34</v>
+      </c>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>0.511</v>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" s="7" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>GREATEC</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>904500</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H60" t="n">
+        <v>70.64</v>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>2.614</v>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>2.571</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" s="7" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>0391</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>AMBEST</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>0.0146</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>847800</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H61" t="n">
+        <v>57.34</v>
+      </c>
+      <c r="I61" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>1.358</v>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>1.223</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" s="7" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0275</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>OPPSTAR</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>0.006999999999999999</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>818700</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H62" t="n">
+        <v>56.78</v>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" s="7" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0368</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>OXB</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E63" s="10" t="n">
+        <v>-0.0095</v>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>798100</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H63" t="n">
+        <v>69.04000000000001</v>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>0.447</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" s="7" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>5296</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>MRDIY</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E64" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>792500</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H64" t="n">
+        <v>33.87</v>
+      </c>
+      <c r="I64" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>1.296</v>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>1.396</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" s="7" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>0223</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>SAMAIDEN</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>0.0224</v>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>780400</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H65" t="n">
+        <v>75.12</v>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>2.631</v>
+      </c>
+      <c r="K65" s="2" t="n">
+        <v>1.987</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" s="7" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>0083</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>NOTION</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="E66" s="10" t="n">
+        <v>-0.0069</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>695300</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H66" t="n">
+        <v>64.69</v>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v>0.599</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" s="7" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0056</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>NCT</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E67" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>693300</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H67" t="n">
+        <v>48.46</v>
+      </c>
+      <c r="I67" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="K67" s="2" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" s="7" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>3336</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>IJM</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>688900</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H68" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="I68" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>2.785</v>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>2.688</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" s="7" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>RHBBANK</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="E69" s="10" t="n">
+        <v>-0.0067</v>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>636800</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H69" t="n">
+        <v>24.16</v>
+      </c>
+      <c r="I69" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>7.711</v>
+      </c>
+      <c r="K69" s="2" t="n">
+        <v>8.146000000000001</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" s="7" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>0196</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>QES</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>628500</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H70" t="n">
+        <v>60.17</v>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>0.584</v>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v>0.578</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" s="7" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>0291</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>CHB</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>0.06320000000000001</v>
+      </c>
+      <c r="F71" s="4" t="n">
+        <v>603800</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H71" t="n">
+        <v>80.88</v>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>2.391</v>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>2.123</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" s="7" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0321</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>SDCG</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="E72" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="4" t="n">
+        <v>601600</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H72" t="n">
+        <v>70.22</v>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" s="7" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>AMBANK</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="E73" s="10" t="n">
+        <v>-0.0201</v>
+      </c>
+      <c r="F73" s="4" t="n">
+        <v>562600</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H73" t="n">
+        <v>30.11</v>
+      </c>
+      <c r="I73" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>6.571</v>
+      </c>
+      <c r="K73" s="2" t="n">
+        <v>6.865</v>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" s="7" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>5317</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>CPETECH</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>0.0292</v>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>546300</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H74" t="n">
+        <v>64.52</v>
+      </c>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>1.285</v>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v>1.184</v>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" s="7" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>0372</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>CHEEDING</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="E75" s="10" t="n">
+        <v>-0.0077</v>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>523800</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H75" t="n">
+        <v>58.19</v>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>0.617</v>
+      </c>
+      <c r="K75" s="2" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M7"/>
+  <autoFilter ref="A1:M75"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-07/bursa-report-2026-10-07.xlsx
+++ b/docs/downloads/2026-10-07/bursa-report-2026-10-07.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-07" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-07'!$A$1:$M$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-07'!$A$1:$M$119</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M75"/>
+  <dimension ref="A1:M119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -552,19 +552,19 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.06860000000000001</v>
+        <v>0.05139999999999999</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>81712800</v>
+        <v>111396700</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>1.48</v>
+        <v>2.02</v>
       </c>
       <c r="H2" t="n">
-        <v>77.87</v>
+        <v>76.86</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.773</v>
+        <v>0.771</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.704</v>
+        <v>0.703</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" s="7" t="inlineStr"/>
@@ -588,28 +588,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0043</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MTRONIC</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.005</v>
+        <v>0.09</v>
       </c>
       <c r="E3" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>64189800</v>
+        <v>73261400</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>66.40000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="H3" t="n">
-        <v>47.04</v>
+        <v>21.78</v>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.007</v>
+        <v>0.195</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.006</v>
+        <v>0.413</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" s="7" t="inlineStr"/>
@@ -633,39 +633,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>0043</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>MTRONIC</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E4" s="8" t="n">
-        <v>0</v>
+        <v>0.01</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>45362000</v>
+        <v>64444900</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.09</v>
+        <v>66.66</v>
       </c>
       <c r="H4" t="n">
-        <v>21.78</v>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.23</v>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.195</v>
+        <v>0.007</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.413</v>
+        <v>0.006</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
@@ -687,19 +687,19 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.5</v>
+        <v>0.485</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.05429999999999999</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>28772000</v>
+        <v>37796400</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>1.27</v>
+        <v>1.67</v>
       </c>
       <c r="H5" t="n">
-        <v>74.92</v>
+        <v>73.14</v>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.409</v>
+        <v>0.407</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.343</v>
+        <v>0.342</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -732,19 +732,19 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.34</v>
+        <v>0.335</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.0303</v>
+        <v>0.0152</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>17826600</v>
+        <v>31430200</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.36</v>
+        <v>0.64</v>
       </c>
       <c r="H6" t="n">
-        <v>79.56</v>
+        <v>78.84</v>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
@@ -768,40 +768,33 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>SLGC Berhad</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>-0.04</v>
+        <v>0.255</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.02</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>17075600</v>
+        <v>23305600</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="H7" t="n">
-        <v>61.99</v>
+        <v>0.28</v>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J7" s="2" t="n">
-        <v>0.348</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>0.227</v>
-      </c>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="2" t="n"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
     </row>
@@ -813,33 +806,40 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SLGC Berhad</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>0.04</v>
+        <v>0.36</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>-0.04</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>14628200</v>
+        <v>19772000</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.17</v>
+        <v>0.48</v>
+      </c>
+      <c r="H8" t="n">
+        <v>61.99</v>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J8" s="2" t="n"/>
-      <c r="K8" s="2" t="n"/>
+      <c r="J8" s="2" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0.227</v>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
     </row>
@@ -851,28 +851,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>9393</t>
+          <t>0163</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ITRONIC</t>
+          <t>CAREPLS</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>-0.1667</v>
+        <v>0.09</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>14254600</v>
+        <v>15886500</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>11.59</v>
+        <v>1.49</v>
       </c>
       <c r="H9" t="n">
-        <v>37.04</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
@@ -880,10 +880,10 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.031</v>
+        <v>0.083</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.031</v>
+        <v>0.078</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
@@ -896,39 +896,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0163</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CAREPLS</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>0</v>
+        <v>0.6</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>-0.0083</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>12469100</v>
+        <v>14791400</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>1.17</v>
+        <v>0.57</v>
       </c>
       <c r="H10" t="n">
-        <v>64.26000000000001</v>
-      </c>
-      <c r="I10" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.69</v>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.083</v>
+        <v>0.575</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.078</v>
+        <v>0.501</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
@@ -941,39 +941,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>9393</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>ITRONIC</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>0.0446</v>
+        <v>0.025</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>-0.1667</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>10193600</v>
+        <v>14404600</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.8</v>
+        <v>11.71</v>
       </c>
       <c r="H11" t="n">
-        <v>64.48999999999999</v>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.04</v>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.082</v>
+        <v>0.031</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1.035</v>
+        <v>0.031</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
@@ -986,28 +986,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>-0.0083</v>
+        <v>1.14</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0.0179</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>7775400</v>
+        <v>14364300</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.3</v>
+        <v>1.13</v>
       </c>
       <c r="H12" t="n">
-        <v>68.69</v>
+        <v>61.25</v>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
@@ -1015,10 +1015,10 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.575</v>
+        <v>1.079</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.501</v>
+        <v>1.035</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
@@ -1031,28 +1031,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1.27</v>
+        <v>0.65</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0.016</v>
+        <v>0.0317</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>7396800</v>
+        <v>11889700</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.74</v>
+        <v>0.65</v>
       </c>
       <c r="H13" t="n">
-        <v>65.45999999999999</v>
+        <v>67.37</v>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.175</v>
+        <v>0.571</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>1.119</v>
+        <v>0.511</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
@@ -1076,28 +1076,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7191</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ADVENTA</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>0.09089999999999999</v>
+        <v>1.25</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>7356700</v>
+        <v>9532300</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>13.12</v>
+        <v>0.96</v>
       </c>
       <c r="H14" t="n">
-        <v>77.04000000000001</v>
+        <v>63.49</v>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
@@ -1105,10 +1105,10 @@
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.143</v>
+        <v>1.173</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.135</v>
+        <v>1.119</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
@@ -1121,39 +1121,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>7191</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>ADVENTA</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.395</v>
+        <v>0.165</v>
       </c>
       <c r="E15" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>6707000</v>
+        <v>9326100</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.59</v>
+        <v>16.64</v>
       </c>
       <c r="H15" t="n">
-        <v>38.38</v>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.63</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.404</v>
+        <v>0.141</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.411</v>
+        <v>0.134</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
@@ -1166,28 +1166,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7803</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>HEXCARE</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>0.1667</v>
+        <v>7.38</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>-0.0416</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>5898500</v>
+        <v>7540700</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>3.39</v>
+        <v>0.62</v>
       </c>
       <c r="H16" t="n">
-        <v>63.59</v>
+        <v>34.45</v>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.062</v>
+        <v>7.729</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.061</v>
+        <v>7.751</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
@@ -1211,39 +1211,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.305</v>
+        <v>0.395</v>
       </c>
       <c r="E17" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>4759400</v>
+        <v>6813000</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.77</v>
+        <v>0.6</v>
       </c>
       <c r="H17" t="n">
-        <v>71.65000000000001</v>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.38</v>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.288</v>
+        <v>0.404</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.273</v>
+        <v>0.411</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
@@ -1256,28 +1256,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>7803</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>HEXCARE</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>7.45</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>-0.0325</v>
+        <v>0.065</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>0.0833</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>4004100</v>
+        <v>6550900</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.33</v>
+        <v>3.76</v>
       </c>
       <c r="H18" t="n">
-        <v>36.54</v>
+        <v>57.12</v>
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>7.736</v>
+        <v>0.061</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>7.752</v>
+        <v>0.061</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1301,28 +1301,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>COMFORT</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>0.0571</v>
+        <v>0.46</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>-0.0316</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>3960600</v>
+        <v>6438900</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>3.24</v>
+        <v>0.67</v>
       </c>
       <c r="H19" t="n">
-        <v>71.83</v>
+        <v>53.38</v>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
@@ -1330,10 +1330,10 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.162</v>
+        <v>0.454</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.153</v>
+        <v>0.423</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1346,28 +1346,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>COMFORT</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.84</v>
+        <v>0.175</v>
       </c>
       <c r="E20" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>3651600</v>
+        <v>6331100</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.28</v>
+        <v>5.18</v>
       </c>
       <c r="H20" t="n">
-        <v>66.81999999999999</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.764</v>
+        <v>0.161</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.708</v>
+        <v>0.153</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1391,28 +1391,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.825</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>-0.0179</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>3565100</v>
+        <v>5707700</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.57</v>
+        <v>0.43</v>
       </c>
       <c r="H21" t="n">
-        <v>75.2</v>
+        <v>63.55</v>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
@@ -1420,10 +1420,10 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.732</v>
+        <v>0.762</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.654</v>
+        <v>0.708</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1436,28 +1436,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>0.02</v>
+        <v>0.305</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>3263100</v>
+        <v>5533900</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.12</v>
+        <v>0.9</v>
       </c>
       <c r="H22" t="n">
-        <v>61.53</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.484</v>
+        <v>0.288</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.477</v>
+        <v>0.273</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1481,39 +1481,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>0131</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>DFX</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
         <v>0.15</v>
       </c>
-      <c r="E23" s="8" t="n">
-        <v>0</v>
+      <c r="E23" s="10" t="n">
+        <v>-0.0323</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>3224500</v>
+        <v>5021300</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.17</v>
+        <v>0.72</v>
       </c>
       <c r="H23" t="n">
-        <v>30.36</v>
-      </c>
-      <c r="I23" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>78.90000000000001</v>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.168</v>
+        <v>0.111</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.204</v>
+        <v>0.092</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1526,28 +1526,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.2</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E24" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>3091200</v>
+        <v>4847300</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.13</v>
+        <v>0.32</v>
       </c>
       <c r="H24" t="n">
-        <v>54.23</v>
+        <v>50.2</v>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.197</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.183</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1571,28 +1571,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>-0.0101</v>
+        <v>0.15</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>2868600</v>
+        <v>4806700</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.08</v>
+        <v>0.26</v>
       </c>
       <c r="H25" t="n">
-        <v>28.04</v>
+        <v>30.36</v>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.168</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.768</v>
+        <v>0.204</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1616,39 +1616,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.47</v>
+        <v>9.9</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>-0.0105</v>
+        <v>-0.006999999999999999</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2676700</v>
+        <v>4583400</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.28</v>
+        <v>0.38</v>
       </c>
       <c r="H26" t="n">
-        <v>56.29</v>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.44</v>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.455</v>
+        <v>10.072</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.424</v>
+        <v>10.234</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1661,28 +1661,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>0.022</v>
+        <v>0.175</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>-0.0278</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2646000</v>
+        <v>4231800</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>62.39</v>
+        <v>59.26</v>
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.775</v>
+        <v>0.164</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>1.616</v>
+        <v>0.129</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1706,28 +1706,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5142</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>WASCO</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.775</v>
+        <v>0.83</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.0915</v>
+        <v>0.0247</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2560800</v>
+        <v>4191700</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>2.23</v>
+        <v>0.67</v>
       </c>
       <c r="H28" t="n">
-        <v>61.84</v>
+        <v>74.26000000000001</v>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.732</v>
+        <v>0.731</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.721</v>
+        <v>0.653</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1751,39 +1751,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>0.0164</v>
+        <v>0.49</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>-0.0101</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2384600</v>
+        <v>4116000</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.23</v>
+        <v>0.11</v>
       </c>
       <c r="H29" t="n">
-        <v>55.75</v>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.04</v>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.609</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.61</v>
+        <v>0.768</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1796,39 +1796,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5115</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ALAM</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.235</v>
+        <v>1.84</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>0.175</v>
+        <v>0.011</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2328700</v>
+        <v>3807600</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>4.19</v>
+        <v>0.17</v>
       </c>
       <c r="H30" t="n">
-        <v>53.85</v>
-      </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.91</v>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.225</v>
+        <v>1.773</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.242</v>
+        <v>1.615</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1841,39 +1841,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>3.61</v>
+        <v>0.505</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0.0434</v>
+        <v>0.01</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2284100</v>
+        <v>3618200</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="H31" t="n">
-        <v>54.81</v>
-      </c>
-      <c r="I31" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.08</v>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>3.582</v>
+        <v>0.483</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>2.669</v>
+        <v>0.477</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1886,39 +1886,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E32" s="8" t="n">
-        <v>0</v>
+        <v>0.305</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>0.0339</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2066500</v>
+        <v>3548200</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.13</v>
+        <v>0.35</v>
       </c>
       <c r="H32" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="I32" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.3</v>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.276</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.305</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1931,28 +1931,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>0209</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>AIMFLEX</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>0.0151</v>
+        <v>0.11</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1757800</v>
+        <v>3400900</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.75</v>
+        <v>0.53</v>
       </c>
       <c r="H33" t="n">
-        <v>33.03</v>
+        <v>41.61</v>
       </c>
       <c r="I33" s="9" t="inlineStr">
         <is>
@@ -1960,10 +1960,10 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.066</v>
+        <v>0.116</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>1.13</v>
+        <v>0.123</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1976,39 +1976,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.2</v>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1745700</v>
+        <v>3281400</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="H34" t="n">
-        <v>65.61</v>
-      </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.23</v>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.569</v>
+        <v>0.197</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.51</v>
+        <v>0.183</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2021,28 +2021,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>6.27</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>0.045</v>
+        <v>0.78</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1699100</v>
+        <v>3210900</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.44</v>
+        <v>0.23</v>
       </c>
       <c r="H35" t="n">
-        <v>62.47</v>
+        <v>53.14</v>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>5.696</v>
+        <v>0.775</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>5.761</v>
+        <v>0.775</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2066,39 +2066,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>5142</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>WASCO</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E36" s="8" t="n">
-        <v>0</v>
+        <v>0.78</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>0.09859999999999999</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>1676900</v>
+        <v>3189400</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>1.78</v>
+        <v>2.78</v>
       </c>
       <c r="H36" t="n">
-        <v>45.51</v>
-      </c>
-      <c r="I36" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.81</v>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.261</v>
+        <v>0.733</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.264</v>
+        <v>0.721</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2111,28 +2111,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.3</v>
+        <v>0.73</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>0.0169</v>
+        <v>0.0282</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>1668300</v>
+        <v>3111300</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.17</v>
+        <v>0.4</v>
       </c>
       <c r="H37" t="n">
-        <v>59.64</v>
+        <v>59.4</v>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
@@ -2140,10 +2140,10 @@
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.276</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.305</v>
+        <v>0.676</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2156,39 +2156,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.82</v>
+        <v>7.26</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>-0.0061</v>
+        <v>-0.0229</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>1639100</v>
+        <v>3068400</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.61</v>
+        <v>0.34</v>
       </c>
       <c r="H38" t="n">
-        <v>81.56</v>
-      </c>
-      <c r="I38" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>21.25</v>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.584</v>
+        <v>7.7</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.455</v>
+        <v>8.144</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2201,28 +2201,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ALPHA</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>-0.0175</v>
+        <v>0.415</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>0.0641</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>1634100</v>
+        <v>3037800</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.76</v>
+        <v>1.86</v>
       </c>
       <c r="H39" t="n">
-        <v>68.5</v>
+        <v>63.21</v>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.255</v>
+        <v>0.386</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.257</v>
+        <v>0.39</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2246,28 +2246,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E40" s="8" t="n">
-        <v>0</v>
+        <v>0.62</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>0.0164</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>1590800</v>
+        <v>3019900</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.11</v>
+        <v>0.29</v>
       </c>
       <c r="H40" t="n">
-        <v>53.14</v>
+        <v>55.75</v>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.775</v>
+        <v>0.609</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.775</v>
+        <v>0.61</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2291,39 +2291,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>0.0672</v>
+        <v>4.61</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>-0.0128</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>1510200</v>
+        <v>2985600</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>1.11</v>
+        <v>0.18</v>
       </c>
       <c r="H41" t="n">
-        <v>71.61</v>
-      </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.29</v>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.648</v>
+        <v>4.758</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0.613</v>
+        <v>4.906</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2336,28 +2336,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E42" s="8" t="n">
-        <v>0</v>
+        <v>0.41</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>-0.012</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>1444500</v>
+        <v>2978500</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="H42" t="n">
-        <v>66</v>
+        <v>68.03</v>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.344</v>
+        <v>0.386</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.323</v>
+        <v>0.375</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2381,39 +2381,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.79</v>
+        <v>3.56</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>0.0064</v>
+        <v>0.0289</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>1443400</v>
+        <v>2919800</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.88</v>
+        <v>0.25</v>
       </c>
       <c r="H43" t="n">
-        <v>69.79000000000001</v>
-      </c>
-      <c r="I43" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.77</v>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.699</v>
+        <v>3.577</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.6860000000000001</v>
+        <v>2.668</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2426,39 +2426,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>2.18</v>
+        <v>0.3</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>0.0046</v>
+        <v>0.0169</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>1431500</v>
+        <v>2801400</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.1</v>
+        <v>0.19</v>
       </c>
       <c r="H44" t="n">
-        <v>43.79</v>
-      </c>
-      <c r="I44" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.62</v>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>2.248</v>
+        <v>0.291</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>2.223</v>
+        <v>0.279</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2471,39 +2471,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E45" s="8" t="n">
-        <v>0</v>
+        <v>2.11</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>0.0144</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>1422400</v>
+        <v>2748200</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="H45" t="n">
-        <v>72.51000000000001</v>
-      </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.77</v>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.387</v>
+        <v>2.1</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.375</v>
+        <v>2.078</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2516,28 +2516,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>0.0515</v>
+        <v>0.36</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>-0.0137</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>1319100</v>
+        <v>2703300</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.43</v>
+        <v>0.35</v>
       </c>
       <c r="H46" t="n">
-        <v>80.78</v>
+        <v>62.63</v>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.208</v>
+        <v>0.343</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.985</v>
+        <v>0.323</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2561,38 +2561,40 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E47" s="8" t="n">
-        <v>0</v>
+        <v>6.32</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>0.0533</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>1248400</v>
+        <v>2653700</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.08</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H47" t="n">
-        <v>18.18</v>
-      </c>
-      <c r="I47" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.21</v>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="K47" s="2" t="n"/>
+        <v>5.701</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>5.762</v>
+      </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
     </row>
@@ -2604,39 +2606,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>0.0231</v>
+        <v>2.16</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>-0.0046</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>1237700</v>
+        <v>2630400</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="H48" t="n">
-        <v>63.95</v>
-      </c>
-      <c r="I48" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.1</v>
+      </c>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.657</v>
+        <v>2.247</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>1.679</v>
+        <v>2.222</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2649,39 +2651,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>9.960000000000001</v>
-      </c>
-      <c r="E49" s="10" t="n">
-        <v>-0.001</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>0.0062</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>1200700</v>
+        <v>2579700</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.1</v>
+        <v>0.42</v>
       </c>
       <c r="H49" t="n">
-        <v>37.54</v>
-      </c>
-      <c r="I49" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>72</v>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>10.078</v>
+        <v>0.781</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>10.235</v>
+        <v>0.762</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2694,39 +2696,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5115</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>ALAM</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>2.09</v>
+        <v>0.24</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>0.0048</v>
+        <v>0.2</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>1192200</v>
+        <v>2548800</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.06</v>
+        <v>4.59</v>
       </c>
       <c r="H50" t="n">
-        <v>49.12</v>
-      </c>
-      <c r="I50" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.39</v>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>2.098</v>
+        <v>0.225</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>2.078</v>
+        <v>0.242</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2739,28 +2741,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>2.75</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>0.0036</v>
+        <v>0.0108</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>1155900</v>
+        <v>2490400</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.35</v>
+        <v>0.48</v>
       </c>
       <c r="H51" t="n">
-        <v>70.62</v>
+        <v>66.5</v>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
@@ -2768,10 +2770,10 @@
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>2.591</v>
+        <v>0.904</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>2.251</v>
+        <v>0.86</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2784,28 +2786,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0.47</v>
+        <v>0.63</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>0.033</v>
+        <v>0.0413</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>1146000</v>
+        <v>2486100</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.37</v>
+        <v>0.79</v>
       </c>
       <c r="H52" t="n">
-        <v>74.2</v>
+        <v>63.2</v>
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
@@ -2813,10 +2815,10 @@
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.407</v>
+        <v>0.585</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.362</v>
+        <v>0.579</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2838,19 +2840,19 @@
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="E53" s="10" t="n">
-        <v>-0.002</v>
+        <v>5</v>
+      </c>
+      <c r="E53" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>1063900</v>
+        <v>2223800</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="H53" t="n">
-        <v>60.39</v>
+        <v>61.16</v>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
@@ -2858,10 +2860,10 @@
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>4.896</v>
+        <v>4.897</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>4.627</v>
+        <v>4.628</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2874,39 +2876,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="E54" s="10" t="n">
-        <v>-0.0068</v>
+        <v>1.15</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>0.036</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>1052500</v>
+        <v>2121600</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.21</v>
+        <v>0.44</v>
       </c>
       <c r="H54" t="n">
-        <v>44.42</v>
-      </c>
-      <c r="I54" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>77.15000000000001</v>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.465</v>
+        <v>1.04</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>1.469</v>
+        <v>0.874</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2919,28 +2921,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0249</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>LGMS</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="E55" s="8" t="n">
-        <v>0</v>
+        <v>0.705</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>0.0522</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>1048100</v>
+        <v>1840500</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="H55" t="n">
-        <v>75.3</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
@@ -2948,10 +2950,10 @@
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.514</v>
+        <v>0.647</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0.501</v>
+        <v>0.613</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2964,39 +2966,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>0.795</v>
+        <v>1.01</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0.0127</v>
+        <v>0.0151</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>1005000</v>
+        <v>1827000</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.13</v>
+        <v>0.78</v>
       </c>
       <c r="H56" t="n">
-        <v>55.54</v>
-      </c>
-      <c r="I56" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.03</v>
+      </c>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.777</v>
+        <v>1.066</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0.772</v>
+        <v>1.13</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -3009,28 +3011,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E57" s="10" t="n">
-        <v>-0.011</v>
+        <v>0.795</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>0.0127</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>1002200</v>
+        <v>1813800</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="H57" t="n">
-        <v>60.94</v>
+        <v>55.54</v>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
@@ -3038,10 +3040,10 @@
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.42</v>
+        <v>0.777</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.41</v>
+        <v>0.772</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3054,28 +3056,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="E58" s="8" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>-0.0182</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>974300</v>
+        <v>1783900</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.19</v>
+        <v>0.67</v>
       </c>
       <c r="H58" t="n">
-        <v>64.02</v>
+        <v>79.81</v>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
@@ -3083,10 +3085,10 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.903</v>
+        <v>0.583</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.86</v>
+        <v>0.455</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3099,39 +3101,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>0.535</v>
+        <v>0.79</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>0.019</v>
+        <v>0.0064</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>936200</v>
+        <v>1779000</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.06</v>
+        <v>1.08</v>
       </c>
       <c r="H59" t="n">
-        <v>58.34</v>
-      </c>
-      <c r="I59" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.79000000000001</v>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.511</v>
+        <v>0.699</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0.432</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3144,39 +3146,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>0.0072</v>
+        <v>0.0109</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>904500</v>
+        <v>1746700</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="H60" t="n">
-        <v>70.64</v>
-      </c>
-      <c r="I60" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.64</v>
+      </c>
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>2.614</v>
+        <v>2.786</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>2.571</v>
+        <v>2.689</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3189,39 +3191,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>1.39</v>
+        <v>2.8</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>0.0146</v>
+        <v>0.0036</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>847800</v>
+        <v>1743700</v>
       </c>
       <c r="G61" s="5" t="n">
         <v>0.32</v>
       </c>
       <c r="H61" t="n">
-        <v>57.34</v>
-      </c>
-      <c r="I61" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.09999999999999</v>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.358</v>
+        <v>2.613</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>1.223</v>
+        <v>2.571</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3234,28 +3236,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>0.715</v>
+        <v>0.47</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.033</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>818700</v>
+        <v>1714800</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.11</v>
+        <v>0.55</v>
       </c>
       <c r="H62" t="n">
-        <v>56.78</v>
+        <v>74.2</v>
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
@@ -3263,10 +3265,10 @@
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.407</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0.675</v>
+        <v>0.362</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3279,28 +3281,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>ALPHA</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>0.52</v>
+        <v>0.275</v>
       </c>
       <c r="E63" s="10" t="n">
-        <v>-0.0095</v>
+        <v>-0.0351</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>798100</v>
+        <v>1703000</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.21</v>
+        <v>0.79</v>
       </c>
       <c r="H63" t="n">
-        <v>69.04000000000001</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
@@ -3308,10 +3310,10 @@
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.462</v>
+        <v>0.255</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0.447</v>
+        <v>0.257</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3333,19 +3335,19 @@
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E64" s="8" t="n">
-        <v>0</v>
+        <v>1.24</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>-0.008</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>792500</v>
+        <v>1702300</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.08</v>
+        <v>0.17</v>
       </c>
       <c r="H64" t="n">
-        <v>33.87</v>
+        <v>32.4</v>
       </c>
       <c r="I64" s="9" t="inlineStr">
         <is>
@@ -3353,7 +3355,7 @@
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.296</v>
+        <v>1.295</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>1.396</v>
@@ -3369,28 +3371,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>3.19</v>
+        <v>1.43</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>0.0224</v>
+        <v>0.0515</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>780400</v>
+        <v>1682600</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.2</v>
+        <v>0.54</v>
       </c>
       <c r="H65" t="n">
-        <v>75.12</v>
+        <v>80.78</v>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
@@ -3398,10 +3400,10 @@
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>2.631</v>
+        <v>1.208</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>1.987</v>
+        <v>0.985</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3414,39 +3416,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="E66" s="10" t="n">
-        <v>-0.0069</v>
+        <v>0.26</v>
+      </c>
+      <c r="E66" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>695300</v>
+        <v>1681900</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.08</v>
+        <v>1.79</v>
       </c>
       <c r="H66" t="n">
-        <v>64.69</v>
-      </c>
-      <c r="I66" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.51</v>
+      </c>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.663</v>
+        <v>0.261</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.599</v>
+        <v>0.264</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3459,39 +3461,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>VSTECS</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E67" s="8" t="n">
-        <v>0</v>
+        <v>1.75</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>0.0116</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>693300</v>
+        <v>1671300</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.31</v>
+        <v>1.09</v>
       </c>
       <c r="H67" t="n">
-        <v>48.46</v>
-      </c>
-      <c r="I67" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.19</v>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>1.655</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>1.678</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3504,28 +3506,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>2.78</v>
+        <v>0.285</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0.0072</v>
+        <v>0.0179</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>688900</v>
+        <v>1625100</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.05</v>
+        <v>0.24</v>
       </c>
       <c r="H68" t="n">
-        <v>51.7</v>
+        <v>39.83</v>
       </c>
       <c r="I68" s="9" t="inlineStr">
         <is>
@@ -3533,10 +3535,10 @@
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>2.785</v>
+        <v>0.292</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>2.688</v>
+        <v>0.309</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3549,39 +3551,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>7.38</v>
+        <v>0.635</v>
       </c>
       <c r="E69" s="10" t="n">
-        <v>-0.0067</v>
+        <v>-0.0231</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>636800</v>
+        <v>1543000</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="H69" t="n">
-        <v>24.16</v>
-      </c>
-      <c r="I69" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.38</v>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>7.711</v>
+        <v>0.616</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>8.146000000000001</v>
+        <v>0.609</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3594,39 +3596,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.615</v>
+        <v>0.535</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0.0165</v>
+        <v>0.019</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>628500</v>
+        <v>1522800</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="H70" t="n">
-        <v>60.17</v>
-      </c>
-      <c r="I70" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.34</v>
+      </c>
+      <c r="I70" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.584</v>
+        <v>0.511</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0.578</v>
+        <v>0.432</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3639,39 +3641,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0291</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CHB</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="E71" s="3" t="n">
-        <v>0.06320000000000001</v>
+        <v>6.25</v>
+      </c>
+      <c r="E71" s="10" t="n">
+        <v>-0.034</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>603800</v>
+        <v>1471400</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="H71" t="n">
-        <v>80.88</v>
-      </c>
-      <c r="I71" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.93</v>
+      </c>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>2.391</v>
+        <v>6.562</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>2.123</v>
+        <v>6.863</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3684,28 +3686,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E72" s="8" t="n">
-        <v>0</v>
+        <v>0.45</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>-0.011</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>601600</v>
+        <v>1458200</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.1</v>
+        <v>0.23</v>
       </c>
       <c r="H72" t="n">
-        <v>70.22</v>
+        <v>60.94</v>
       </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
@@ -3713,10 +3715,10 @@
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.781</v>
+        <v>0.42</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0.762</v>
+        <v>0.41</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
@@ -3729,39 +3731,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>6.34</v>
-      </c>
-      <c r="E73" s="10" t="n">
-        <v>-0.0201</v>
+        <v>3.15</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>0.009599999999999999</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>562600</v>
+        <v>1448000</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.14</v>
+        <v>0.36</v>
       </c>
       <c r="H73" t="n">
-        <v>30.11</v>
-      </c>
-      <c r="I73" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.45</v>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>6.571</v>
+        <v>2.627</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>6.865</v>
+        <v>1.986</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3774,28 +3776,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0399</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>1.41</v>
+        <v>0.49</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>0.0292</v>
+        <v>0.0208</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>546300</v>
+        <v>1444300</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.13</v>
+        <v>0.72</v>
       </c>
       <c r="H74" t="n">
-        <v>64.52</v>
+        <v>62.32</v>
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
@@ -3803,10 +3805,10 @@
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1.285</v>
+        <v>0.458</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>1.184</v>
+        <v>0.461</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3819,28 +3821,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>0348</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>CLITE</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="E75" s="10" t="n">
-        <v>-0.0077</v>
+        <v>0.26</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>0.0196</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>523800</v>
+        <v>1443300</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.14</v>
+        <v>0.89</v>
       </c>
       <c r="H75" t="n">
-        <v>58.19</v>
+        <v>73.25</v>
       </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
@@ -3848,16 +3850,1990 @@
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.617</v>
+        <v>0.23</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0.609</v>
+        <v>0.199</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
     </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>LGMS</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E76" s="10" t="n">
+        <v>-0.008800000000000001</v>
+      </c>
+      <c r="F76" s="4" t="n">
+        <v>1425200</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H76" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>0.513</v>
+      </c>
+      <c r="K76" s="2" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" s="7" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>5327</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>MEGAFB</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>0.0036</v>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>1420400</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H77" t="n">
+        <v>70.62</v>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>2.591</v>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" s="7" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>0104</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>GENETEC</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E78" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>1369700</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H78" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" s="7" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>0469</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>GTA</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="E79" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>1305000</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H79" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="I79" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="K79" s="2" t="n"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" s="7" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0166</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>INARI</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="E80" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>1291900</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H80" t="n">
+        <v>58.79</v>
+      </c>
+      <c r="I80" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>2.586</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>2.487</v>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" s="7" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>7155</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>SKPRES</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="E81" s="10" t="n">
+        <v>-0.0132</v>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>1280100</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H81" t="n">
+        <v>68.06</v>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" s="7" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>0083</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>NOTION</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>0.0139</v>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>1279200</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H82" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>0.664</v>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" s="7" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>5148</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>UEMS</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="E83" s="10" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F83" s="4" t="n">
+        <v>1266000</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H83" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="I83" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" s="7" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>0259</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>SNS</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>0.0198</v>
+      </c>
+      <c r="F84" s="4" t="n">
+        <v>1264100</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H84" t="n">
+        <v>48.37</v>
+      </c>
+      <c r="I84" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" s="7" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>6742</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>YTLPOWR</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="E85" s="10" t="n">
+        <v>-0.0036</v>
+      </c>
+      <c r="F85" s="4" t="n">
+        <v>1158500</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H85" t="n">
+        <v>48.54</v>
+      </c>
+      <c r="I85" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>5.304</v>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" s="7" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>0468</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>UNIPAC</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E86" s="10" t="n">
+        <v>-0.0357</v>
+      </c>
+      <c r="F86" s="4" t="n">
+        <v>1138700</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H86" t="n">
+        <v>31.12</v>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="n"/>
+      <c r="K86" s="2" t="n"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" s="7" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>8052</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>CGB</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="E87" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="4" t="n">
+        <v>1138500</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H87" t="n">
+        <v>46.41</v>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="K87" s="2" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" s="7" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>0291</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>CHB</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>0.0595</v>
+      </c>
+      <c r="F88" s="4" t="n">
+        <v>1103400</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H88" t="n">
+        <v>80.68000000000001</v>
+      </c>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>2.122</v>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" s="7" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>5337</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ECOSHOP</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="E89" s="10" t="n">
+        <v>-0.0068</v>
+      </c>
+      <c r="F89" s="4" t="n">
+        <v>1099500</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H89" t="n">
+        <v>44.42</v>
+      </c>
+      <c r="I89" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>1.465</v>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>1.469</v>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" s="7" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>5127</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ARREIT</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>0.0132</v>
+      </c>
+      <c r="F90" s="4" t="n">
+        <v>1092600</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="H90" t="n">
+        <v>64.69</v>
+      </c>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" s="7" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>9679</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>WCT</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="E91" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="4" t="n">
+        <v>1046700</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H91" t="n">
+        <v>38.26</v>
+      </c>
+      <c r="I91" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" s="7" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>0198</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>GDB</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="F92" s="4" t="n">
+        <v>1028000</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="H92" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="I92" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>0.443</v>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" s="7" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>0391</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>AMBEST</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>0.0146</v>
+      </c>
+      <c r="F93" s="4" t="n">
+        <v>951200</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H93" t="n">
+        <v>57.34</v>
+      </c>
+      <c r="I93" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>1.358</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>1.223</v>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" s="7" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>PENTA</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="E94" s="10" t="n">
+        <v>-0.0296</v>
+      </c>
+      <c r="F94" s="4" t="n">
+        <v>936300</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H94" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>5.381</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>5.328</v>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" s="7" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>0368</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>OXB</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="E95" s="10" t="n">
+        <v>-0.019</v>
+      </c>
+      <c r="F95" s="4" t="n">
+        <v>933100</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H95" t="n">
+        <v>67.16</v>
+      </c>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>0.447</v>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" s="7" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>8664</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>SPSETIA</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E96" s="10" t="n">
+        <v>-0.0203</v>
+      </c>
+      <c r="F96" s="4" t="n">
+        <v>919200</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H96" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="I96" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>0.764</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>0.824</v>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" s="7" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>5317</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>CPETECH</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>0.0219</v>
+      </c>
+      <c r="F97" s="4" t="n">
+        <v>896400</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H97" t="n">
+        <v>63.86</v>
+      </c>
+      <c r="I97" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>1.284</v>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>1.184</v>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" s="7" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>4197</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>SIME</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="E98" s="10" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="F98" s="4" t="n">
+        <v>789400</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H98" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="I98" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>2.457</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>2.342</v>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" s="7" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>0127</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>JHM</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>0.0167</v>
+      </c>
+      <c r="F99" s="4" t="n">
+        <v>781900</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H99" t="n">
+        <v>72.16</v>
+      </c>
+      <c r="I99" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" s="7" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>0339</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>CBHB</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E100" s="10" t="n">
+        <v>-0.008699999999999999</v>
+      </c>
+      <c r="F100" s="4" t="n">
+        <v>736500</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H100" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="I100" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>1.063</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>0.904</v>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" s="7" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>UUE</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E101" s="10" t="n">
+        <v>-0.0064</v>
+      </c>
+      <c r="F101" s="4" t="n">
+        <v>705600</v>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H101" t="n">
+        <v>67.56999999999999</v>
+      </c>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>0.642</v>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" s="7" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>0056</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>NCT</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E102" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="4" t="n">
+        <v>693300</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H102" t="n">
+        <v>48.46</v>
+      </c>
+      <c r="I102" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" s="7" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>5356</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>STRATUS</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="E103" s="10" t="n">
+        <v>-0.0064</v>
+      </c>
+      <c r="F103" s="4" t="n">
+        <v>683000</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H103" t="n">
+        <v>59.22</v>
+      </c>
+      <c r="I103" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>2.984</v>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>2.804</v>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" s="7" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1171</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>MBSB</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="E104" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="4" t="n">
+        <v>681800</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H104" t="n">
+        <v>35.63</v>
+      </c>
+      <c r="I104" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" s="7" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>0167</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>MCLEAN</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E105" s="10" t="n">
+        <v>-0.0128</v>
+      </c>
+      <c r="F105" s="4" t="n">
+        <v>676500</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H105" t="n">
+        <v>51.63</v>
+      </c>
+      <c r="I105" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" s="7" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>0340</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>NORTHERN</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E106" s="10" t="n">
+        <v>-0.0234</v>
+      </c>
+      <c r="F106" s="4" t="n">
+        <v>674400</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H106" t="n">
+        <v>73.41</v>
+      </c>
+      <c r="I106" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" s="7" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>0.0244</v>
+      </c>
+      <c r="F107" s="4" t="n">
+        <v>630300</v>
+      </c>
+      <c r="G107" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H107" t="n">
+        <v>73.09</v>
+      </c>
+      <c r="I107" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>2.948</v>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>2.779</v>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" s="7" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>0215</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>SLVEST</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E108" s="10" t="n">
+        <v>-0.0092</v>
+      </c>
+      <c r="F108" s="4" t="n">
+        <v>618100</v>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H108" t="n">
+        <v>70.17</v>
+      </c>
+      <c r="I108" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>3.923</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>3.399</v>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" s="7" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>0217</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>PWRWELL</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E109" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="4" t="n">
+        <v>617700</v>
+      </c>
+      <c r="G109" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H109" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="I109" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>1.148</v>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>1.057</v>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" s="7" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>GCB</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E110" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="4" t="n">
+        <v>598800</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H110" t="n">
+        <v>43.85</v>
+      </c>
+      <c r="I110" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="n">
+        <v>1.334</v>
+      </c>
+      <c r="K110" s="2" t="n">
+        <v>1.307</v>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" s="7" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>5285</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>SDG</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="E111" s="10" t="n">
+        <v>-0.0049</v>
+      </c>
+      <c r="F111" s="4" t="n">
+        <v>597600</v>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H111" t="n">
+        <v>40.43</v>
+      </c>
+      <c r="I111" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" s="7" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>0466</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>SRKKAI</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="E112" s="10" t="n">
+        <v>-0.009300000000000001</v>
+      </c>
+      <c r="F112" s="4" t="n">
+        <v>557200</v>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H112" t="n">
+        <v>52.14</v>
+      </c>
+      <c r="I112" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>0.534</v>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" s="7" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>5878</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>KPJ</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="E113" s="10" t="n">
+        <v>-0.0195</v>
+      </c>
+      <c r="F113" s="4" t="n">
+        <v>554700</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H113" t="n">
+        <v>34.84</v>
+      </c>
+      <c r="I113" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>2.634</v>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>2.799</v>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" s="7" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>GENTING</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="E114" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="4" t="n">
+        <v>546500</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H114" t="n">
+        <v>32.96</v>
+      </c>
+      <c r="I114" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>2.036</v>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" s="7" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>0120</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>VIS</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E115" s="10" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F115" s="4" t="n">
+        <v>541300</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H115" t="n">
+        <v>84.91</v>
+      </c>
+      <c r="I115" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" s="7" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>0045</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>SSB8</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="E116" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="4" t="n">
+        <v>534000</v>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H116" t="n">
+        <v>57.54</v>
+      </c>
+      <c r="I116" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" s="7" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>7579</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>AWC</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="E117" s="10" t="n">
+        <v>-0.0216</v>
+      </c>
+      <c r="F117" s="4" t="n">
+        <v>525400</v>
+      </c>
+      <c r="G117" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H117" t="n">
+        <v>69.78</v>
+      </c>
+      <c r="I117" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" s="7" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>4715</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>GENM</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="E118" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="4" t="n">
+        <v>519100</v>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H118" t="n">
+        <v>31.04</v>
+      </c>
+      <c r="I118" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="n">
+        <v>1.517</v>
+      </c>
+      <c r="K118" s="2" t="n">
+        <v>1.631</v>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" s="7" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>5005</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>UNISEM</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="F119" s="4" t="n">
+        <v>500900</v>
+      </c>
+      <c r="G119" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H119" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="I119" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="n">
+        <v>4.349</v>
+      </c>
+      <c r="K119" s="2" t="n">
+        <v>4.369</v>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M75"/>
+  <autoFilter ref="A1:M119"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-07/bursa-report-2026-10-07.xlsx
+++ b/docs/downloads/2026-10-07/bursa-report-2026-10-07.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-07" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-07'!$A$1:$M$152</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-07'!$A$1:$M$173</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M152"/>
+  <dimension ref="A1:M173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.835</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.1761</v>
+        <v>0.1408</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>5231300</v>
+        <v>6974100</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>4.56</v>
+        <v>6.08</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>70.98999999999999</v>
+        <v>67.77</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.738</v>
+        <v>0.736</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0.722</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多，但RSI达70.99已近超买，现价高于50日均线约15.7%，信号可靠性偏弱。</t>
+          <t>SAR转多，现价0.81高于50日均线0.722约12%，RSI 67.77接近超买区，信号偏强但需留意短线过热。</t>
         </is>
       </c>
     </row>
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>0.905</v>
+        <v>0.89</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>0.0343</v>
+        <v>0.0171</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>146315000</v>
+        <v>175869100</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>2.66</v>
+        <v>3.19</v>
       </c>
       <c r="H3" t="n">
-        <v>75.75</v>
+        <v>74.53</v>
       </c>
       <c r="I3" s="13" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="J3" s="9" t="n">
-        <v>0.77</v>
+        <v>0.768</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>0.703</v>
@@ -670,10 +670,10 @@
         <v>0</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>86699100</v>
+        <v>124754000</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.17</v>
+        <v>0.24</v>
       </c>
       <c r="H4" t="n">
         <v>21.78</v>
@@ -709,23 +709,23 @@
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>1</v>
+        <v>0.005</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>64501700</v>
+        <v>64663700</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>66.72</v>
+        <v>66.89</v>
       </c>
       <c r="H5" t="n">
-        <v>55.23</v>
-      </c>
-      <c r="I5" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.04</v>
+      </c>
+      <c r="I5" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J5" s="9" t="n">
@@ -754,19 +754,19 @@
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.48</v>
+        <v>0.465</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>0.0435</v>
+        <v>0.0109</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>44230000</v>
+        <v>52688500</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>1.95</v>
+        <v>2.33</v>
       </c>
       <c r="H6" t="n">
-        <v>72.48999999999999</v>
+        <v>70.33</v>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.407</v>
+        <v>0.405</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>0.342</v>
@@ -805,10 +805,10 @@
         <v>0</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>39455600</v>
+        <v>40472800</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="H7" t="n">
         <v>78.06999999999999</v>
@@ -850,10 +850,10 @@
         <v>0.02</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>25903300</v>
+        <v>26526600</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
@@ -873,39 +873,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>9393</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>ITRONIC</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.36</v>
+        <v>0.025</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>-0.04</v>
+        <v>-0.1667</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>20359100</v>
+        <v>23213200</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.49</v>
+        <v>18.87</v>
       </c>
       <c r="H9" t="n">
-        <v>61.99</v>
-      </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.04</v>
+      </c>
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.348</v>
+        <v>0.031</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.227</v>
+        <v>0.031</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -918,28 +918,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>0.0238</v>
+        <v>0.36</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>-0.04</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>18631200</v>
+        <v>20532500</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1.01</v>
+        <v>0.49</v>
       </c>
       <c r="H10" t="n">
-        <v>66.8</v>
+        <v>61.99</v>
       </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.57</v>
+        <v>0.348</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.511</v>
+        <v>0.227</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -963,39 +963,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>9393</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ITRONIC</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="E11" s="17" t="n">
-        <v>-0.1667</v>
+        <v>0.65</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>0.0317</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>17687200</v>
+        <v>20463900</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>14.38</v>
+        <v>1.11</v>
       </c>
       <c r="H11" t="n">
-        <v>37.04</v>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.37</v>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.031</v>
+        <v>0.571</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.031</v>
+        <v>0.511</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1017,19 +1017,19 @@
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>0.0089</v>
+        <v>1.11</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>-0.0089</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>16838200</v>
+        <v>19299100</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="H12" t="n">
-        <v>60.03</v>
+        <v>56.89</v>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>1.078</v>
+        <v>1.076</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>1.034</v>
@@ -1068,10 +1068,10 @@
         <v>0</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>16014800</v>
+        <v>16217500</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="H13" t="n">
         <v>64.26000000000001</v>
@@ -1113,10 +1113,10 @@
         <v>-0.0165</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>14841200</v>
+        <v>15107300</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="H14" t="n">
         <v>65.73999999999999</v>
@@ -1143,39 +1143,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>1.24</v>
+        <v>7.36</v>
       </c>
       <c r="E15" s="17" t="n">
-        <v>-0.008</v>
+        <v>-0.0442</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>11196100</v>
+        <v>12894600</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="H15" t="n">
-        <v>61.73</v>
-      </c>
-      <c r="I15" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.89</v>
+      </c>
+      <c r="I15" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>1.172</v>
+        <v>7.728</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>1.119</v>
+        <v>7.75</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1188,39 +1188,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>7.37</v>
+        <v>1.22</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>-0.0429</v>
+        <v>-0.024</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>11177900</v>
+        <v>12798900</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.91</v>
+        <v>1.29</v>
       </c>
       <c r="H16" t="n">
-        <v>34.17</v>
-      </c>
-      <c r="I16" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.48</v>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>7.728</v>
+        <v>1.17</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>7.75</v>
+        <v>1.118</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1233,28 +1233,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7191</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ADVENTA</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E17" s="15" t="n">
-        <v>0</v>
+        <v>0.505</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>0.01</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>9655500</v>
+        <v>10069400</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>17.23</v>
+        <v>0.38</v>
       </c>
       <c r="H17" t="n">
-        <v>71.63</v>
+        <v>60.08</v>
       </c>
       <c r="I17" s="13" t="inlineStr">
         <is>
@@ -1262,10 +1262,10 @@
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.141</v>
+        <v>0.483</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.134</v>
+        <v>0.477</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1278,28 +1278,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>0.04650000000000001</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>9174200</v>
+        <v>10023500</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.44</v>
+        <v>0.65</v>
       </c>
       <c r="H18" t="n">
-        <v>45.69</v>
+        <v>50.2</v>
       </c>
       <c r="I18" s="16" t="inlineStr">
         <is>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.228</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.243</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1323,39 +1323,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E19" s="15" t="n">
-        <v>0</v>
+        <v>0.22</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>0.0233</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>8928300</v>
+        <v>10010200</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.34</v>
+        <v>0.48</v>
       </c>
       <c r="H19" t="n">
-        <v>58.53</v>
-      </c>
-      <c r="I19" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.12</v>
+      </c>
+      <c r="I19" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.483</v>
+        <v>0.227</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.477</v>
+        <v>0.243</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1368,39 +1368,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>7191</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>ADVENTA</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="E20" s="17" t="n">
-        <v>-0.0278</v>
+        <v>0.165</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>8270600</v>
+        <v>9708700</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.13</v>
+        <v>17.32</v>
       </c>
       <c r="H20" t="n">
-        <v>59.26</v>
-      </c>
-      <c r="I20" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.63</v>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.164</v>
+        <v>0.141</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.129</v>
+        <v>0.134</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1413,28 +1413,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="E21" s="15" t="n">
-        <v>0</v>
+        <v>0.175</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>-0.0278</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>8187300</v>
+        <v>8703300</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.25</v>
+        <v>0.13</v>
       </c>
       <c r="H21" t="n">
-        <v>44.39</v>
+        <v>59.26</v>
       </c>
       <c r="I21" s="16" t="inlineStr">
         <is>
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.157</v>
+        <v>0.164</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.147</v>
+        <v>0.129</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1458,28 +1458,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.395</v>
+        <v>0.145</v>
       </c>
       <c r="E22" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>7715800</v>
+        <v>8670300</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.68</v>
+        <v>0.26</v>
       </c>
       <c r="H22" t="n">
-        <v>38.38</v>
+        <v>44.39</v>
       </c>
       <c r="I22" s="16" t="inlineStr">
         <is>
@@ -1487,10 +1487,10 @@
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.404</v>
+        <v>0.157</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.411</v>
+        <v>0.147</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1503,39 +1503,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="E23" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>7577000</v>
+        <v>7805100</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.49</v>
+        <v>0.55</v>
       </c>
       <c r="H23" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="I23" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.14</v>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.775</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.775</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1548,39 +1548,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="E24" s="17" t="n">
-        <v>-0.0421</v>
+        <v>0.395</v>
+      </c>
+      <c r="E24" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>7137400</v>
+        <v>7780900</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.75</v>
+        <v>0.68</v>
       </c>
       <c r="H24" t="n">
-        <v>52.03</v>
-      </c>
-      <c r="I24" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.38</v>
+      </c>
+      <c r="I24" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.454</v>
+        <v>0.404</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.423</v>
+        <v>0.411</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1593,39 +1593,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>7803</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>HEXCARE</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>0.0833</v>
+        <v>0.455</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>-0.0421</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>6846000</v>
+        <v>7657700</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>3.93</v>
+        <v>0.8</v>
       </c>
       <c r="H25" t="n">
-        <v>57.12</v>
-      </c>
-      <c r="I25" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.03</v>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.061</v>
+        <v>0.454</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.061</v>
+        <v>0.423</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1647,19 +1647,19 @@
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>0.0286</v>
+        <v>0.175</v>
+      </c>
+      <c r="E26" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>6821500</v>
+        <v>7394100</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>5.58</v>
+        <v>6.05</v>
       </c>
       <c r="H26" t="n">
-        <v>69.34999999999999</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I26" s="13" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.162</v>
+        <v>0.161</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>0.153</v>
@@ -1698,10 +1698,10 @@
         <v>-0.0179</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>6245400</v>
+        <v>6992800</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="H27" t="n">
         <v>63.55</v>
@@ -1728,39 +1728,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0131</t>
+          <t>7803</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DFX</t>
+          <t>HEXCARE</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E28" s="17" t="n">
-        <v>-0.0323</v>
+        <v>0.065</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>0.0833</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>6061300</v>
+        <v>6856000</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.87</v>
+        <v>3.94</v>
       </c>
       <c r="H28" t="n">
-        <v>78.90000000000001</v>
-      </c>
-      <c r="I28" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.12</v>
+      </c>
+      <c r="I28" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.111</v>
+        <v>0.061</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.092</v>
+        <v>0.061</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1773,28 +1773,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>9.9</v>
+        <v>0.305</v>
       </c>
       <c r="E29" s="17" t="n">
-        <v>-0.006999999999999999</v>
+        <v>-0.0161</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>5707300</v>
+        <v>6616700</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.48</v>
+        <v>0.35</v>
       </c>
       <c r="H29" t="n">
-        <v>34.44</v>
+        <v>52.4</v>
       </c>
       <c r="I29" s="16" t="inlineStr">
         <is>
@@ -1802,10 +1802,10 @@
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>10.072</v>
+        <v>0.304</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>10.234</v>
+        <v>0.294</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1818,39 +1818,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E30" s="15" t="n">
-        <v>0</v>
+        <v>9.9</v>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>-0.006999999999999999</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>5633900</v>
+        <v>6268500</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.91</v>
+        <v>0.53</v>
       </c>
       <c r="H30" t="n">
-        <v>71.65000000000001</v>
-      </c>
-      <c r="I30" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.44</v>
+      </c>
+      <c r="I30" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.288</v>
+        <v>10.072</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.273</v>
+        <v>10.234</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1863,39 +1863,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>0.0185</v>
+        <v>0.28</v>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>4913200</v>
+        <v>6164900</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="H31" t="n">
-        <v>73.77</v>
-      </c>
-      <c r="I31" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.85</v>
+      </c>
+      <c r="I31" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.73</v>
+        <v>0.292</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.653</v>
+        <v>0.309</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1908,28 +1908,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E32" s="15" t="n">
-        <v>0</v>
+        <v>1.85</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>0.0165</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>4859700</v>
+        <v>6144300</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="H32" t="n">
-        <v>30.36</v>
+        <v>61.66</v>
       </c>
       <c r="I32" s="16" t="inlineStr">
         <is>
@@ -1937,10 +1937,10 @@
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.168</v>
+        <v>1.774</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.204</v>
+        <v>1.616</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1953,28 +1953,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0131</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>DFX</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E33" s="10" t="n">
-        <v>0.0164</v>
+        <v>0.15</v>
+      </c>
+      <c r="E33" s="17" t="n">
+        <v>-0.0323</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>4676300</v>
+        <v>6087200</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.44</v>
+        <v>0.87</v>
       </c>
       <c r="H33" t="n">
-        <v>55.75</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I33" s="13" t="inlineStr">
         <is>
@@ -1982,10 +1982,10 @@
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.609</v>
+        <v>0.111</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.61</v>
+        <v>0.092</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1998,39 +1998,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E34" s="15" t="n">
-        <v>0</v>
+        <v>0.485</v>
+      </c>
+      <c r="E34" s="17" t="n">
+        <v>-0.0202</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>4632700</v>
+        <v>5741500</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.33</v>
+        <v>0.15</v>
       </c>
       <c r="H34" t="n">
-        <v>53.14</v>
-      </c>
-      <c r="I34" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.56</v>
+      </c>
+      <c r="I34" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.775</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.775</v>
+        <v>0.768</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2043,39 +2043,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.305</v>
+      </c>
+      <c r="E35" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>4585100</v>
+        <v>5633900</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.2</v>
+        <v>0.91</v>
       </c>
       <c r="H35" t="n">
-        <v>60.12</v>
-      </c>
-      <c r="I35" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.65000000000001</v>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>1.772</v>
+        <v>0.288</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>1.615</v>
+        <v>0.273</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2088,39 +2088,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0209</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AIMFLEX</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E36" s="15" t="n">
-        <v>0</v>
+        <v>0.83</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>0.0247</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>4469100</v>
+        <v>5555900</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="H36" t="n">
-        <v>41.61</v>
-      </c>
-      <c r="I36" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.26000000000001</v>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.116</v>
+        <v>0.731</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.123</v>
+        <v>0.653</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2133,28 +2133,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0209</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>AIMFLEX</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E37" s="17" t="n">
-        <v>-0.0161</v>
+        <v>0.11</v>
+      </c>
+      <c r="E37" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>4332700</v>
+        <v>5482900</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.23</v>
+        <v>0.85</v>
       </c>
       <c r="H37" t="n">
-        <v>52.4</v>
+        <v>41.61</v>
       </c>
       <c r="I37" s="16" t="inlineStr">
         <is>
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.304</v>
+        <v>0.116</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.294</v>
+        <v>0.123</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2178,39 +2178,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E38" s="10" t="n">
-        <v>0.0169</v>
+        <v>0.15</v>
+      </c>
+      <c r="E38" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>4321700</v>
+        <v>5143700</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.43</v>
+        <v>0.28</v>
       </c>
       <c r="H38" t="n">
-        <v>59.64</v>
-      </c>
-      <c r="I38" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.36</v>
+      </c>
+      <c r="I38" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.276</v>
+        <v>0.168</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.305</v>
+        <v>0.204</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2223,28 +2223,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0328</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>3REN</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>0.0513</v>
+        <v>0.295</v>
+      </c>
+      <c r="E39" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>4264100</v>
+        <v>5110800</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>2.61</v>
+        <v>0.35</v>
       </c>
       <c r="H39" t="n">
-        <v>61.55</v>
+        <v>52.96</v>
       </c>
       <c r="I39" s="13" t="inlineStr">
         <is>
@@ -2252,10 +2252,10 @@
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.385</v>
+        <v>0.29</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.39</v>
+        <v>0.279</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2268,39 +2268,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="E40" s="17" t="n">
-        <v>-0.0202</v>
+        <v>0.3</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>0.0169</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>4251900</v>
+        <v>5031500</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.11</v>
+        <v>0.5</v>
       </c>
       <c r="H40" t="n">
-        <v>27.56</v>
-      </c>
-      <c r="I40" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.64</v>
+      </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.276</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.768</v>
+        <v>0.305</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2313,28 +2313,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E41" s="17" t="n">
-        <v>-0.0137</v>
+        <v>0.405</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>0.0385</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>4191900</v>
+        <v>4977700</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.54</v>
+        <v>3.04</v>
       </c>
       <c r="H41" t="n">
-        <v>62.63</v>
+        <v>59.74</v>
       </c>
       <c r="I41" s="13" t="inlineStr">
         <is>
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.343</v>
+        <v>0.385</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.323</v>
+        <v>0.39</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2358,39 +2358,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E42" s="10" t="n">
-        <v>0.0141</v>
+        <v>2.16</v>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>-0.0046</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>4145000</v>
+        <v>4767300</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.53</v>
+        <v>0.33</v>
       </c>
       <c r="H42" t="n">
-        <v>57.69</v>
-      </c>
-      <c r="I42" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.1</v>
+      </c>
+      <c r="I42" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.6889999999999999</v>
+        <v>2.247</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.676</v>
+        <v>2.222</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2403,39 +2403,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0395</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>OGX</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="E43" s="17" t="n">
-        <v>-0.0175</v>
+        <v>0.47</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>0.0444</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>3974500</v>
+        <v>4691400</v>
       </c>
       <c r="G43" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H43" t="n">
+        <v>60.55</v>
+      </c>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J43" s="9" t="n">
         <v>0.44</v>
       </c>
-      <c r="H43" t="n">
-        <v>22.14</v>
-      </c>
-      <c r="I43" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J43" s="9" t="n">
-        <v>7.703</v>
-      </c>
       <c r="K43" s="9" t="n">
-        <v>8.145</v>
+        <v>0.45</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2448,39 +2448,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="E44" s="17" t="n">
-        <v>-0.0107</v>
+        <v>0.62</v>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>0.0164</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>3636600</v>
+        <v>4677300</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.22</v>
+        <v>0.44</v>
       </c>
       <c r="H44" t="n">
-        <v>29.94</v>
-      </c>
-      <c r="I44" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.75</v>
+      </c>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>4.759</v>
+        <v>0.609</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>4.906</v>
+        <v>0.61</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2493,39 +2493,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E45" s="15" t="n">
-        <v>0</v>
+        <v>4.62</v>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>-0.0107</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>3597300</v>
+        <v>4633600</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="H45" t="n">
-        <v>72.51000000000001</v>
-      </c>
-      <c r="I45" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.94</v>
+      </c>
+      <c r="I45" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.387</v>
+        <v>4.759</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.375</v>
+        <v>4.906</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2538,28 +2538,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.805</v>
+        <v>0.415</v>
       </c>
       <c r="E46" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>3564000</v>
+        <v>4589800</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.58</v>
+        <v>0.39</v>
       </c>
       <c r="H46" t="n">
-        <v>70.22</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.781</v>
+        <v>0.387</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.762</v>
+        <v>0.375</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2583,28 +2583,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>2.15</v>
+        <v>7.3</v>
       </c>
       <c r="E47" s="17" t="n">
-        <v>-0.0092</v>
+        <v>-0.0175</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>3538700</v>
+        <v>4579900</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="H47" t="n">
-        <v>41.39</v>
+        <v>22.14</v>
       </c>
       <c r="I47" s="16" t="inlineStr">
         <is>
@@ -2612,10 +2612,10 @@
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>2.246</v>
+        <v>7.703</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>2.222</v>
+        <v>8.145</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2628,39 +2628,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E48" s="15" t="n">
-        <v>0</v>
+        <v>0.725</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>0.0211</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3481400</v>
+        <v>4523800</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.14</v>
+        <v>0.58</v>
       </c>
       <c r="H48" t="n">
-        <v>54.23</v>
-      </c>
-      <c r="I48" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.56</v>
+      </c>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.197</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.183</v>
+        <v>0.676</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2673,39 +2673,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="E49" s="15" t="n">
-        <v>0</v>
+        <v>2.71</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>0.015</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>3402300</v>
+        <v>4500900</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="H49" t="n">
-        <v>47.68</v>
-      </c>
-      <c r="I49" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.27</v>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>2.097</v>
+        <v>2.59</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>2.078</v>
+        <v>2.487</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2718,39 +2718,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="E50" s="10" t="n">
-        <v>0.0347</v>
+        <v>0.805</v>
+      </c>
+      <c r="E50" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>3352400</v>
+        <v>4389800</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.28</v>
+        <v>0.72</v>
       </c>
       <c r="H50" t="n">
-        <v>54.19</v>
-      </c>
-      <c r="I50" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.22</v>
+      </c>
+      <c r="I50" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>3.579</v>
+        <v>0.781</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>2.668</v>
+        <v>0.762</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2763,39 +2763,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>1.23</v>
+        <v>4.99</v>
       </c>
       <c r="E51" s="17" t="n">
-        <v>-0.016</v>
+        <v>-0.002</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>3256000</v>
+        <v>4197900</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.32</v>
+        <v>0.16</v>
       </c>
       <c r="H51" t="n">
-        <v>31.06</v>
-      </c>
-      <c r="I51" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.39</v>
+      </c>
+      <c r="I51" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>1.294</v>
+        <v>4.896</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>1.396</v>
+        <v>4.627</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2808,39 +2808,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E52" s="15" t="n">
-        <v>0</v>
+        <v>0.36</v>
+      </c>
+      <c r="E52" s="17" t="n">
+        <v>-0.0137</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>3232400</v>
+        <v>4191900</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.47</v>
+        <v>0.54</v>
       </c>
       <c r="H52" t="n">
-        <v>33.85</v>
-      </c>
-      <c r="I52" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.63</v>
+      </c>
+      <c r="I52" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.292</v>
+        <v>0.343</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.309</v>
+        <v>0.323</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2853,39 +2853,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.625</v>
+        <v>3.52</v>
       </c>
       <c r="E53" s="10" t="n">
-        <v>0.0331</v>
+        <v>0.0173</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>3213300</v>
+        <v>3987100</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>1.03</v>
+        <v>0.33</v>
       </c>
       <c r="H53" t="n">
-        <v>62.24</v>
-      </c>
-      <c r="I53" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.9</v>
+      </c>
+      <c r="I53" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.585</v>
+        <v>3.573</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.579</v>
+        <v>2.667</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2898,28 +2898,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>6.34</v>
-      </c>
-      <c r="E54" s="10" t="n">
-        <v>0.0567</v>
+        <v>0.865</v>
+      </c>
+      <c r="E54" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>3203300</v>
+        <v>3918400</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.83</v>
+        <v>0.21</v>
       </c>
       <c r="H54" t="n">
-        <v>63.5</v>
+        <v>46.41</v>
       </c>
       <c r="I54" s="13" t="inlineStr">
         <is>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>5.703</v>
+        <v>0.868</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>5.762</v>
+        <v>0.869</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2943,28 +2943,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0395</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>OGX</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.46</v>
+        <v>6.4</v>
       </c>
       <c r="E55" s="10" t="n">
-        <v>0.0222</v>
+        <v>0.0667</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>3165900</v>
+        <v>3783300</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>1.35</v>
+        <v>0.98</v>
       </c>
       <c r="H55" t="n">
-        <v>57.68</v>
+        <v>64.34</v>
       </c>
       <c r="I55" s="13" t="inlineStr">
         <is>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.439</v>
+        <v>5.709</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.45</v>
+        <v>5.764</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2988,39 +2988,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.3</v>
+        <v>2.09</v>
       </c>
       <c r="E56" s="10" t="n">
-        <v>0.0169</v>
+        <v>0.0048</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>3148000</v>
+        <v>3725200</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="H56" t="n">
-        <v>54.62</v>
-      </c>
-      <c r="I56" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.12</v>
+      </c>
+      <c r="I56" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.291</v>
+        <v>2.098</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.279</v>
+        <v>2.078</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3033,39 +3033,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="E57" s="10" t="n">
-        <v>0.025</v>
+        <v>1.23</v>
+      </c>
+      <c r="E57" s="17" t="n">
+        <v>-0.016</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>3113500</v>
+        <v>3664600</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.58</v>
+        <v>0.36</v>
       </c>
       <c r="H57" t="n">
-        <v>72.84</v>
-      </c>
-      <c r="I57" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.06</v>
+      </c>
+      <c r="I57" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.54</v>
+        <v>1.294</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.489</v>
+        <v>1.396</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3078,28 +3078,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E58" s="15" t="n">
-        <v>0</v>
+        <v>0.63</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>0.0413</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>3031500</v>
+        <v>3645200</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.16</v>
+        <v>1.16</v>
       </c>
       <c r="H58" t="n">
-        <v>46.41</v>
+        <v>63.2</v>
       </c>
       <c r="I58" s="13" t="inlineStr">
         <is>
@@ -3107,10 +3107,10 @@
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.868</v>
+        <v>0.585</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.869</v>
+        <v>0.579</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3123,39 +3123,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="E59" s="15" t="n">
-        <v>0</v>
+        <v>0.195</v>
+      </c>
+      <c r="E59" s="17" t="n">
+        <v>-0.025</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>2852200</v>
+        <v>3537000</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="H59" t="n">
-        <v>61.16</v>
-      </c>
-      <c r="I59" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.04</v>
+      </c>
+      <c r="I59" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>4.897</v>
+        <v>0.196</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>4.628</v>
+        <v>0.183</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3168,28 +3168,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="E60" s="15" t="n">
-        <v>0</v>
+        <v>1.17</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>0.0541</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>2768100</v>
+        <v>3535100</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.54</v>
+        <v>0.73</v>
       </c>
       <c r="H60" t="n">
-        <v>64.02</v>
+        <v>78.63</v>
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
@@ -3197,10 +3197,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.903</v>
+        <v>1.042</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.86</v>
+        <v>0.875</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3213,28 +3213,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.795</v>
+        <v>0.62</v>
       </c>
       <c r="E61" s="10" t="n">
-        <v>0.0127</v>
+        <v>0.0333</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>2666400</v>
+        <v>3403100</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.34</v>
+        <v>0.63</v>
       </c>
       <c r="H61" t="n">
-        <v>55.54</v>
+        <v>73.48</v>
       </c>
       <c r="I61" s="13" t="inlineStr">
         <is>
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.777</v>
+        <v>0.541</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.772</v>
+        <v>0.489</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3258,28 +3258,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5115</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ALAM</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.24</v>
+        <v>0.795</v>
       </c>
       <c r="E62" s="10" t="n">
-        <v>0.2</v>
+        <v>0.0127</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>2607400</v>
+        <v>3317700</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>4.7</v>
+        <v>0.42</v>
       </c>
       <c r="H62" t="n">
-        <v>56.39</v>
+        <v>55.54</v>
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
@@ -3287,10 +3287,10 @@
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.225</v>
+        <v>0.777</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.242</v>
+        <v>0.772</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3303,28 +3303,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>1.16</v>
+        <v>0.735</v>
       </c>
       <c r="E63" s="10" t="n">
-        <v>0.045</v>
+        <v>0.0208</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>2571500</v>
+        <v>3296800</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.53</v>
+        <v>0.37</v>
       </c>
       <c r="H63" t="n">
-        <v>77.91</v>
+        <v>68.04000000000001</v>
       </c>
       <c r="I63" s="13" t="inlineStr">
         <is>
@@ -3332,10 +3332,10 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>1.041</v>
+        <v>0.665</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>0.874</v>
+        <v>0.6</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3357,19 +3357,19 @@
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.51</v>
+        <v>0.515</v>
       </c>
       <c r="E64" s="10" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.0198</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>2451700</v>
+        <v>3213900</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.4</v>
+        <v>0.53</v>
       </c>
       <c r="H64" t="n">
-        <v>46.44</v>
+        <v>48.37</v>
       </c>
       <c r="I64" s="16" t="inlineStr">
         <is>
@@ -3393,39 +3393,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>5115</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>ALAM</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>6.24</v>
-      </c>
-      <c r="E65" s="17" t="n">
-        <v>-0.0355</v>
+        <v>0.235</v>
+      </c>
+      <c r="E65" s="10" t="n">
+        <v>0.175</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>2409200</v>
+        <v>3185300</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.61</v>
+        <v>5.74</v>
       </c>
       <c r="H65" t="n">
-        <v>26.62</v>
-      </c>
-      <c r="I65" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.85</v>
+      </c>
+      <c r="I65" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>6.561</v>
+        <v>0.225</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>6.863</v>
+        <v>0.242</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3438,39 +3438,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>2.81</v>
+        <v>0.73</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>0.0181</v>
+        <v>0.08960000000000001</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>2397800</v>
+        <v>3031400</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.18</v>
+        <v>2.24</v>
       </c>
       <c r="H66" t="n">
-        <v>54.41</v>
-      </c>
-      <c r="I66" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.73</v>
+      </c>
+      <c r="I66" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>2.788</v>
+        <v>0.649</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>2.689</v>
+        <v>0.613</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3483,28 +3483,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E67" s="10" t="n">
-        <v>0.019</v>
+        <v>6.22</v>
+      </c>
+      <c r="E67" s="17" t="n">
+        <v>-0.0386</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2273500</v>
+        <v>3026800</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.14</v>
+        <v>0.77</v>
       </c>
       <c r="H67" t="n">
-        <v>58.34</v>
+        <v>26.01</v>
       </c>
       <c r="I67" s="16" t="inlineStr">
         <is>
@@ -3512,10 +3512,10 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.511</v>
+        <v>6.56</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.432</v>
+        <v>6.863</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3528,39 +3528,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.23</v>
+        <v>0.925</v>
       </c>
       <c r="E68" s="17" t="n">
-        <v>-0.0213</v>
+        <v>-0.0054</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>2227300</v>
+        <v>3010400</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.08</v>
+        <v>0.58</v>
       </c>
       <c r="H68" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="I68" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.73</v>
+      </c>
+      <c r="I68" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.255</v>
+        <v>0.903</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.308</v>
+        <v>0.86</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3582,19 +3582,19 @@
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E69" s="15" t="n">
-        <v>0</v>
+        <v>0.245</v>
+      </c>
+      <c r="E69" s="17" t="n">
+        <v>-0.0392</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>2199600</v>
+        <v>2905600</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>1.35</v>
+        <v>1.79</v>
       </c>
       <c r="H69" t="n">
-        <v>71.55</v>
+        <v>63.48</v>
       </c>
       <c r="I69" s="13" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>0.229</v>
+        <v>0.228</v>
       </c>
       <c r="K69" s="9" t="n">
         <v>0.199</v>
@@ -3618,39 +3618,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E70" s="10" t="n">
-        <v>0.0597</v>
+        <v>0.37</v>
+      </c>
+      <c r="E70" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>2141400</v>
+        <v>2763700</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>1.58</v>
+        <v>0.41</v>
       </c>
       <c r="H70" t="n">
-        <v>70.81999999999999</v>
-      </c>
-      <c r="I70" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.59</v>
+      </c>
+      <c r="I70" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.647</v>
+        <v>0.367</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.613</v>
+        <v>0.368</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3663,39 +3663,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.79</v>
+        <v>0.53</v>
       </c>
       <c r="E71" s="10" t="n">
-        <v>0.0064</v>
+        <v>0.0095</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>2122600</v>
+        <v>2660800</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>1.29</v>
+        <v>0.16</v>
       </c>
       <c r="H71" t="n">
-        <v>69.79000000000001</v>
-      </c>
-      <c r="I71" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.54</v>
+      </c>
+      <c r="I71" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.699</v>
+        <v>0.51</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.432</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3708,39 +3708,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="E72" s="17" t="n">
-        <v>-0.022</v>
+        <v>2.79</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>0.0109</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>2105600</v>
+        <v>2468400</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.33</v>
+        <v>0.18</v>
       </c>
       <c r="H72" t="n">
-        <v>59.26</v>
-      </c>
-      <c r="I72" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.64</v>
+      </c>
+      <c r="I72" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>0.419</v>
+        <v>2.786</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0.41</v>
+        <v>2.689</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3753,28 +3753,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="E73" s="10" t="n">
-        <v>0.0515</v>
+        <v>0.45</v>
+      </c>
+      <c r="E73" s="17" t="n">
+        <v>-0.011</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>2103100</v>
+        <v>2438100</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.68</v>
+        <v>0.38</v>
       </c>
       <c r="H73" t="n">
-        <v>80.78</v>
+        <v>60.94</v>
       </c>
       <c r="I73" s="13" t="inlineStr">
         <is>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>1.208</v>
+        <v>0.42</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.985</v>
+        <v>0.41</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3798,28 +3798,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0249</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>LGMS</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E74" s="17" t="n">
-        <v>-0.0263</v>
+        <v>2.96</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>0.0172</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>2101000</v>
+        <v>2409600</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>3.12</v>
+        <v>0.24</v>
       </c>
       <c r="H74" t="n">
-        <v>67.48999999999999</v>
+        <v>63.53</v>
       </c>
       <c r="I74" s="13" t="inlineStr">
         <is>
@@ -3827,10 +3827,10 @@
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>0.513</v>
+        <v>2.77</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>0.501</v>
+        <v>2.582</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3843,28 +3843,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E75" s="15" t="n">
-        <v>0</v>
+        <v>2.82</v>
+      </c>
+      <c r="E75" s="10" t="n">
+        <v>0.0108</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1980300</v>
+        <v>2384100</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.22</v>
+        <v>0.44</v>
       </c>
       <c r="H75" t="n">
-        <v>66.04000000000001</v>
+        <v>71.17</v>
       </c>
       <c r="I75" s="13" t="inlineStr">
         <is>
@@ -3872,10 +3872,10 @@
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>0.663</v>
+        <v>2.615</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>0.599</v>
+        <v>2.571</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3888,28 +3888,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="E76" s="10" t="n">
-        <v>0.0072</v>
+        <v>0.785</v>
+      </c>
+      <c r="E76" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1973500</v>
+        <v>2334300</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.36</v>
+        <v>1.42</v>
       </c>
       <c r="H76" t="n">
-        <v>70.64</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="I76" s="13" t="inlineStr">
         <is>
@@ -3917,10 +3917,10 @@
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>2.614</v>
+        <v>0.699</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>2.571</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3933,39 +3933,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.805</v>
+        <v>0.225</v>
       </c>
       <c r="E77" s="17" t="n">
-        <v>-0.0242</v>
+        <v>-0.0426</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1955100</v>
+        <v>2279800</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.73</v>
+        <v>0.08</v>
       </c>
       <c r="H77" t="n">
-        <v>78.95999999999999</v>
-      </c>
-      <c r="I77" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.32</v>
+      </c>
+      <c r="I77" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.582</v>
+        <v>0.255</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.455</v>
+        <v>0.308</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3978,39 +3978,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>1</v>
+        <v>1.45</v>
       </c>
       <c r="E78" s="10" t="n">
-        <v>0.005</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>1902000</v>
+        <v>2274000</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.82</v>
+        <v>0.73</v>
       </c>
       <c r="H78" t="n">
-        <v>29.96</v>
-      </c>
-      <c r="I78" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>81.55</v>
+      </c>
+      <c r="I78" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>1.065</v>
+        <v>1.21</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>1.13</v>
+        <v>0.986</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4023,28 +4023,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>0249</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>LGMS</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E79" s="10" t="n">
-        <v>0.022</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E79" s="17" t="n">
+        <v>-0.0175</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>1872000</v>
+        <v>2214300</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.6</v>
+        <v>3.29</v>
       </c>
       <c r="H79" t="n">
-        <v>73.41</v>
+        <v>69.91</v>
       </c>
       <c r="I79" s="13" t="inlineStr">
         <is>
@@ -4052,10 +4052,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.406</v>
+        <v>0.513</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.362</v>
+        <v>0.501</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4068,28 +4068,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="E80" s="10" t="n">
-        <v>0.0116</v>
+        <v>0.805</v>
+      </c>
+      <c r="E80" s="17" t="n">
+        <v>-0.0242</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>1844700</v>
+        <v>2178100</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>1.21</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H80" t="n">
-        <v>62.19</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="I80" s="13" t="inlineStr">
         <is>
@@ -4097,10 +4097,10 @@
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>1.655</v>
+        <v>0.582</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>1.678</v>
+        <v>0.455</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4113,39 +4113,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="E81" s="15" t="n">
-        <v>0</v>
+        <v>0.53</v>
+      </c>
+      <c r="E81" s="17" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>1806700</v>
+        <v>2080300</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="H81" t="n">
-        <v>70.12</v>
-      </c>
-      <c r="I81" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.86</v>
+      </c>
+      <c r="I81" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>2.591</v>
+        <v>0.556</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>2.251</v>
+        <v>0.585</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4158,39 +4158,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>5209</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>GASMSIA</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="E82" s="17" t="n">
-        <v>-0.0037</v>
+        <v>5.18</v>
+      </c>
+      <c r="E82" s="10" t="n">
+        <v>0.0177</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>1732800</v>
+        <v>2077900</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.1</v>
+        <v>2.57</v>
       </c>
       <c r="H82" t="n">
-        <v>57.87</v>
-      </c>
-      <c r="I82" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.77</v>
+      </c>
+      <c r="I82" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>2.585</v>
+        <v>4.998</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>2.486</v>
+        <v>5.026</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4203,39 +4203,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E83" s="17" t="n">
-        <v>-0.0203</v>
+        <v>0.33</v>
+      </c>
+      <c r="E83" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>1721600</v>
+        <v>2074200</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H83" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="I83" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.33</v>
+      </c>
+      <c r="I83" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>0.764</v>
+        <v>0.323</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.824</v>
+        <v>0.339</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4248,39 +4248,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ALPHA</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>0.275</v>
+        <v>6.06</v>
       </c>
       <c r="E84" s="17" t="n">
-        <v>-0.0351</v>
+        <v>-0.0098</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>1721000</v>
+        <v>2060700</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.8</v>
+        <v>0.16</v>
       </c>
       <c r="H84" t="n">
-        <v>64.26000000000001</v>
-      </c>
-      <c r="I84" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.03</v>
+      </c>
+      <c r="I84" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>0.255</v>
+        <v>6.197</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>0.257</v>
+        <v>6.419</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4293,39 +4293,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.635</v>
+        <v>0.99</v>
       </c>
       <c r="E85" s="17" t="n">
-        <v>-0.0231</v>
+        <v>-0.005</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>1710900</v>
+        <v>2044500</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="H85" t="n">
-        <v>55.38</v>
-      </c>
-      <c r="I85" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.67</v>
+      </c>
+      <c r="I85" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.616</v>
+        <v>1.064</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.609</v>
+        <v>1.13</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4338,39 +4338,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E86" s="15" t="n">
-        <v>0</v>
+        <v>5.56</v>
+      </c>
+      <c r="E86" s="17" t="n">
+        <v>-0.0036</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>1705600</v>
+        <v>1930800</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.33</v>
+        <v>0.13</v>
       </c>
       <c r="H86" t="n">
-        <v>53.33</v>
-      </c>
-      <c r="I86" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.54</v>
+      </c>
+      <c r="I86" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>0.323</v>
+        <v>5.65</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0.339</v>
+        <v>5.304</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4383,39 +4383,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E87" s="15" t="n">
-        <v>0</v>
+        <v>3.1</v>
+      </c>
+      <c r="E87" s="17" t="n">
+        <v>-0.0064</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1681900</v>
+        <v>1923200</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>1.79</v>
+        <v>0.48</v>
       </c>
       <c r="H87" t="n">
-        <v>45.51</v>
-      </c>
-      <c r="I87" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>72.92</v>
+      </c>
+      <c r="I87" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>0.261</v>
+        <v>2.622</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>0.264</v>
+        <v>1.985</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4428,28 +4428,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="E88" s="10" t="n">
-        <v>0.0032</v>
+        <v>2.74</v>
+      </c>
+      <c r="E88" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>1667500</v>
+        <v>1906100</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.42</v>
+        <v>0.58</v>
       </c>
       <c r="H88" t="n">
-        <v>74.09999999999999</v>
+        <v>70.12</v>
       </c>
       <c r="I88" s="13" t="inlineStr">
         <is>
@@ -4457,10 +4457,10 @@
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>2.625</v>
+        <v>2.591</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>1.986</v>
+        <v>2.251</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4473,28 +4473,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E89" s="15" t="n">
-        <v>0</v>
+        <v>0.47</v>
+      </c>
+      <c r="E89" s="10" t="n">
+        <v>0.033</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1580300</v>
+        <v>1892700</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.14</v>
+        <v>0.61</v>
       </c>
       <c r="H89" t="n">
-        <v>74.43000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="I89" s="13" t="inlineStr">
         <is>
@@ -4502,10 +4502,10 @@
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>1.064</v>
+        <v>0.407</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0.904</v>
+        <v>0.362</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4518,39 +4518,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>VSTECS</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E90" s="17" t="n">
-        <v>-0.0182</v>
+        <v>1.77</v>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>0.0231</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>1568200</v>
+        <v>1883600</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.39</v>
+        <v>1.23</v>
       </c>
       <c r="H90" t="n">
-        <v>66.16</v>
-      </c>
-      <c r="I90" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.95</v>
+      </c>
+      <c r="I90" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.246</v>
+        <v>1.657</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.217</v>
+        <v>1.679</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4563,39 +4563,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0291</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>CHB</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="E91" s="10" t="n">
-        <v>0.052</v>
+        <v>4.64</v>
+      </c>
+      <c r="E91" s="17" t="n">
+        <v>-0.0064</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1563600</v>
+        <v>1819700</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>1</v>
+        <v>0.19</v>
       </c>
       <c r="H91" t="n">
-        <v>80.25</v>
-      </c>
-      <c r="I91" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.1</v>
+      </c>
+      <c r="I91" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>2.388</v>
+        <v>4.702</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>2.122</v>
+        <v>4.624</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4608,28 +4608,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>6.05</v>
+        <v>0.73</v>
       </c>
       <c r="E92" s="17" t="n">
-        <v>-0.0114</v>
+        <v>-0.0135</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1556600</v>
+        <v>1794100</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.12</v>
+        <v>0.32</v>
       </c>
       <c r="H92" t="n">
-        <v>38.58</v>
+        <v>34.7</v>
       </c>
       <c r="I92" s="16" t="inlineStr">
         <is>
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>6.196</v>
+        <v>0.764</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>6.419</v>
+        <v>0.824</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4653,39 +4653,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0291</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>CHB</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>5.56</v>
-      </c>
-      <c r="E93" s="17" t="n">
-        <v>-0.0036</v>
+        <v>2.85</v>
+      </c>
+      <c r="E93" s="10" t="n">
+        <v>0.0595</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1498200</v>
+        <v>1783800</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.1</v>
+        <v>1.14</v>
       </c>
       <c r="H93" t="n">
-        <v>48.54</v>
-      </c>
-      <c r="I93" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>80.68000000000001</v>
+      </c>
+      <c r="I93" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>5.65</v>
+        <v>2.39</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>5.304</v>
+        <v>2.122</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4698,28 +4698,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0399</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AMS</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="E94" s="10" t="n">
-        <v>0.0104</v>
+        <v>1.15</v>
+      </c>
+      <c r="E94" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1476900</v>
+        <v>1739100</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.74</v>
+        <v>0.15</v>
       </c>
       <c r="H94" t="n">
-        <v>60.97</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="I94" s="13" t="inlineStr">
         <is>
@@ -4727,10 +4727,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>0.458</v>
+        <v>1.064</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.461</v>
+        <v>0.904</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4743,28 +4743,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>0.52</v>
+        <v>0.635</v>
       </c>
       <c r="E95" s="17" t="n">
-        <v>-0.0095</v>
+        <v>-0.0231</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1433800</v>
+        <v>1729900</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.37</v>
+        <v>0.45</v>
       </c>
       <c r="H95" t="n">
-        <v>69.04000000000001</v>
+        <v>55.38</v>
       </c>
       <c r="I95" s="13" t="inlineStr">
         <is>
@@ -4772,10 +4772,10 @@
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>0.462</v>
+        <v>0.616</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>0.447</v>
+        <v>0.609</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4788,28 +4788,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>5127</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ARREIT</t>
+          <t>ALPHA</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E96" s="10" t="n">
-        <v>0.0263</v>
+        <v>0.275</v>
+      </c>
+      <c r="E96" s="17" t="n">
+        <v>-0.0351</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1408200</v>
+        <v>1721000</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>7.69</v>
+        <v>0.8</v>
       </c>
       <c r="H96" t="n">
-        <v>67.43000000000001</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="I96" s="13" t="inlineStr">
         <is>
@@ -4817,10 +4817,10 @@
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.369</v>
+        <v>0.255</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.372</v>
+        <v>0.257</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4833,28 +4833,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="E97" s="15" t="n">
-        <v>0</v>
+        <v>0.265</v>
+      </c>
+      <c r="E97" s="10" t="n">
+        <v>0.0192</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1341000</v>
+        <v>1702600</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.36</v>
+        <v>1.81</v>
       </c>
       <c r="H97" t="n">
-        <v>38.26</v>
+        <v>57.12</v>
       </c>
       <c r="I97" s="16" t="inlineStr">
         <is>
@@ -4862,10 +4862,10 @@
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>0.368</v>
+        <v>0.261</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0.386</v>
+        <v>0.264</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4878,39 +4878,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>CLOUDPT</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="E98" s="17" t="n">
-        <v>-0.01</v>
+        <v>0.51</v>
+      </c>
+      <c r="E98" s="10" t="n">
+        <v>0.02</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1329000</v>
+        <v>1692400</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.19</v>
+        <v>1.15</v>
       </c>
       <c r="H98" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="I98" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.29</v>
+      </c>
+      <c r="I98" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>0.532</v>
+        <v>0.485</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>0.575</v>
+        <v>0.476</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4923,39 +4923,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E99" s="17" t="n">
-        <v>-0.0132</v>
+        <v>1.37</v>
+      </c>
+      <c r="E99" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1325100</v>
+        <v>1687500</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.15</v>
+        <v>0.89</v>
       </c>
       <c r="H99" t="n">
-        <v>68.06</v>
-      </c>
-      <c r="I99" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.6</v>
+      </c>
+      <c r="I99" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.349</v>
+        <v>1.369</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.318</v>
+        <v>1.334</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
@@ -4983,13 +4983,13 @@
         <v>0</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1311100</v>
+        <v>1649800</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.09</v>
+        <v>0.41</v>
       </c>
       <c r="H100" t="n">
-        <v>18.18</v>
+        <v>69.5</v>
       </c>
       <c r="I100" s="16" t="inlineStr">
         <is>
@@ -4997,9 +4997,11 @@
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="K100" s="9" t="n"/>
+        <v>0.246</v>
+      </c>
+      <c r="K100" s="9" t="n">
+        <v>0.217</v>
+      </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
     </row>
@@ -5011,39 +5013,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0337</t>
+          <t>0399</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E101" s="15" t="n">
-        <v>0</v>
+        <v>0.485</v>
+      </c>
+      <c r="E101" s="10" t="n">
+        <v>0.0104</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1297400</v>
+        <v>1596100</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="H101" t="n">
-        <v>52.31</v>
-      </c>
-      <c r="I101" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.97</v>
+      </c>
+      <c r="I101" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>0.236</v>
+        <v>0.458</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>0.243</v>
+        <v>0.461</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5056,39 +5058,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="E102" s="10" t="n">
-        <v>0.004</v>
+        <v>0.52</v>
+      </c>
+      <c r="E102" s="17" t="n">
+        <v>-0.0095</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1195700</v>
+        <v>1593500</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.08</v>
+        <v>0.41</v>
       </c>
       <c r="H102" t="n">
-        <v>57.34</v>
-      </c>
-      <c r="I102" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.04000000000001</v>
+      </c>
+      <c r="I102" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>2.459</v>
+        <v>0.462</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>2.342</v>
+        <v>0.447</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5101,28 +5103,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="E103" s="17" t="n">
-        <v>-0.0329</v>
+        <v>3.42</v>
+      </c>
+      <c r="E103" s="10" t="n">
+        <v>0.04269999999999999</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1192400</v>
+        <v>1581500</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.36</v>
+        <v>0.54</v>
       </c>
       <c r="H103" t="n">
-        <v>63.31</v>
+        <v>74.48999999999999</v>
       </c>
       <c r="I103" s="13" t="inlineStr">
         <is>
@@ -5130,10 +5132,10 @@
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>5.379</v>
+        <v>2.954</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>5.327</v>
+        <v>2.78</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5146,28 +5148,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>1.45</v>
+        <v>0.49</v>
       </c>
       <c r="E104" s="17" t="n">
-        <v>-0.0068</v>
+        <v>-0.02</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1168300</v>
+        <v>1497700</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="H104" t="n">
-        <v>44.42</v>
+        <v>26.23</v>
       </c>
       <c r="I104" s="16" t="inlineStr">
         <is>
@@ -5175,10 +5177,10 @@
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>1.465</v>
+        <v>0.532</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>1.469</v>
+        <v>0.575</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5191,28 +5193,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0172</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>OCK</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E105" s="17" t="n">
-        <v>-0.0211</v>
+        <v>0.33</v>
+      </c>
+      <c r="E105" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1148100</v>
+        <v>1486800</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.35</v>
+        <v>0.24</v>
       </c>
       <c r="H105" t="n">
-        <v>56.06</v>
+        <v>31.86</v>
       </c>
       <c r="I105" s="16" t="inlineStr">
         <is>
@@ -5220,10 +5222,10 @@
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>0.46</v>
+        <v>0.342</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0.419</v>
+        <v>0.346</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5236,36 +5238,40 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>5127</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>ARREIT</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E106" s="17" t="n">
-        <v>-0.0357</v>
+        <v>0.39</v>
+      </c>
+      <c r="E106" s="10" t="n">
+        <v>0.0263</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1138700</v>
+        <v>1441200</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.09</v>
+        <v>7.87</v>
       </c>
       <c r="H106" t="n">
-        <v>31.12</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="I106" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J106" s="9" t="n"/>
-      <c r="K106" s="9" t="n"/>
+      <c r="J106" s="9" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="K106" s="9" t="n">
+        <v>0.372</v>
+      </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
     </row>
@@ -5277,28 +5283,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E107" s="17" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.275</v>
+      </c>
+      <c r="E107" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1126200</v>
+        <v>1377300</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.18</v>
+        <v>0.09</v>
       </c>
       <c r="H107" t="n">
-        <v>46.42</v>
+        <v>18.18</v>
       </c>
       <c r="I107" s="16" t="inlineStr">
         <is>
@@ -5306,11 +5312,9 @@
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>1.149</v>
-      </c>
-      <c r="K107" s="9" t="n">
-        <v>1.164</v>
-      </c>
+        <v>0.293</v>
+      </c>
+      <c r="K107" s="9" t="n"/>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
     </row>
@@ -5322,39 +5326,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E108" s="17" t="n">
-        <v>-0.0192</v>
+        <v>0.355</v>
+      </c>
+      <c r="E108" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1119400</v>
+        <v>1346000</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="H108" t="n">
-        <v>50.56</v>
-      </c>
-      <c r="I108" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.26</v>
+      </c>
+      <c r="I108" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>0.766</v>
+        <v>0.368</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>0.746</v>
+        <v>0.386</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5367,39 +5371,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="E109" s="10" t="n">
-        <v>0.0146</v>
+        <v>0.375</v>
+      </c>
+      <c r="E109" s="17" t="n">
+        <v>-0.0132</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1087400</v>
+        <v>1335100</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.41</v>
+        <v>0.16</v>
       </c>
       <c r="H109" t="n">
-        <v>57.34</v>
-      </c>
-      <c r="I109" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.06</v>
+      </c>
+      <c r="I109" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>1.358</v>
+        <v>0.349</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>1.223</v>
+        <v>0.318</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5412,39 +5416,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>MFLOUR</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>0.78</v>
+        <v>0.605</v>
       </c>
       <c r="E110" s="17" t="n">
-        <v>-0.0064</v>
+        <v>-0.008199999999999999</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1063400</v>
+        <v>1330000</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.15</v>
+        <v>0.61</v>
       </c>
       <c r="H110" t="n">
-        <v>67.56999999999999</v>
-      </c>
-      <c r="I110" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.29</v>
+      </c>
+      <c r="I110" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>0.719</v>
+        <v>0.623</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>0.642</v>
+        <v>0.638</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5457,28 +5461,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E111" s="10" t="n">
-        <v>0.012</v>
+        <v>1.13</v>
+      </c>
+      <c r="E111" s="17" t="n">
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1041900</v>
+        <v>1327300</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.89</v>
+        <v>0.21</v>
       </c>
       <c r="H111" t="n">
-        <v>43.5</v>
+        <v>46.42</v>
       </c>
       <c r="I111" s="16" t="inlineStr">
         <is>
@@ -5486,10 +5490,10 @@
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>0.424</v>
+        <v>1.149</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>0.443</v>
+        <v>1.164</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5502,28 +5506,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="E112" s="10" t="n">
-        <v>0.0146</v>
+        <v>5.88</v>
+      </c>
+      <c r="E112" s="17" t="n">
+        <v>-0.0329</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>1008600</v>
+        <v>1318400</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.25</v>
+        <v>0.39</v>
       </c>
       <c r="H112" t="n">
-        <v>63.18</v>
+        <v>63.31</v>
       </c>
       <c r="I112" s="13" t="inlineStr">
         <is>
@@ -5531,10 +5535,10 @@
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>1.283</v>
+        <v>5.379</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>1.184</v>
+        <v>5.327</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5547,40 +5551,36 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="E113" s="10" t="n">
-        <v>0.0244</v>
+        <v>0.27</v>
+      </c>
+      <c r="E113" s="17" t="n">
+        <v>-0.0357</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>923800</v>
+        <v>1311200</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.32</v>
+        <v>0.1</v>
       </c>
       <c r="H113" t="n">
-        <v>73.09</v>
+        <v>31.12</v>
       </c>
       <c r="I113" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J113" s="9" t="n">
-        <v>2.948</v>
-      </c>
-      <c r="K113" s="9" t="n">
-        <v>2.779</v>
-      </c>
+      <c r="J113" s="9" t="n"/>
+      <c r="K113" s="9" t="n"/>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
     </row>
@@ -5592,28 +5592,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>E&amp;O</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>1.82</v>
+        <v>0.76</v>
       </c>
       <c r="E114" s="17" t="n">
-        <v>-0.0109</v>
+        <v>-0.013</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>878300</v>
+        <v>1304100</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.2</v>
+        <v>0.91</v>
       </c>
       <c r="H114" t="n">
-        <v>30.93</v>
+        <v>44.8</v>
       </c>
       <c r="I114" s="16" t="inlineStr">
         <is>
@@ -5621,10 +5621,10 @@
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>1.908</v>
+        <v>0.771</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>2.035</v>
+        <v>0.767</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5637,39 +5637,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="E115" s="17" t="n">
-        <v>-0.0391</v>
+        <v>0.24</v>
+      </c>
+      <c r="E115" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>878000</v>
+        <v>1297400</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.12</v>
+        <v>0.74</v>
       </c>
       <c r="H115" t="n">
-        <v>70.95</v>
-      </c>
-      <c r="I115" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.31</v>
+      </c>
+      <c r="I115" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>1.058</v>
+        <v>0.236</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.243</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5682,28 +5682,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E116" s="17" t="n">
-        <v>-0.009300000000000001</v>
+        <v>0.475</v>
+      </c>
+      <c r="E116" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>875500</v>
+        <v>1282200</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.24</v>
+        <v>0.39</v>
       </c>
       <c r="H116" t="n">
-        <v>33.64</v>
+        <v>61.26</v>
       </c>
       <c r="I116" s="16" t="inlineStr">
         <is>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>0.556</v>
+        <v>0.461</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>0.585</v>
+        <v>0.419</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5727,39 +5727,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="E117" s="17" t="n">
-        <v>-0.009599999999999999</v>
+        <v>1.39</v>
+      </c>
+      <c r="E117" s="10" t="n">
+        <v>0.0146</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>865800</v>
+        <v>1264900</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.2</v>
+        <v>0.47</v>
       </c>
       <c r="H117" t="n">
-        <v>58.59</v>
-      </c>
-      <c r="I117" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.34</v>
+      </c>
+      <c r="I117" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>2.983</v>
+        <v>1.358</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>2.804</v>
+        <v>1.223</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5772,39 +5772,39 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>4.33</v>
+        <v>1.83</v>
       </c>
       <c r="E118" s="17" t="n">
-        <v>-0.0092</v>
+        <v>-0.0054</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>849800</v>
+        <v>1264700</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.1</v>
+        <v>0.28</v>
       </c>
       <c r="H118" t="n">
-        <v>70.17</v>
-      </c>
-      <c r="I118" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.91</v>
+      </c>
+      <c r="I118" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>3.923</v>
+        <v>1.909</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>3.399</v>
+        <v>2.036</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5817,28 +5817,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>MFLOUR</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E119" s="17" t="n">
-        <v>-0.008199999999999999</v>
+        <v>2.48</v>
+      </c>
+      <c r="E119" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>836600</v>
+        <v>1259000</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.38</v>
+        <v>0.09</v>
       </c>
       <c r="H119" t="n">
-        <v>38.29</v>
+        <v>56.21</v>
       </c>
       <c r="I119" s="16" t="inlineStr">
         <is>
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>0.623</v>
+        <v>2.458</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>0.638</v>
+        <v>2.342</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5862,39 +5862,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>FFB</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>1.78</v>
+        <v>0.77</v>
       </c>
       <c r="E120" s="17" t="n">
-        <v>-0.0111</v>
+        <v>-0.0128</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>835000</v>
+        <v>1254100</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.3</v>
+        <v>0.41</v>
       </c>
       <c r="H120" t="n">
-        <v>23.22</v>
-      </c>
-      <c r="I120" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.63</v>
+      </c>
+      <c r="I120" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>1.903</v>
+        <v>0.767</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>2.032</v>
+        <v>0.746</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5907,39 +5907,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>2.94</v>
+        <v>1.76</v>
       </c>
       <c r="E121" s="10" t="n">
-        <v>0.0103</v>
+        <v>0.0115</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>824300</v>
+        <v>1222500</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.08</v>
+        <v>0.24</v>
       </c>
       <c r="H121" t="n">
-        <v>62.74</v>
-      </c>
-      <c r="I121" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.13</v>
+      </c>
+      <c r="I121" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>2.768</v>
+        <v>1.753</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>2.582</v>
+        <v>1.782</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5952,28 +5952,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>2.52</v>
+        <v>1.45</v>
       </c>
       <c r="E122" s="17" t="n">
-        <v>-0.0195</v>
+        <v>-0.0068</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>767400</v>
+        <v>1203300</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.12</v>
+        <v>0.24</v>
       </c>
       <c r="H122" t="n">
-        <v>34.84</v>
+        <v>44.42</v>
       </c>
       <c r="I122" s="16" t="inlineStr">
         <is>
@@ -5981,10 +5981,10 @@
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>2.634</v>
+        <v>1.465</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>2.799</v>
+        <v>1.469</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -6012,10 +6012,10 @@
         <v>0</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>735500</v>
+        <v>1198100</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.11</v>
+        <v>0.18</v>
       </c>
       <c r="H123" t="n">
         <v>37.31</v>
@@ -6042,39 +6042,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E124" s="17" t="n">
-        <v>-0.005699999999999999</v>
+        <v>1.42</v>
+      </c>
+      <c r="E124" s="10" t="n">
+        <v>0.0365</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>728000</v>
+        <v>1194400</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.24</v>
+        <v>0.29</v>
       </c>
       <c r="H124" t="n">
-        <v>53.32</v>
-      </c>
-      <c r="I124" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.15000000000001</v>
+      </c>
+      <c r="I124" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>0.864</v>
+        <v>1.286</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>0.858</v>
+        <v>1.185</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6087,39 +6087,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>UNISEM</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>4.44</v>
+        <v>0.64</v>
       </c>
       <c r="E125" s="10" t="n">
-        <v>0.0137</v>
+        <v>0.0159</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>726400</v>
+        <v>1190200</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.27</v>
+        <v>0.32</v>
       </c>
       <c r="H125" t="n">
-        <v>53.56</v>
-      </c>
-      <c r="I125" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>87.18000000000001</v>
+      </c>
+      <c r="I125" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>4.35</v>
+        <v>0.482</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>4.369</v>
+        <v>0.433</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6132,40 +6132,33 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0466</t>
+          <t>0475</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>SRKKAI</t>
+          <t>GBBOND</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E126" s="17" t="n">
-        <v>-0.0185</v>
+        <v>0.225</v>
+      </c>
+      <c r="E126" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>715200</v>
+        <v>1149600</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="H126" t="n">
-        <v>50.33</v>
-      </c>
-      <c r="I126" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J126" s="9" t="n">
-        <v>0.527</v>
-      </c>
-      <c r="K126" s="9" t="n">
-        <v>0.533</v>
-      </c>
+        <v>0.04</v>
+      </c>
+      <c r="I126" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J126" s="9" t="n"/>
+      <c r="K126" s="9" t="n"/>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
     </row>
@@ -6177,28 +6170,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E127" s="15" t="n">
-        <v>0</v>
+        <v>0.78</v>
+      </c>
+      <c r="E127" s="17" t="n">
+        <v>-0.0064</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>694100</v>
+        <v>1133700</v>
       </c>
       <c r="G127" s="12" t="n">
         <v>0.16</v>
       </c>
       <c r="H127" t="n">
-        <v>65.7</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="I127" s="13" t="inlineStr">
         <is>
@@ -6206,10 +6199,10 @@
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>1.148</v>
+        <v>0.719</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>1.057</v>
+        <v>0.642</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6222,39 +6215,39 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E128" s="15" t="n">
-        <v>0</v>
+        <v>4.31</v>
+      </c>
+      <c r="E128" s="17" t="n">
+        <v>-0.0137</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>693300</v>
+        <v>1128800</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.31</v>
+        <v>0.13</v>
       </c>
       <c r="H128" t="n">
-        <v>48.46</v>
-      </c>
-      <c r="I128" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.2</v>
+      </c>
+      <c r="I128" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>3.921</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>3.398</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6267,39 +6260,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>3</v>
+        <v>1.19</v>
       </c>
       <c r="E129" s="17" t="n">
-        <v>-0.0132</v>
+        <v>-0.0083</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>680100</v>
+        <v>1080200</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="H129" t="n">
-        <v>50.88</v>
-      </c>
-      <c r="I129" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.19</v>
+      </c>
+      <c r="I129" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>2.986</v>
+        <v>1.147</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>3.037</v>
+        <v>1.057</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6312,39 +6305,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E130" s="10" t="n">
-        <v>0.0215</v>
+        <v>0.865</v>
+      </c>
+      <c r="E130" s="17" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>679700</v>
+        <v>1078000</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="H130" t="n">
-        <v>56.93</v>
-      </c>
-      <c r="I130" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.32</v>
+      </c>
+      <c r="I130" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>0.922</v>
+        <v>0.864</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>0.842</v>
+        <v>0.858</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6357,28 +6350,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E131" s="10" t="n">
-        <v>0.0053</v>
+        <v>0.415</v>
+      </c>
+      <c r="E131" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>671100</v>
+        <v>1061800</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.39</v>
+        <v>0.9</v>
       </c>
       <c r="H131" t="n">
-        <v>34.76</v>
+        <v>39.02</v>
       </c>
       <c r="I131" s="16" t="inlineStr">
         <is>
@@ -6386,10 +6379,10 @@
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>0.971</v>
+        <v>0.424</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>0.997</v>
+        <v>0.443</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6402,39 +6395,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>7202</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>HEXRTL</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="E132" s="17" t="n">
-        <v>-0.0198</v>
+        <v>0.4</v>
+      </c>
+      <c r="E132" s="10" t="n">
+        <v>0.0959</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>670000</v>
+        <v>1002700</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.08</v>
+        <v>3.08</v>
       </c>
       <c r="H132" t="n">
-        <v>59.55</v>
-      </c>
-      <c r="I132" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.96</v>
+      </c>
+      <c r="I132" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>0.959</v>
+        <v>0.406</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.411</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6447,39 +6440,39 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>0.68</v>
+        <v>2.51</v>
       </c>
       <c r="E133" s="17" t="n">
-        <v>-0.0216</v>
+        <v>-0.0233</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>649300</v>
+        <v>997700</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.29</v>
+        <v>0.15</v>
       </c>
       <c r="H133" t="n">
-        <v>69.78</v>
-      </c>
-      <c r="I133" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.18</v>
+      </c>
+      <c r="I133" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>0.619</v>
+        <v>2.633</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>0.523</v>
+        <v>2.799</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6492,39 +6485,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>1.72</v>
+        <v>1.24</v>
       </c>
       <c r="E134" s="17" t="n">
-        <v>-0.0115</v>
+        <v>-0.0313</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>638100</v>
+        <v>986400</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="H134" t="n">
-        <v>44.38</v>
-      </c>
-      <c r="I134" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>72.16</v>
+      </c>
+      <c r="I134" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>1.749</v>
+        <v>1.059</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>1.782</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6537,39 +6530,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>12.98</v>
+        <v>4.31</v>
       </c>
       <c r="E135" s="10" t="n">
-        <v>0.0062</v>
+        <v>0.004699999999999999</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>632400</v>
+        <v>985500</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="H135" t="n">
-        <v>42.22</v>
-      </c>
-      <c r="I135" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.42</v>
+      </c>
+      <c r="I135" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>13.068</v>
+        <v>4.524</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>13.616</v>
+        <v>4.871</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6582,39 +6575,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E136" s="15" t="n">
-        <v>0</v>
+        <v>12.92</v>
+      </c>
+      <c r="E136" s="10" t="n">
+        <v>0.0016</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>619300</v>
+        <v>961900</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="H136" t="n">
-        <v>43.85</v>
-      </c>
-      <c r="I136" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>39.45</v>
+      </c>
+      <c r="I136" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>1.334</v>
+        <v>13.062</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>1.307</v>
+        <v>13.615</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6627,39 +6620,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>FFB</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>0.64</v>
+        <v>1.79</v>
       </c>
       <c r="E137" s="17" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.005600000000000001</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>616500</v>
+        <v>934800</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.17</v>
+        <v>0.33</v>
       </c>
       <c r="H137" t="n">
-        <v>55.69</v>
-      </c>
-      <c r="I137" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>24.01</v>
+      </c>
+      <c r="I137" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>0.63</v>
+        <v>1.904</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>0.598</v>
+        <v>2.032</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6672,28 +6665,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="E138" s="10" t="n">
-        <v>0.0141</v>
+        <v>3.12</v>
+      </c>
+      <c r="E138" s="17" t="n">
+        <v>-0.0032</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>610400</v>
+        <v>924700</v>
       </c>
       <c r="G138" s="12" t="n">
         <v>0.21</v>
       </c>
       <c r="H138" t="n">
-        <v>79.86</v>
+        <v>59.87</v>
       </c>
       <c r="I138" s="13" t="inlineStr">
         <is>
@@ -6701,10 +6694,10 @@
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>1.18</v>
+        <v>2.985</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>1.139</v>
+        <v>2.805</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6717,39 +6710,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>OSK</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>0.625</v>
+        <v>1.66</v>
       </c>
       <c r="E139" s="17" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0235</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>598000</v>
+        <v>922000</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.16</v>
+        <v>0.67</v>
       </c>
       <c r="H139" t="n">
-        <v>84.91</v>
-      </c>
-      <c r="I139" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>21.7</v>
+      </c>
+      <c r="I139" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>0.481</v>
+        <v>1.82</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>0.432</v>
+        <v>1.935</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6762,39 +6755,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="E140" s="10" t="n">
-        <v>0.015</v>
+        <v>3</v>
+      </c>
+      <c r="E140" s="17" t="n">
+        <v>-0.0132</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>592200</v>
+        <v>905000</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.19</v>
+        <v>0.3</v>
       </c>
       <c r="H140" t="n">
-        <v>64.09</v>
-      </c>
-      <c r="I140" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.88</v>
+      </c>
+      <c r="I140" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>3.857</v>
+        <v>2.986</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>3.542</v>
+        <v>3.037</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6807,28 +6800,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>OSK</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="E141" s="17" t="n">
-        <v>-0.0176</v>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E141" s="10" t="n">
+        <v>0.0053</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>586100</v>
+        <v>891900</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.43</v>
+        <v>0.52</v>
       </c>
       <c r="H141" t="n">
-        <v>22.33</v>
+        <v>34.76</v>
       </c>
       <c r="I141" s="16" t="inlineStr">
         <is>
@@ -6836,10 +6829,10 @@
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>1.821</v>
+        <v>0.971</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>1.935</v>
+        <v>0.997</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6852,39 +6845,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>0466</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>SRKKAI</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="E142" s="15" t="n">
-        <v>0</v>
+        <v>0.53</v>
+      </c>
+      <c r="E142" s="17" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>565200</v>
+        <v>883100</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>0.09</v>
+        <v>0.82</v>
       </c>
       <c r="H142" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="I142" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.33</v>
+      </c>
+      <c r="I142" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>3.493</v>
+        <v>0.527</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>3.667</v>
+        <v>0.533</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6897,39 +6890,39 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E143" s="15" t="n">
-        <v>0</v>
+        <v>0.68</v>
+      </c>
+      <c r="E143" s="17" t="n">
+        <v>-0.0216</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>557800</v>
+        <v>879100</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="H143" t="n">
-        <v>46.29</v>
-      </c>
-      <c r="I143" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.78</v>
+      </c>
+      <c r="I143" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>1.263</v>
+        <v>0.619</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>1.319</v>
+        <v>0.523</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6942,39 +6935,39 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>2.39</v>
+        <v>0.995</v>
       </c>
       <c r="E144" s="17" t="n">
-        <v>-0.0083</v>
+        <v>-0.0149</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>554200</v>
+        <v>865300</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="H144" t="n">
-        <v>72.08</v>
-      </c>
-      <c r="I144" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.39</v>
+      </c>
+      <c r="I144" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>2.084</v>
+        <v>0.96</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>1.944</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -6987,28 +6980,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>0.965</v>
-      </c>
-      <c r="E145" s="10" t="n">
-        <v>0.0105</v>
+        <v>3.32</v>
+      </c>
+      <c r="E145" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>552800</v>
+        <v>864600</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="H145" t="n">
-        <v>31.66</v>
+        <v>30.1</v>
       </c>
       <c r="I145" s="16" t="inlineStr">
         <is>
@@ -7016,10 +7009,10 @@
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>1.008</v>
+        <v>3.493</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>1.075</v>
+        <v>3.667</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7032,28 +7025,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="E146" s="15" t="n">
-        <v>0</v>
+        <v>0.96</v>
+      </c>
+      <c r="E146" s="10" t="n">
+        <v>0.0052</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>552600</v>
+        <v>820500</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="H146" t="n">
-        <v>31.04</v>
+        <v>29.5</v>
       </c>
       <c r="I146" s="16" t="inlineStr">
         <is>
@@ -7061,10 +7054,10 @@
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>1.517</v>
+        <v>1.007</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>1.631</v>
+        <v>1.075</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -7077,28 +7070,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>7.94</v>
-      </c>
-      <c r="E147" s="17" t="n">
-        <v>-0.0075</v>
+        <v>1.43</v>
+      </c>
+      <c r="E147" s="10" t="n">
+        <v>0.006999999999999999</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>545800</v>
+        <v>819600</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>0.14</v>
+        <v>0.28</v>
       </c>
       <c r="H147" t="n">
-        <v>73</v>
+        <v>79.45</v>
       </c>
       <c r="I147" s="13" t="inlineStr">
         <is>
@@ -7106,10 +7099,10 @@
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>7.075</v>
+        <v>1.179</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>6.693</v>
+        <v>1.139</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
@@ -7122,39 +7115,39 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>UNISEM</t>
         </is>
       </c>
       <c r="D148" s="9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E148" s="17" t="n">
-        <v>-0.0167</v>
+        <v>4.43</v>
+      </c>
+      <c r="E148" s="10" t="n">
+        <v>0.0114</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>544200</v>
+        <v>801100</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>0.16</v>
+        <v>0.3</v>
       </c>
       <c r="H148" t="n">
-        <v>74.95999999999999</v>
-      </c>
-      <c r="I148" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.2</v>
+      </c>
+      <c r="I148" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>0.982</v>
+        <v>4.349</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>0.841</v>
+        <v>4.369</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -7167,28 +7160,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>PADINI</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D149" s="9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="E149" s="15" t="n">
-        <v>0</v>
+        <v>7.97</v>
+      </c>
+      <c r="E149" s="17" t="n">
+        <v>-0.0038</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>539700</v>
+        <v>764500</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>0.28</v>
+        <v>0.19</v>
       </c>
       <c r="H149" t="n">
-        <v>43.68</v>
+        <v>73.97</v>
       </c>
       <c r="I149" s="13" t="inlineStr">
         <is>
@@ -7196,10 +7189,10 @@
         </is>
       </c>
       <c r="J149" s="9" t="n">
-        <v>1.061</v>
+        <v>7.077</v>
       </c>
       <c r="K149" s="9" t="n">
-        <v>1.206</v>
+        <v>6.693</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="14" t="inlineStr"/>
@@ -7212,28 +7205,28 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0351</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>LSH</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D150" s="9" t="n">
-        <v>1.74</v>
+        <v>4.03</v>
       </c>
       <c r="E150" s="10" t="n">
-        <v>0.0296</v>
+        <v>0.0075</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>524700</v>
+        <v>749100</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>0.97</v>
+        <v>0.24</v>
       </c>
       <c r="H150" t="n">
-        <v>75.41</v>
+        <v>63.01</v>
       </c>
       <c r="I150" s="13" t="inlineStr">
         <is>
@@ -7241,10 +7234,10 @@
         </is>
       </c>
       <c r="J150" s="9" t="n">
-        <v>1.629</v>
+        <v>3.854</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>1.606</v>
+        <v>3.542</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -7257,28 +7250,28 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D151" s="9" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E151" s="10" t="n">
-        <v>0.01</v>
+        <v>5.2</v>
+      </c>
+      <c r="E151" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>519500</v>
+        <v>733900</v>
       </c>
       <c r="G151" s="12" t="n">
-        <v>0.35</v>
+        <v>0.15</v>
       </c>
       <c r="H151" t="n">
-        <v>59.81</v>
+        <v>61.57</v>
       </c>
       <c r="I151" s="13" t="inlineStr">
         <is>
@@ -7286,10 +7279,10 @@
         </is>
       </c>
       <c r="J151" s="9" t="n">
-        <v>0.484</v>
+        <v>5.042</v>
       </c>
       <c r="K151" s="9" t="n">
-        <v>0.476</v>
+        <v>5.058</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="14" t="inlineStr"/>
@@ -7302,45 +7295,990 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D152" s="9" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="E152" s="15" t="n">
-        <v>0</v>
+        <v>0.95</v>
+      </c>
+      <c r="E152" s="10" t="n">
+        <v>0.0215</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>515100</v>
+        <v>732800</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>0.1</v>
+        <v>0.39</v>
       </c>
       <c r="H152" t="n">
-        <v>26.38</v>
-      </c>
-      <c r="I152" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.93</v>
+      </c>
+      <c r="I152" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J152" s="9" t="n">
-        <v>4.522</v>
+        <v>0.922</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>4.871</v>
+        <v>0.842</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
     </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>6971</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>KOBAY</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E153" s="17" t="n">
+        <v>-0.0141</v>
+      </c>
+      <c r="F153" s="11" t="n">
+        <v>723500</v>
+      </c>
+      <c r="G153" s="12" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="H153" t="n">
+        <v>37.67</v>
+      </c>
+      <c r="I153" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J153" s="9" t="n">
+        <v>2.244</v>
+      </c>
+      <c r="K153" s="9" t="n">
+        <v>2.323</v>
+      </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" s="14" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>7174</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="D154" s="9" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E154" s="17" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F154" s="11" t="n">
+        <v>718500</v>
+      </c>
+      <c r="G154" s="12" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H154" t="n">
+        <v>85.22</v>
+      </c>
+      <c r="I154" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J154" s="9" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="K154" s="9" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" s="14" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>0263</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>BETA</t>
+        </is>
+      </c>
+      <c r="D155" s="9" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="E155" s="10" t="n">
+        <v>0.05429999999999999</v>
+      </c>
+      <c r="F155" s="11" t="n">
+        <v>701600</v>
+      </c>
+      <c r="G155" s="12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="H155" t="n">
+        <v>48.64</v>
+      </c>
+      <c r="I155" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J155" s="9" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="K155" s="9" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" s="14" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>0056</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>NCT</t>
+        </is>
+      </c>
+      <c r="D156" s="9" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E156" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" s="11" t="n">
+        <v>693300</v>
+      </c>
+      <c r="G156" s="12" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H156" t="n">
+        <v>48.46</v>
+      </c>
+      <c r="I156" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J156" s="9" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="K156" s="9" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" s="14" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>7293</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>YINSON</t>
+        </is>
+      </c>
+      <c r="D157" s="9" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="E157" s="10" t="n">
+        <v>0.004699999999999999</v>
+      </c>
+      <c r="F157" s="11" t="n">
+        <v>675700</v>
+      </c>
+      <c r="G157" s="12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H157" t="n">
+        <v>56.83</v>
+      </c>
+      <c r="I157" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J157" s="9" t="n">
+        <v>2.082</v>
+      </c>
+      <c r="K157" s="9" t="n">
+        <v>2.035</v>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" s="14" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>GCB</t>
+        </is>
+      </c>
+      <c r="D158" s="9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E158" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F158" s="11" t="n">
+        <v>673500</v>
+      </c>
+      <c r="G158" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H158" t="n">
+        <v>43.85</v>
+      </c>
+      <c r="I158" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J158" s="9" t="n">
+        <v>1.334</v>
+      </c>
+      <c r="K158" s="9" t="n">
+        <v>1.307</v>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" s="14" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>0375</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>THMY</t>
+        </is>
+      </c>
+      <c r="D159" s="9" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="E159" s="17" t="n">
+        <v>-0.0083</v>
+      </c>
+      <c r="F159" s="11" t="n">
+        <v>671500</v>
+      </c>
+      <c r="G159" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H159" t="n">
+        <v>72.08</v>
+      </c>
+      <c r="I159" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J159" s="9" t="n">
+        <v>2.084</v>
+      </c>
+      <c r="K159" s="9" t="n">
+        <v>1.944</v>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" s="14" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>0338</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>KOPI</t>
+        </is>
+      </c>
+      <c r="D160" s="9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E160" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F160" s="11" t="n">
+        <v>663900</v>
+      </c>
+      <c r="G160" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H160" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="I160" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J160" s="9" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="K160" s="9" t="n">
+        <v>0.968</v>
+      </c>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" s="14" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>8869</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>PMETAL</t>
+        </is>
+      </c>
+      <c r="D161" s="9" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="E161" s="10" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="F161" s="11" t="n">
+        <v>656600</v>
+      </c>
+      <c r="G161" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H161" t="n">
+        <v>32.48</v>
+      </c>
+      <c r="I161" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J161" s="9" t="n">
+        <v>7.465</v>
+      </c>
+      <c r="K161" s="9" t="n">
+        <v>7.754</v>
+      </c>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" s="14" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>7277</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>DIALOG</t>
+        </is>
+      </c>
+      <c r="D162" s="9" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="E162" s="10" t="n">
+        <v>0.0107</v>
+      </c>
+      <c r="F162" s="11" t="n">
+        <v>650300</v>
+      </c>
+      <c r="G162" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H162" t="n">
+        <v>41.41</v>
+      </c>
+      <c r="I162" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J162" s="9" t="n">
+        <v>1.934</v>
+      </c>
+      <c r="K162" s="9" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" s="14" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>0351</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>LSH</t>
+        </is>
+      </c>
+      <c r="D163" s="9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="E163" s="10" t="n">
+        <v>0.0355</v>
+      </c>
+      <c r="F163" s="11" t="n">
+        <v>640300</v>
+      </c>
+      <c r="G163" s="12" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="H163" t="n">
+        <v>76.36</v>
+      </c>
+      <c r="I163" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J163" s="9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="K163" s="9" t="n">
+        <v>1.606</v>
+      </c>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" s="14" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>0045</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>SSB8</t>
+        </is>
+      </c>
+      <c r="D164" s="9" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E164" s="17" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F164" s="11" t="n">
+        <v>631500</v>
+      </c>
+      <c r="G164" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H164" t="n">
+        <v>55.69</v>
+      </c>
+      <c r="I164" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J164" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K164" s="9" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" s="14" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>5351</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="D165" s="9" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E165" s="10" t="n">
+        <v>0.0675</v>
+      </c>
+      <c r="F165" s="11" t="n">
+        <v>625000</v>
+      </c>
+      <c r="G165" s="12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H165" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="I165" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J165" s="9" t="n">
+        <v>0.859</v>
+      </c>
+      <c r="K165" s="9" t="n">
+        <v>0.928</v>
+      </c>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" s="14" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>7052</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>PADINI</t>
+        </is>
+      </c>
+      <c r="D166" s="9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E166" s="10" t="n">
+        <v>0.009399999999999999</v>
+      </c>
+      <c r="F166" s="11" t="n">
+        <v>602500</v>
+      </c>
+      <c r="G166" s="12" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H166" t="n">
+        <v>46.04</v>
+      </c>
+      <c r="I166" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J166" s="9" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="K166" s="9" t="n">
+        <v>1.207</v>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" s="14" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>4715</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>GENM</t>
+        </is>
+      </c>
+      <c r="D167" s="9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="E167" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F167" s="11" t="n">
+        <v>600800</v>
+      </c>
+      <c r="G167" s="12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H167" t="n">
+        <v>31.04</v>
+      </c>
+      <c r="I167" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J167" s="9" t="n">
+        <v>1.517</v>
+      </c>
+      <c r="K167" s="9" t="n">
+        <v>1.631</v>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" s="14" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>HIBISCS</t>
+        </is>
+      </c>
+      <c r="D168" s="9" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="E168" s="10" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="F168" s="11" t="n">
+        <v>599000</v>
+      </c>
+      <c r="G168" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H168" t="n">
+        <v>48.99</v>
+      </c>
+      <c r="I168" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J168" s="9" t="n">
+        <v>2.188</v>
+      </c>
+      <c r="K168" s="9" t="n">
+        <v>2.119</v>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" s="14" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>5335</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>HI</t>
+        </is>
+      </c>
+      <c r="D169" s="9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="E169" s="17" t="n">
+        <v>-0.0275</v>
+      </c>
+      <c r="F169" s="11" t="n">
+        <v>592700</v>
+      </c>
+      <c r="G169" s="12" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H169" t="n">
+        <v>40.19</v>
+      </c>
+      <c r="I169" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J169" s="9" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="K169" s="9" t="n">
+        <v>1.841</v>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" s="14" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>0376</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>IAB</t>
+        </is>
+      </c>
+      <c r="D170" s="9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E170" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F170" s="11" t="n">
+        <v>576000</v>
+      </c>
+      <c r="G170" s="12" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H170" t="n">
+        <v>46.29</v>
+      </c>
+      <c r="I170" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J170" s="9" t="n">
+        <v>1.263</v>
+      </c>
+      <c r="K170" s="9" t="n">
+        <v>1.319</v>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" s="14" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>0246</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>CNERGEN</t>
+        </is>
+      </c>
+      <c r="D171" s="9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="E171" s="17" t="n">
+        <v>-0.0167</v>
+      </c>
+      <c r="F171" s="11" t="n">
+        <v>549800</v>
+      </c>
+      <c r="G171" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H171" t="n">
+        <v>74.95999999999999</v>
+      </c>
+      <c r="I171" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J171" s="9" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="K171" s="9" t="n">
+        <v>0.841</v>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" s="14" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D172" s="9" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="E172" s="17" t="n">
+        <v>-0.0118</v>
+      </c>
+      <c r="F172" s="11" t="n">
+        <v>520400</v>
+      </c>
+      <c r="G172" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H172" t="n">
+        <v>58.33</v>
+      </c>
+      <c r="I172" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J172" s="9" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="K172" s="9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" s="14" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>6947</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="D173" s="9" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="E173" s="17" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F173" s="11" t="n">
+        <v>512800</v>
+      </c>
+      <c r="G173" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H173" t="n">
+        <v>31.43</v>
+      </c>
+      <c r="I173" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J173" s="9" t="n">
+        <v>2.601</v>
+      </c>
+      <c r="K173" s="9" t="n">
+        <v>2.743</v>
+      </c>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M152"/>
+  <autoFilter ref="A1:M173"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-07/bursa-report-2026-10-07.xlsx
+++ b/docs/downloads/2026-10-07/bursa-report-2026-10-07.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-07" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-07'!$A$1:$M$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-07'!$A$1:$M$187</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,10 +38,10 @@
       <color rgb="000CA30C"/>
     </font>
     <font>
-      <color rgb="00898781"/>
+      <color rgb="00D03B3B"/>
     </font>
     <font>
-      <color rgb="00D03B3B"/>
+      <color rgb="00898781"/>
     </font>
   </fonts>
   <fills count="4">
@@ -97,7 +97,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M173"/>
+  <dimension ref="A1:M187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.1408</v>
+        <v>0.1268</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>6974100</v>
+        <v>7607500</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>6.08</v>
+        <v>6.64</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>67.77</v>
+        <v>66.27</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.736</v>
+        <v>0.735</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0.722</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多，现价0.81高于50日均线0.722约12%，RSI 67.77接近超买区，信号偏强但需留意短线过热。</t>
+          <t>现价0.8高于50日均线0.722，SAR转多信号获均线支撑；RSI 66.27接近超买区，动能偏强但上行空间有限。</t>
         </is>
       </c>
     </row>
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>0.0171</v>
+        <v>0.005699999999999999</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>175869100</v>
+        <v>211453800</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>3.19</v>
+        <v>3.84</v>
       </c>
       <c r="H3" t="n">
-        <v>74.53</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="I3" s="13" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="J3" s="9" t="n">
-        <v>0.768</v>
+        <v>0.767</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>0.703</v>
@@ -664,19 +664,19 @@
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.09</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="E4" s="15" t="n">
-        <v>0</v>
+        <v>-0.0556</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>124754000</v>
+        <v>136613100</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="H4" t="n">
-        <v>21.78</v>
+        <v>21.4</v>
       </c>
       <c r="I4" s="16" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.195</v>
+        <v>0.194</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>0.413</v>
@@ -709,23 +709,23 @@
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E5" s="15" t="n">
-        <v>0</v>
+        <v>0.01</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>64663700</v>
+        <v>64665700</v>
       </c>
       <c r="G5" s="12" t="n">
         <v>66.89</v>
       </c>
       <c r="H5" t="n">
-        <v>47.04</v>
-      </c>
-      <c r="I5" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.23</v>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J5" s="9" t="n">
@@ -760,10 +760,10 @@
         <v>0.0109</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>52688500</v>
+        <v>55810800</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>2.33</v>
+        <v>2.46</v>
       </c>
       <c r="H6" t="n">
         <v>70.33</v>
@@ -799,19 +799,19 @@
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.33</v>
+        <v>0.325</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>0</v>
+        <v>-0.0152</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>40472800</v>
+        <v>46035500</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.83</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>78.06999999999999</v>
+        <v>75.34</v>
       </c>
       <c r="I7" s="13" t="inlineStr">
         <is>
@@ -835,33 +835,40 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>9393</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SLGC Berhad</t>
+          <t>ITRONIC</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>26526600</v>
+        <v>27607800</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="I8" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J8" s="9" t="n"/>
-      <c r="K8" s="9" t="n"/>
+        <v>22.44</v>
+      </c>
+      <c r="H8" t="n">
+        <v>46.69</v>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>0.031</v>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
     </row>
@@ -873,40 +880,33 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>9393</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ITRONIC</t>
+          <t>SLGC Berhad</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="E9" s="17" t="n">
-        <v>-0.1667</v>
+        <v>0.255</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>0.02</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>23213200</v>
+        <v>27218500</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>18.87</v>
-      </c>
-      <c r="H9" t="n">
-        <v>37.04</v>
-      </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J9" s="9" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="K9" s="9" t="n">
-        <v>0.031</v>
-      </c>
+        <v>0.33</v>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="n"/>
+      <c r="K9" s="9" t="n"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
     </row>
@@ -918,28 +918,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E10" s="17" t="n">
-        <v>-0.04</v>
+        <v>0.66</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>0.0476</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>20532500</v>
+        <v>24206300</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.49</v>
+        <v>1.32</v>
       </c>
       <c r="H10" t="n">
-        <v>61.99</v>
+        <v>68.45</v>
       </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.348</v>
+        <v>0.572</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.227</v>
+        <v>0.511</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -963,28 +963,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>0.0317</v>
+        <v>1.1</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>-0.0179</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>20463900</v>
+        <v>20828200</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1.11</v>
+        <v>1.64</v>
       </c>
       <c r="H11" t="n">
-        <v>67.37</v>
+        <v>55.16</v>
       </c>
       <c r="I11" s="13" t="inlineStr">
         <is>
@@ -992,10 +992,10 @@
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.571</v>
+        <v>1.075</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.511</v>
+        <v>1.034</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1008,28 +1008,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>-0.0089</v>
+        <v>0.36</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>-0.04</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>19299100</v>
+        <v>20533500</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>1.52</v>
+        <v>0.49</v>
       </c>
       <c r="H12" t="n">
-        <v>56.89</v>
+        <v>61.99</v>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>1.076</v>
+        <v>0.348</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>1.034</v>
+        <v>0.227</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1053,39 +1053,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0163</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CAREPLS</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.09</v>
+        <v>0.595</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>0</v>
+        <v>-0.0165</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>16217500</v>
+        <v>17890000</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>1.52</v>
+        <v>0.68</v>
       </c>
       <c r="H13" t="n">
-        <v>64.26000000000001</v>
-      </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.73999999999999</v>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.083</v>
+        <v>0.575</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.078</v>
+        <v>0.501</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1098,39 +1098,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0163</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>CAREPLS</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.595</v>
+        <v>0.09</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>-0.0165</v>
+        <v>0</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>15107300</v>
+        <v>16317500</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.58</v>
+        <v>1.53</v>
       </c>
       <c r="H14" t="n">
-        <v>65.73999999999999</v>
-      </c>
-      <c r="I14" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>64.26000000000001</v>
+      </c>
+      <c r="I14" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.575</v>
+        <v>0.083</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.501</v>
+        <v>0.078</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1143,39 +1143,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>7.36</v>
-      </c>
-      <c r="E15" s="17" t="n">
-        <v>-0.0442</v>
+        <v>1.2</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>-0.04</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>12894600</v>
+        <v>16270900</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>1.05</v>
+        <v>1.64</v>
       </c>
       <c r="H15" t="n">
-        <v>33.89</v>
-      </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.56</v>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>7.728</v>
+        <v>1.169</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>7.75</v>
+        <v>1.118</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1188,39 +1188,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="E16" s="17" t="n">
-        <v>-0.024</v>
+        <v>7.33</v>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>-0.0481</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>12798900</v>
+        <v>16053400</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="H16" t="n">
-        <v>58.48</v>
-      </c>
-      <c r="I16" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.09</v>
+      </c>
+      <c r="I16" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>1.17</v>
+        <v>7.725</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>1.118</v>
+        <v>7.75</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1233,39 +1233,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>0.01</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>10069400</v>
+        <v>12418100</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.38</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>60.08</v>
-      </c>
-      <c r="I17" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.2</v>
+      </c>
+      <c r="I17" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.483</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.477</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1278,39 +1278,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E18" s="15" t="n">
-        <v>0</v>
+        <v>0.505</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>0.01</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>10023500</v>
+        <v>10661800</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.65</v>
+        <v>0.4</v>
       </c>
       <c r="H18" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="I18" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.08</v>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.483</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.477</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1338,10 +1338,10 @@
         <v>0.0233</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>10010200</v>
+        <v>10067700</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="H19" t="n">
         <v>42.12</v>
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.165</v>
+        <v>0.16</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>0</v>
+        <v>-0.0303</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>9708700</v>
+        <v>9914900</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>17.32</v>
+        <v>17.69</v>
       </c>
       <c r="H20" t="n">
-        <v>71.63</v>
+        <v>66.42</v>
       </c>
       <c r="I20" s="13" t="inlineStr">
         <is>
@@ -1424,14 +1424,14 @@
       <c r="D21" s="9" t="n">
         <v>0.175</v>
       </c>
-      <c r="E21" s="17" t="n">
+      <c r="E21" s="15" t="n">
         <v>-0.0278</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>8703300</v>
+        <v>9353100</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="H21" t="n">
         <v>59.26</v>
@@ -1458,28 +1458,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.145</v>
+        <v>0.305</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>0</v>
+        <v>-0.0161</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>8670300</v>
+        <v>9047800</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.26</v>
+        <v>0.47</v>
       </c>
       <c r="H22" t="n">
-        <v>44.39</v>
+        <v>52.4</v>
       </c>
       <c r="I22" s="16" t="inlineStr">
         <is>
@@ -1487,10 +1487,10 @@
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.157</v>
+        <v>0.304</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.147</v>
+        <v>0.294</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1514,14 +1514,14 @@
       <c r="D23" s="9" t="n">
         <v>0.78</v>
       </c>
-      <c r="E23" s="15" t="n">
+      <c r="E23" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>7805100</v>
+        <v>8857800</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.55</v>
+        <v>0.63</v>
       </c>
       <c r="H23" t="n">
         <v>53.14</v>
@@ -1548,28 +1548,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="E24" s="15" t="n">
-        <v>0</v>
+        <v>0.15</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>0.0345</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>7780900</v>
+        <v>8680300</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.68</v>
+        <v>0.26</v>
       </c>
       <c r="H24" t="n">
-        <v>38.38</v>
+        <v>47.02</v>
       </c>
       <c r="I24" s="16" t="inlineStr">
         <is>
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.404</v>
+        <v>0.157</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.411</v>
+        <v>0.147</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1593,39 +1593,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.455</v>
+        <v>0.395</v>
       </c>
       <c r="E25" s="17" t="n">
-        <v>-0.0421</v>
+        <v>0</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>7657700</v>
+        <v>8241200</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.8</v>
+        <v>0.72</v>
       </c>
       <c r="H25" t="n">
-        <v>52.03</v>
-      </c>
-      <c r="I25" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.38</v>
+      </c>
+      <c r="I25" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.454</v>
+        <v>0.404</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.423</v>
+        <v>0.411</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1638,28 +1638,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>COMFORT</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.175</v>
+        <v>0.46</v>
       </c>
       <c r="E26" s="15" t="n">
-        <v>0</v>
+        <v>-0.0316</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>7394100</v>
+        <v>8045100</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>6.05</v>
+        <v>0.84</v>
       </c>
       <c r="H26" t="n">
-        <v>66.40000000000001</v>
+        <v>53.38</v>
       </c>
       <c r="I26" s="13" t="inlineStr">
         <is>
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.161</v>
+        <v>0.454</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.153</v>
+        <v>0.423</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1683,28 +1683,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>COMFORT</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.825</v>
+        <v>0.175</v>
       </c>
       <c r="E27" s="17" t="n">
-        <v>-0.0179</v>
+        <v>0</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>6992800</v>
+        <v>7472600</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.53</v>
+        <v>6.11</v>
       </c>
       <c r="H27" t="n">
-        <v>63.55</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I27" s="13" t="inlineStr">
         <is>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.762</v>
+        <v>0.161</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.708</v>
+        <v>0.153</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1728,28 +1728,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>7803</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>HEXCARE</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="E28" s="10" t="n">
-        <v>0.0833</v>
+        <v>9.9</v>
+      </c>
+      <c r="E28" s="15" t="n">
+        <v>-0.006999999999999999</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>6856000</v>
+        <v>7418200</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>3.94</v>
+        <v>0.62</v>
       </c>
       <c r="H28" t="n">
-        <v>57.12</v>
+        <v>34.44</v>
       </c>
       <c r="I28" s="16" t="inlineStr">
         <is>
@@ -1757,10 +1757,10 @@
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.061</v>
+        <v>10.072</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.061</v>
+        <v>10.234</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1773,39 +1773,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E29" s="17" t="n">
-        <v>-0.0161</v>
+        <v>0.82</v>
+      </c>
+      <c r="E29" s="15" t="n">
+        <v>-0.0238</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>6616700</v>
+        <v>7397300</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.35</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H29" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="I29" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.53</v>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.304</v>
+        <v>0.762</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.294</v>
+        <v>0.708</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1818,39 +1818,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="E30" s="17" t="n">
-        <v>-0.006999999999999999</v>
+        <v>0.745</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>0.0347</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>6268500</v>
+        <v>7088400</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.53</v>
+        <v>0.8</v>
       </c>
       <c r="H30" t="n">
-        <v>34.44</v>
-      </c>
-      <c r="I30" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.25</v>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>10.072</v>
+        <v>0.666</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>10.234</v>
+        <v>0.6</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1863,28 +1863,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E31" s="15" t="n">
-        <v>0</v>
+        <v>1.87</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>0.0275</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>6164900</v>
+        <v>7062900</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.9</v>
+        <v>0.31</v>
       </c>
       <c r="H31" t="n">
-        <v>33.85</v>
+        <v>63.09</v>
       </c>
       <c r="I31" s="16" t="inlineStr">
         <is>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.292</v>
+        <v>1.776</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.309</v>
+        <v>1.616</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1908,28 +1908,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>7803</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>HEXCARE</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>1.85</v>
+        <v>0.065</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>0.0165</v>
+        <v>0.0833</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>6144300</v>
+        <v>6856000</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.27</v>
+        <v>3.94</v>
       </c>
       <c r="H32" t="n">
-        <v>61.66</v>
+        <v>57.12</v>
       </c>
       <c r="I32" s="16" t="inlineStr">
         <is>
@@ -1937,10 +1937,10 @@
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>1.774</v>
+        <v>0.061</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>1.616</v>
+        <v>0.061</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1953,39 +1953,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0131</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DFX</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.15</v>
+        <v>0.28</v>
       </c>
       <c r="E33" s="17" t="n">
-        <v>-0.0323</v>
+        <v>0</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>6087200</v>
+        <v>6424200</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>78.90000000000001</v>
-      </c>
-      <c r="I33" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.85</v>
+      </c>
+      <c r="I33" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.111</v>
+        <v>0.292</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.092</v>
+        <v>0.309</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1998,39 +1998,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="E34" s="17" t="n">
-        <v>-0.0202</v>
+        <v>0.835</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>0.0309</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>5741500</v>
+        <v>6195900</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.15</v>
+        <v>0.99</v>
       </c>
       <c r="H34" t="n">
-        <v>27.56</v>
-      </c>
-      <c r="I34" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.73999999999999</v>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.731</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.768</v>
+        <v>0.654</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2043,28 +2043,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0131</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>DFX</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E35" s="15" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="E35" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>5633900</v>
+        <v>6149700</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="H35" t="n">
-        <v>71.65000000000001</v>
+        <v>83.98999999999999</v>
       </c>
       <c r="I35" s="13" t="inlineStr">
         <is>
@@ -2072,10 +2072,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.288</v>
+        <v>0.112</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.273</v>
+        <v>0.092</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2088,39 +2088,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="E36" s="10" t="n">
-        <v>0.0247</v>
+        <v>2.16</v>
+      </c>
+      <c r="E36" s="15" t="n">
+        <v>-0.0046</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>5555900</v>
+        <v>5960000</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.89</v>
+        <v>0.41</v>
       </c>
       <c r="H36" t="n">
-        <v>74.26000000000001</v>
-      </c>
-      <c r="I36" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.1</v>
+      </c>
+      <c r="I36" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.731</v>
+        <v>2.247</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.653</v>
+        <v>2.222</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2133,39 +2133,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0209</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AIMFLEX</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.11</v>
+        <v>0.41</v>
       </c>
       <c r="E37" s="15" t="n">
-        <v>0</v>
+        <v>-0.012</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>5482900</v>
+        <v>5934000</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.85</v>
+        <v>0.51</v>
       </c>
       <c r="H37" t="n">
-        <v>41.61</v>
-      </c>
-      <c r="I37" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.03</v>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.116</v>
+        <v>0.386</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.123</v>
+        <v>0.375</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2178,28 +2178,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="E38" s="15" t="n">
+        <v>-0.0202</v>
+      </c>
+      <c r="F38" s="11" t="n">
+        <v>5836700</v>
+      </c>
+      <c r="G38" s="12" t="n">
         <v>0.15</v>
       </c>
-      <c r="E38" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="11" t="n">
-        <v>5143700</v>
-      </c>
-      <c r="G38" s="12" t="n">
-        <v>0.28</v>
-      </c>
       <c r="H38" t="n">
-        <v>30.36</v>
+        <v>27.56</v>
       </c>
       <c r="I38" s="16" t="inlineStr">
         <is>
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.168</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.204</v>
+        <v>0.768</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2223,39 +2223,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0209</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>AIMFLEX</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E39" s="15" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E39" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>5110800</v>
+        <v>5802000</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.35</v>
+        <v>0.9</v>
       </c>
       <c r="H39" t="n">
-        <v>52.96</v>
-      </c>
-      <c r="I39" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.61</v>
+      </c>
+      <c r="I39" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.29</v>
+        <v>0.116</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.279</v>
+        <v>0.123</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2268,39 +2268,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E40" s="10" t="n">
-        <v>0.0169</v>
+        <v>4.62</v>
+      </c>
+      <c r="E40" s="15" t="n">
+        <v>-0.0107</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>5031500</v>
+        <v>5721300</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
       <c r="H40" t="n">
-        <v>59.64</v>
-      </c>
-      <c r="I40" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.94</v>
+      </c>
+      <c r="I40" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.276</v>
+        <v>4.759</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.305</v>
+        <v>4.906</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2313,28 +2313,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0328</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>3REN</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.405</v>
+        <v>2.7</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>0.0385</v>
+        <v>0.0112</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>4977700</v>
+        <v>5681200</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>3.04</v>
+        <v>0.32</v>
       </c>
       <c r="H41" t="n">
-        <v>59.74</v>
+        <v>60.67</v>
       </c>
       <c r="I41" s="13" t="inlineStr">
         <is>
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.385</v>
+        <v>2.589</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.39</v>
+        <v>2.487</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2358,39 +2358,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="E42" s="17" t="n">
-        <v>-0.0046</v>
+        <v>0.62</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>0.0164</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>4767300</v>
+        <v>5672200</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="H42" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="I42" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.75</v>
+      </c>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>2.247</v>
+        <v>0.609</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>2.222</v>
+        <v>0.61</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2403,28 +2403,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0395</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>OGX</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E43" s="10" t="n">
-        <v>0.0444</v>
+        <v>0.305</v>
+      </c>
+      <c r="E43" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>4691400</v>
+        <v>5634900</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>2</v>
+        <v>0.91</v>
       </c>
       <c r="H43" t="n">
-        <v>60.55</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="I43" s="13" t="inlineStr">
         <is>
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.44</v>
+        <v>0.288</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.45</v>
+        <v>0.273</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2448,28 +2448,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E44" s="10" t="n">
-        <v>0.0164</v>
+        <v>0.865</v>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>4677300</v>
+        <v>5387800</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.44</v>
+        <v>0.29</v>
       </c>
       <c r="H44" t="n">
-        <v>55.75</v>
+        <v>46.41</v>
       </c>
       <c r="I44" s="13" t="inlineStr">
         <is>
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.609</v>
+        <v>0.868</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.61</v>
+        <v>0.869</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2493,39 +2493,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>4.62</v>
+        <v>0.295</v>
       </c>
       <c r="E45" s="17" t="n">
-        <v>-0.0107</v>
+        <v>0</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>4633600</v>
+        <v>5371500</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.28</v>
+        <v>0.36</v>
       </c>
       <c r="H45" t="n">
-        <v>29.94</v>
-      </c>
-      <c r="I45" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.96</v>
+      </c>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>4.759</v>
+        <v>0.29</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>4.906</v>
+        <v>0.279</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2538,28 +2538,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0395</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>OGX</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E46" s="15" t="n">
-        <v>0</v>
+        <v>0.47</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>0.0444</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>4589800</v>
+        <v>5345000</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.39</v>
+        <v>2.28</v>
       </c>
       <c r="H46" t="n">
-        <v>72.51000000000001</v>
+        <v>60.55</v>
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.387</v>
+        <v>0.44</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.375</v>
+        <v>0.45</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2583,39 +2583,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="E47" s="17" t="n">
-        <v>-0.0175</v>
+        <v>4.99</v>
+      </c>
+      <c r="E47" s="15" t="n">
+        <v>-0.002</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>4579900</v>
+        <v>5283000</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="H47" t="n">
-        <v>22.14</v>
-      </c>
-      <c r="I47" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.39</v>
+      </c>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>7.703</v>
+        <v>4.896</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>8.145</v>
+        <v>4.627</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2628,28 +2628,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E48" s="10" t="n">
-        <v>0.0211</v>
+        <v>0.805</v>
+      </c>
+      <c r="E48" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>4523800</v>
+        <v>5257200</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.58</v>
+        <v>0.86</v>
       </c>
       <c r="H48" t="n">
-        <v>58.56</v>
+        <v>70.22</v>
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
@@ -2657,10 +2657,10 @@
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.781</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.676</v>
+        <v>0.762</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2673,39 +2673,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="E49" s="10" t="n">
-        <v>0.015</v>
+        <v>0.15</v>
+      </c>
+      <c r="E49" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>4500900</v>
+        <v>5151800</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.26</v>
+        <v>0.28</v>
       </c>
       <c r="H49" t="n">
-        <v>61.27</v>
-      </c>
-      <c r="I49" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.36</v>
+      </c>
+      <c r="I49" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>2.59</v>
+        <v>0.168</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>2.487</v>
+        <v>0.204</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2718,28 +2718,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E50" s="15" t="n">
-        <v>0</v>
+        <v>0.3</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>0.0169</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>4389800</v>
+        <v>5061700</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.72</v>
+        <v>0.5</v>
       </c>
       <c r="H50" t="n">
-        <v>70.22</v>
+        <v>59.64</v>
       </c>
       <c r="I50" s="13" t="inlineStr">
         <is>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.781</v>
+        <v>0.276</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.762</v>
+        <v>0.305</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2763,28 +2763,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="E51" s="17" t="n">
-        <v>-0.002</v>
+        <v>0.405</v>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>0.0385</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>4197900</v>
+        <v>4977700</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.16</v>
+        <v>3.04</v>
       </c>
       <c r="H51" t="n">
-        <v>60.39</v>
+        <v>59.74</v>
       </c>
       <c r="I51" s="13" t="inlineStr">
         <is>
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>4.896</v>
+        <v>0.385</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>4.627</v>
+        <v>0.39</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2808,39 +2808,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E52" s="17" t="n">
-        <v>-0.0137</v>
+        <v>7.29</v>
+      </c>
+      <c r="E52" s="15" t="n">
+        <v>-0.0188</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>4191900</v>
+        <v>4898000</v>
       </c>
       <c r="G52" s="12" t="n">
         <v>0.54</v>
       </c>
       <c r="H52" t="n">
-        <v>62.63</v>
-      </c>
-      <c r="I52" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>21.91</v>
+      </c>
+      <c r="I52" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.343</v>
+        <v>7.702</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.323</v>
+        <v>8.144</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2853,39 +2853,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>3.52</v>
+        <v>0.725</v>
       </c>
       <c r="E53" s="10" t="n">
-        <v>0.0173</v>
+        <v>0.0211</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>3987100</v>
+        <v>4768700</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.33</v>
+        <v>0.62</v>
       </c>
       <c r="H53" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="I53" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.56</v>
+      </c>
+      <c r="I53" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>3.573</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>2.667</v>
+        <v>0.676</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2898,28 +2898,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E54" s="15" t="n">
-        <v>0</v>
+        <v>0.63</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>0.0413</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>3918400</v>
+        <v>4685200</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.21</v>
+        <v>1.5</v>
       </c>
       <c r="H54" t="n">
-        <v>46.41</v>
+        <v>63.2</v>
       </c>
       <c r="I54" s="13" t="inlineStr">
         <is>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.868</v>
+        <v>0.585</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.869</v>
+        <v>0.579</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2943,39 +2943,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="E55" s="10" t="n">
-        <v>0.0667</v>
+        <v>1.24</v>
+      </c>
+      <c r="E55" s="15" t="n">
+        <v>-0.008</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>3783300</v>
+        <v>4339200</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.98</v>
+        <v>0.42</v>
       </c>
       <c r="H55" t="n">
-        <v>64.34</v>
-      </c>
-      <c r="I55" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.4</v>
+      </c>
+      <c r="I55" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>5.709</v>
+        <v>1.295</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>5.764</v>
+        <v>1.396</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2988,39 +2988,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="E56" s="10" t="n">
-        <v>0.0048</v>
+        <v>0.355</v>
+      </c>
+      <c r="E56" s="15" t="n">
+        <v>-0.0274</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>3725200</v>
+        <v>4280500</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.19</v>
+        <v>0.55</v>
       </c>
       <c r="H56" t="n">
-        <v>49.12</v>
-      </c>
-      <c r="I56" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.59</v>
+      </c>
+      <c r="I56" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>2.098</v>
+        <v>0.343</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>2.078</v>
+        <v>0.322</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3033,39 +3033,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="E57" s="17" t="n">
-        <v>-0.016</v>
+        <v>6.39</v>
+      </c>
+      <c r="E57" s="10" t="n">
+        <v>0.065</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>3664600</v>
+        <v>4261700</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.36</v>
+        <v>1.11</v>
       </c>
       <c r="H57" t="n">
-        <v>31.06</v>
-      </c>
-      <c r="I57" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.2</v>
+      </c>
+      <c r="I57" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>1.294</v>
+        <v>5.708</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>1.396</v>
+        <v>5.763</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3078,39 +3078,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.63</v>
+        <v>3.53</v>
       </c>
       <c r="E58" s="10" t="n">
-        <v>0.0413</v>
+        <v>0.0202</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>3645200</v>
+        <v>4220600</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>1.16</v>
+        <v>0.35</v>
       </c>
       <c r="H58" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="I58" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.12</v>
+      </c>
+      <c r="I58" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.585</v>
+        <v>3.574</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.579</v>
+        <v>2.667</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3123,28 +3123,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="E59" s="17" t="n">
-        <v>-0.025</v>
+        <v>0.52</v>
+      </c>
+      <c r="E59" s="10" t="n">
+        <v>0.0297</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>3537000</v>
+        <v>3927300</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.15</v>
+        <v>0.64</v>
       </c>
       <c r="H59" t="n">
-        <v>51.04</v>
+        <v>50.16</v>
       </c>
       <c r="I59" s="16" t="inlineStr">
         <is>
@@ -3152,10 +3152,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.196</v>
+        <v>0.519</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0.183</v>
+        <v>0.53</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3168,39 +3168,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>1.17</v>
+        <v>2.09</v>
       </c>
       <c r="E60" s="10" t="n">
-        <v>0.0541</v>
+        <v>0.0048</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>3535100</v>
+        <v>3913000</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.73</v>
+        <v>0.2</v>
       </c>
       <c r="H60" t="n">
-        <v>78.63</v>
-      </c>
-      <c r="I60" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.12</v>
+      </c>
+      <c r="I60" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>1.042</v>
+        <v>2.098</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.875</v>
+        <v>2.078</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3222,19 +3222,19 @@
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.62</v>
+        <v>0.615</v>
       </c>
       <c r="E61" s="10" t="n">
-        <v>0.0333</v>
+        <v>0.025</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>3403100</v>
+        <v>3789400</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="H61" t="n">
-        <v>73.48</v>
+        <v>72.84</v>
       </c>
       <c r="I61" s="13" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.541</v>
+        <v>0.54</v>
       </c>
       <c r="K61" s="9" t="n">
         <v>0.489</v>
@@ -3258,28 +3258,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.795</v>
+        <v>1.18</v>
       </c>
       <c r="E62" s="10" t="n">
-        <v>0.0127</v>
+        <v>0.06309999999999999</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>3317700</v>
+        <v>3730000</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.42</v>
+        <v>0.77</v>
       </c>
       <c r="H62" t="n">
-        <v>55.54</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
@@ -3287,10 +3287,10 @@
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.777</v>
+        <v>1.043</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.772</v>
+        <v>0.875</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3303,28 +3303,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.735</v>
+        <v>0.73</v>
       </c>
       <c r="E63" s="10" t="n">
-        <v>0.0208</v>
+        <v>0.08960000000000001</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>3296800</v>
+        <v>3696200</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.37</v>
+        <v>2.73</v>
       </c>
       <c r="H63" t="n">
-        <v>68.04000000000001</v>
+        <v>73.73</v>
       </c>
       <c r="I63" s="13" t="inlineStr">
         <is>
@@ -3332,10 +3332,10 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>0.665</v>
+        <v>0.649</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>0.6</v>
+        <v>0.613</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3348,39 +3348,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.515</v>
+        <v>0.795</v>
       </c>
       <c r="E64" s="10" t="n">
-        <v>0.0198</v>
+        <v>0.0127</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>3213900</v>
+        <v>3639000</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.53</v>
+        <v>0.46</v>
       </c>
       <c r="H64" t="n">
-        <v>48.37</v>
-      </c>
-      <c r="I64" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.54</v>
+      </c>
+      <c r="I64" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>0.518</v>
+        <v>0.777</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.53</v>
+        <v>0.772</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3393,39 +3393,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5115</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ALAM</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E65" s="10" t="n">
-        <v>0.175</v>
+        <v>0.2</v>
+      </c>
+      <c r="E65" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>3185300</v>
+        <v>3638000</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>5.74</v>
+        <v>0.15</v>
       </c>
       <c r="H65" t="n">
-        <v>53.85</v>
-      </c>
-      <c r="I65" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.23</v>
+      </c>
+      <c r="I65" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>0.225</v>
+        <v>0.197</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0.242</v>
+        <v>0.183</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3438,39 +3438,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E66" s="10" t="n">
-        <v>0.08960000000000001</v>
+        <v>6.22</v>
+      </c>
+      <c r="E66" s="15" t="n">
+        <v>-0.0386</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>3031400</v>
+        <v>3325800</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>2.24</v>
+        <v>0.85</v>
       </c>
       <c r="H66" t="n">
-        <v>73.73</v>
-      </c>
-      <c r="I66" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.01</v>
+      </c>
+      <c r="I66" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.649</v>
+        <v>6.56</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.613</v>
+        <v>6.863</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3483,39 +3483,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>5115</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>ALAM</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>6.22</v>
-      </c>
-      <c r="E67" s="17" t="n">
-        <v>-0.0386</v>
+        <v>0.23</v>
+      </c>
+      <c r="E67" s="10" t="n">
+        <v>0.15</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>3026800</v>
+        <v>3249100</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.77</v>
+        <v>5.85</v>
       </c>
       <c r="H67" t="n">
-        <v>26.01</v>
-      </c>
-      <c r="I67" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.99</v>
+      </c>
+      <c r="I67" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>6.56</v>
+        <v>0.225</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>6.863</v>
+        <v>0.242</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3528,39 +3528,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.925</v>
+        <v>0.37</v>
       </c>
       <c r="E68" s="17" t="n">
-        <v>-0.0054</v>
+        <v>0</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>3010400</v>
+        <v>3235700</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.58</v>
+        <v>0.48</v>
       </c>
       <c r="H68" t="n">
-        <v>61.73</v>
-      </c>
-      <c r="I68" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.59</v>
+      </c>
+      <c r="I68" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.903</v>
+        <v>0.367</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.86</v>
+        <v>0.368</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3573,39 +3573,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0348</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CLITE</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>0.245</v>
+        <v>0.525</v>
       </c>
       <c r="E69" s="17" t="n">
-        <v>-0.0392</v>
+        <v>0</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>2905600</v>
+        <v>3175600</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>1.79</v>
+        <v>0.19</v>
       </c>
       <c r="H69" t="n">
-        <v>63.48</v>
-      </c>
-      <c r="I69" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.7</v>
+      </c>
+      <c r="I69" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>0.228</v>
+        <v>0.51</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>0.199</v>
+        <v>0.432</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3618,39 +3618,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.37</v>
+        <v>0.92</v>
       </c>
       <c r="E70" s="15" t="n">
-        <v>0</v>
+        <v>-0.0108</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>2763700</v>
+        <v>3135500</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.41</v>
+        <v>0.61</v>
       </c>
       <c r="H70" t="n">
-        <v>53.59</v>
-      </c>
-      <c r="I70" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.61</v>
+      </c>
+      <c r="I70" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.367</v>
+        <v>0.903</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.368</v>
+        <v>0.86</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3663,28 +3663,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>UNISEM</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.53</v>
+        <v>4.48</v>
       </c>
       <c r="E71" s="10" t="n">
-        <v>0.0095</v>
+        <v>0.0228</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>2660800</v>
+        <v>3064400</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.16</v>
+        <v>1.14</v>
       </c>
       <c r="H71" t="n">
-        <v>57.54</v>
+        <v>54.95</v>
       </c>
       <c r="I71" s="16" t="inlineStr">
         <is>
@@ -3692,10 +3692,10 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.51</v>
+        <v>4.353</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.432</v>
+        <v>4.37</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3708,39 +3708,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>2.79</v>
+        <v>2.95</v>
       </c>
       <c r="E72" s="10" t="n">
-        <v>0.0109</v>
+        <v>0.0137</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>2468400</v>
+        <v>3062400</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.18</v>
+        <v>0.31</v>
       </c>
       <c r="H72" t="n">
-        <v>52.64</v>
-      </c>
-      <c r="I72" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.14</v>
+      </c>
+      <c r="I72" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>2.786</v>
+        <v>2.769</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>2.689</v>
+        <v>2.582</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3753,28 +3753,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>AXTERIA</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E73" s="17" t="n">
-        <v>-0.011</v>
+        <v>0.115</v>
+      </c>
+      <c r="E73" s="10" t="n">
+        <v>0.0455</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>2438100</v>
+        <v>3047800</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.38</v>
+        <v>9.83</v>
       </c>
       <c r="H73" t="n">
-        <v>60.94</v>
+        <v>53.59</v>
       </c>
       <c r="I73" s="13" t="inlineStr">
         <is>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.42</v>
+        <v>0.111</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.41</v>
+        <v>0.12</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3798,28 +3798,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0348</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>CLITE</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="E74" s="10" t="n">
-        <v>0.0172</v>
+        <v>0.245</v>
+      </c>
+      <c r="E74" s="15" t="n">
+        <v>-0.0392</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>2409600</v>
+        <v>3000600</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.24</v>
+        <v>1.84</v>
       </c>
       <c r="H74" t="n">
-        <v>63.53</v>
+        <v>63.48</v>
       </c>
       <c r="I74" s="13" t="inlineStr">
         <is>
@@ -3827,10 +3827,10 @@
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>2.77</v>
+        <v>0.228</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>2.582</v>
+        <v>0.199</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3843,39 +3843,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="E75" s="10" t="n">
-        <v>0.0108</v>
+        <v>0.0181</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>2384100</v>
+        <v>2814100</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.44</v>
+        <v>0.21</v>
       </c>
       <c r="H75" t="n">
-        <v>71.17</v>
-      </c>
-      <c r="I75" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.41</v>
+      </c>
+      <c r="I75" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>2.615</v>
+        <v>2.788</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>2.571</v>
+        <v>2.689</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3888,39 +3888,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.785</v>
+        <v>5.57</v>
       </c>
       <c r="E76" s="15" t="n">
-        <v>0</v>
+        <v>-0.0018</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>2334300</v>
+        <v>2807500</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>1.42</v>
+        <v>0.2</v>
       </c>
       <c r="H76" t="n">
-        <v>69.20999999999999</v>
-      </c>
-      <c r="I76" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.96</v>
+      </c>
+      <c r="I76" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.699</v>
+        <v>5.651</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.6860000000000001</v>
+        <v>5.304</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3933,39 +3933,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E77" s="17" t="n">
-        <v>-0.0426</v>
+        <v>0.45</v>
+      </c>
+      <c r="E77" s="15" t="n">
+        <v>-0.011</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>2279800</v>
+        <v>2603100</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.08</v>
+        <v>0.41</v>
       </c>
       <c r="H77" t="n">
-        <v>31.32</v>
-      </c>
-      <c r="I77" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.94</v>
+      </c>
+      <c r="I77" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.255</v>
+        <v>0.42</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.308</v>
+        <v>0.41</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3978,28 +3978,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>1.45</v>
+        <v>2.81</v>
       </c>
       <c r="E78" s="10" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.0072</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>2274000</v>
+        <v>2561600</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.73</v>
+        <v>0.47</v>
       </c>
       <c r="H78" t="n">
-        <v>81.55</v>
+        <v>70.64</v>
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
@@ -4007,10 +4007,10 @@
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>1.21</v>
+        <v>2.614</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0.986</v>
+        <v>2.571</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4023,28 +4023,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0249</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>LGMS</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E79" s="17" t="n">
-        <v>-0.0175</v>
+        <v>1.43</v>
+      </c>
+      <c r="E79" s="10" t="n">
+        <v>0.0515</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>2214300</v>
+        <v>2551200</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>3.29</v>
+        <v>0.82</v>
       </c>
       <c r="H79" t="n">
-        <v>69.91</v>
+        <v>80.78</v>
       </c>
       <c r="I79" s="13" t="inlineStr">
         <is>
@@ -4052,10 +4052,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.513</v>
+        <v>1.208</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.501</v>
+        <v>0.985</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4068,28 +4068,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>CLOUDPT</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E80" s="17" t="n">
-        <v>-0.0242</v>
+        <v>0.52</v>
+      </c>
+      <c r="E80" s="10" t="n">
+        <v>0.04</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>2178100</v>
+        <v>2510900</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.71</v>
       </c>
       <c r="H80" t="n">
-        <v>78.95999999999999</v>
+        <v>63.95</v>
       </c>
       <c r="I80" s="13" t="inlineStr">
         <is>
@@ -4097,10 +4097,10 @@
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.582</v>
+        <v>0.486</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.455</v>
+        <v>0.477</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4113,39 +4113,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E81" s="17" t="n">
-        <v>-0.0185</v>
+        <v>3.49</v>
+      </c>
+      <c r="E81" s="10" t="n">
+        <v>0.064</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>2080300</v>
+        <v>2506800</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.57</v>
+        <v>0.86</v>
       </c>
       <c r="H81" t="n">
-        <v>31.86</v>
-      </c>
-      <c r="I81" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.95999999999999</v>
+      </c>
+      <c r="I81" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>0.556</v>
+        <v>2.961</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>0.585</v>
+        <v>2.782</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4158,39 +4158,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>GASMSIA</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>5.18</v>
-      </c>
-      <c r="E82" s="10" t="n">
-        <v>0.0177</v>
+        <v>0.225</v>
+      </c>
+      <c r="E82" s="15" t="n">
+        <v>-0.0426</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>2077900</v>
+        <v>2437400</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>2.57</v>
+        <v>0.09</v>
       </c>
       <c r="H82" t="n">
-        <v>61.77</v>
-      </c>
-      <c r="I82" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.32</v>
+      </c>
+      <c r="I82" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>4.998</v>
+        <v>0.255</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>5.026</v>
+        <v>0.308</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4203,28 +4203,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.33</v>
+        <v>0.625</v>
       </c>
       <c r="E83" s="15" t="n">
-        <v>0</v>
+        <v>-0.0385</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>2074200</v>
+        <v>2410900</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.4</v>
+        <v>0.63</v>
       </c>
       <c r="H83" t="n">
-        <v>53.33</v>
+        <v>52.83</v>
       </c>
       <c r="I83" s="13" t="inlineStr">
         <is>
@@ -4232,10 +4232,10 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>0.323</v>
+        <v>0.615</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.339</v>
+        <v>0.609</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4259,14 +4259,14 @@
       <c r="D84" s="9" t="n">
         <v>6.06</v>
       </c>
-      <c r="E84" s="17" t="n">
+      <c r="E84" s="15" t="n">
         <v>-0.0098</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>2060700</v>
+        <v>2404400</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="H84" t="n">
         <v>39.03</v>
@@ -4293,28 +4293,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="E85" s="17" t="n">
-        <v>-0.005</v>
+        <v>0.735</v>
+      </c>
+      <c r="E85" s="15" t="n">
+        <v>-0.0068</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>2044500</v>
+        <v>2401800</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.88</v>
+        <v>0.42</v>
       </c>
       <c r="H85" t="n">
-        <v>27.67</v>
+        <v>35.77</v>
       </c>
       <c r="I85" s="16" t="inlineStr">
         <is>
@@ -4322,10 +4322,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>1.064</v>
+        <v>0.765</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>1.13</v>
+        <v>0.824</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4338,39 +4338,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>5.56</v>
-      </c>
-      <c r="E86" s="17" t="n">
-        <v>-0.0036</v>
+        <v>0.79</v>
+      </c>
+      <c r="E86" s="10" t="n">
+        <v>0.0064</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>1930800</v>
+        <v>2385700</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.13</v>
+        <v>1.45</v>
       </c>
       <c r="H86" t="n">
-        <v>48.54</v>
-      </c>
-      <c r="I86" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.79000000000001</v>
+      </c>
+      <c r="I86" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>5.65</v>
+        <v>0.699</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>5.304</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4383,39 +4383,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="E87" s="17" t="n">
-        <v>-0.0064</v>
+        <v>1.76</v>
+      </c>
+      <c r="E87" s="10" t="n">
+        <v>0.0115</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1923200</v>
+        <v>2384700</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="H87" t="n">
-        <v>72.92</v>
-      </c>
-      <c r="I87" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.13</v>
+      </c>
+      <c r="I87" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>2.622</v>
+        <v>1.753</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>1.985</v>
+        <v>1.782</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4428,28 +4428,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0249</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>LGMS</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>2.74</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="E88" s="15" t="n">
-        <v>0</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>1906100</v>
+        <v>2357100</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.58</v>
+        <v>3.5</v>
       </c>
       <c r="H88" t="n">
-        <v>70.12</v>
+        <v>72.5</v>
       </c>
       <c r="I88" s="13" t="inlineStr">
         <is>
@@ -4457,10 +4457,10 @@
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>2.591</v>
+        <v>0.513</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>2.251</v>
+        <v>0.501</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4473,39 +4473,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E89" s="10" t="n">
-        <v>0.033</v>
+        <v>1.14</v>
+      </c>
+      <c r="E89" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1892700</v>
+        <v>2352600</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.61</v>
+        <v>0.38</v>
       </c>
       <c r="H89" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="I89" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.85</v>
+      </c>
+      <c r="I89" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>0.407</v>
+        <v>1.15</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0.362</v>
+        <v>1.164</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4518,39 +4518,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="E90" s="10" t="n">
-        <v>0.0231</v>
+        <v>0.535</v>
+      </c>
+      <c r="E90" s="15" t="n">
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>1883600</v>
+        <v>2240200</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>1.23</v>
+        <v>0.62</v>
       </c>
       <c r="H90" t="n">
-        <v>63.95</v>
-      </c>
-      <c r="I90" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.64</v>
+      </c>
+      <c r="I90" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>1.657</v>
+        <v>0.556</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>1.679</v>
+        <v>0.585</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4563,39 +4563,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>4.64</v>
+        <v>0.33</v>
       </c>
       <c r="E91" s="17" t="n">
-        <v>-0.0064</v>
+        <v>0</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1819700</v>
+        <v>2236400</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.19</v>
+        <v>0.43</v>
       </c>
       <c r="H91" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="I91" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.33</v>
+      </c>
+      <c r="I91" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>4.702</v>
+        <v>0.323</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>4.624</v>
+        <v>0.339</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4608,28 +4608,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E92" s="17" t="n">
-        <v>-0.0135</v>
+        <v>0.99</v>
+      </c>
+      <c r="E92" s="15" t="n">
+        <v>-0.005</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1794100</v>
+        <v>2224300</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.32</v>
+        <v>0.95</v>
       </c>
       <c r="H92" t="n">
-        <v>34.7</v>
+        <v>27.67</v>
       </c>
       <c r="I92" s="16" t="inlineStr">
         <is>
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>0.764</v>
+        <v>1.064</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>0.824</v>
+        <v>1.13</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4653,28 +4653,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0291</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CHB</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E93" s="10" t="n">
-        <v>0.0595</v>
+        <v>0.8</v>
+      </c>
+      <c r="E93" s="15" t="n">
+        <v>-0.0303</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1783800</v>
+        <v>2211300</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>1.14</v>
+        <v>0.82</v>
       </c>
       <c r="H93" t="n">
-        <v>80.68000000000001</v>
+        <v>78.12</v>
       </c>
       <c r="I93" s="13" t="inlineStr">
         <is>
@@ -4682,10 +4682,10 @@
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>2.39</v>
+        <v>0.582</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>2.122</v>
+        <v>0.455</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4698,28 +4698,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>5209</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>GASMSIA</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E94" s="15" t="n">
-        <v>0</v>
+        <v>5.2</v>
+      </c>
+      <c r="E94" s="10" t="n">
+        <v>0.0216</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1739100</v>
+        <v>2156000</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.15</v>
+        <v>2.67</v>
       </c>
       <c r="H94" t="n">
-        <v>74.43000000000001</v>
+        <v>62.68</v>
       </c>
       <c r="I94" s="13" t="inlineStr">
         <is>
@@ -4727,10 +4727,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>1.064</v>
+        <v>5</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.904</v>
+        <v>5.026</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4743,39 +4743,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E95" s="17" t="n">
-        <v>-0.0231</v>
+        <v>0.495</v>
+      </c>
+      <c r="E95" s="15" t="n">
+        <v>-0.01</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1729900</v>
+        <v>2129200</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="H95" t="n">
-        <v>55.38</v>
-      </c>
-      <c r="I95" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.4</v>
+      </c>
+      <c r="I95" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>0.616</v>
+        <v>0.532</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>0.609</v>
+        <v>0.575</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4788,28 +4788,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ALPHA</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E96" s="17" t="n">
-        <v>-0.0351</v>
+        <v>0.47</v>
+      </c>
+      <c r="E96" s="10" t="n">
+        <v>0.033</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1721000</v>
+        <v>2064500</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.8</v>
+        <v>0.66</v>
       </c>
       <c r="H96" t="n">
-        <v>64.26000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="I96" s="13" t="inlineStr">
         <is>
@@ -4817,10 +4817,10 @@
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.255</v>
+        <v>0.407</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.257</v>
+        <v>0.362</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4833,28 +4833,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>MFLOUR</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E97" s="10" t="n">
-        <v>0.0192</v>
+        <v>0.6</v>
+      </c>
+      <c r="E97" s="15" t="n">
+        <v>-0.0164</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1702600</v>
+        <v>2000900</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>1.81</v>
+        <v>0.91</v>
       </c>
       <c r="H97" t="n">
-        <v>57.12</v>
+        <v>36.4</v>
       </c>
       <c r="I97" s="16" t="inlineStr">
         <is>
@@ -4862,10 +4862,10 @@
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>0.261</v>
+        <v>0.622</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0.264</v>
+        <v>0.638</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4878,28 +4878,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>0291</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>CHB</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>0.51</v>
+        <v>2.89</v>
       </c>
       <c r="E98" s="10" t="n">
-        <v>0.02</v>
+        <v>0.07429999999999999</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1692400</v>
+        <v>2000300</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="H98" t="n">
-        <v>61.29</v>
+        <v>81.48</v>
       </c>
       <c r="I98" s="13" t="inlineStr">
         <is>
@@ -4907,10 +4907,10 @@
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>0.485</v>
+        <v>2.394</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>0.476</v>
+        <v>2.123</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4923,39 +4923,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>1.37</v>
+        <v>3.1</v>
       </c>
       <c r="E99" s="15" t="n">
-        <v>0</v>
+        <v>-0.0064</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1687500</v>
+        <v>1995000</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.89</v>
+        <v>0.5</v>
       </c>
       <c r="H99" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="I99" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>72.92</v>
+      </c>
+      <c r="I99" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>1.369</v>
+        <v>2.622</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>1.334</v>
+        <v>1.985</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4968,39 +4968,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E100" s="15" t="n">
-        <v>0</v>
+        <v>2.75</v>
+      </c>
+      <c r="E100" s="10" t="n">
+        <v>0.0036</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1649800</v>
+        <v>1940400</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.41</v>
+        <v>0.59</v>
       </c>
       <c r="H100" t="n">
-        <v>69.5</v>
-      </c>
-      <c r="I100" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.62</v>
+      </c>
+      <c r="I100" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>0.246</v>
+        <v>2.591</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>0.217</v>
+        <v>2.251</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -5013,28 +5013,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0399</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>AMS</t>
+          <t>VSTECS</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0.485</v>
+        <v>1.76</v>
       </c>
       <c r="E101" s="10" t="n">
-        <v>0.0104</v>
+        <v>0.0173</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1596100</v>
+        <v>1928600</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.8</v>
+        <v>1.26</v>
       </c>
       <c r="H101" t="n">
-        <v>60.97</v>
+        <v>63.09</v>
       </c>
       <c r="I101" s="13" t="inlineStr">
         <is>
@@ -5042,10 +5042,10 @@
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>0.458</v>
+        <v>1.656</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>0.461</v>
+        <v>1.678</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5058,28 +5058,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>0.52</v>
+        <v>1.15</v>
       </c>
       <c r="E102" s="17" t="n">
-        <v>-0.0095</v>
+        <v>0</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1593500</v>
+        <v>1918100</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.41</v>
+        <v>0.17</v>
       </c>
       <c r="H102" t="n">
-        <v>69.04000000000001</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="I102" s="13" t="inlineStr">
         <is>
@@ -5087,10 +5087,10 @@
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>0.462</v>
+        <v>1.064</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>0.447</v>
+        <v>0.904</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5103,39 +5103,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="E103" s="10" t="n">
-        <v>0.04269999999999999</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E103" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1581500</v>
+        <v>1868900</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.54</v>
+        <v>0.84</v>
       </c>
       <c r="H103" t="n">
-        <v>74.48999999999999</v>
-      </c>
-      <c r="I103" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.46</v>
+      </c>
+      <c r="I103" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>2.954</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>2.78</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5148,28 +5148,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="E104" s="17" t="n">
-        <v>-0.02</v>
+        <v>4.61</v>
+      </c>
+      <c r="E104" s="15" t="n">
+        <v>-0.0128</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1497700</v>
+        <v>1850100</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="H104" t="n">
-        <v>26.23</v>
+        <v>42.86</v>
       </c>
       <c r="I104" s="16" t="inlineStr">
         <is>
@@ -5177,10 +5177,10 @@
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>0.532</v>
+        <v>4.7</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0.575</v>
+        <v>4.624</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5193,39 +5193,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.33</v>
+        <v>5.94</v>
       </c>
       <c r="E105" s="15" t="n">
-        <v>0</v>
+        <v>-0.023</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1486800</v>
+        <v>1824100</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.24</v>
+        <v>0.54</v>
       </c>
       <c r="H105" t="n">
-        <v>31.86</v>
-      </c>
-      <c r="I105" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.11</v>
+      </c>
+      <c r="I105" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>0.342</v>
+        <v>5.385</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0.346</v>
+        <v>5.328</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5238,39 +5238,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>5127</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>ARREIT</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.39</v>
+        <v>1.38</v>
       </c>
       <c r="E106" s="10" t="n">
-        <v>0.0263</v>
+        <v>0.0073</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1441200</v>
+        <v>1806900</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>7.87</v>
+        <v>0.95</v>
       </c>
       <c r="H106" t="n">
-        <v>67.43000000000001</v>
-      </c>
-      <c r="I106" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.14</v>
+      </c>
+      <c r="I106" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>0.369</v>
+        <v>1.37</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>0.372</v>
+        <v>1.335</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5283,38 +5283,40 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>0399</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E107" s="15" t="n">
-        <v>0</v>
+        <v>0.485</v>
+      </c>
+      <c r="E107" s="10" t="n">
+        <v>0.0104</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1377300</v>
+        <v>1796000</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.09</v>
+        <v>0.89</v>
       </c>
       <c r="H107" t="n">
-        <v>18.18</v>
-      </c>
-      <c r="I107" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.97</v>
+      </c>
+      <c r="I107" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="K107" s="9" t="n"/>
+        <v>0.458</v>
+      </c>
+      <c r="K107" s="9" t="n">
+        <v>0.461</v>
+      </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
     </row>
@@ -5326,28 +5328,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.355</v>
+        <v>0.465</v>
       </c>
       <c r="E108" s="15" t="n">
-        <v>0</v>
+        <v>-0.0211</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1346000</v>
+        <v>1785000</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.36</v>
+        <v>0.54</v>
       </c>
       <c r="H108" t="n">
-        <v>38.26</v>
+        <v>56.06</v>
       </c>
       <c r="I108" s="16" t="inlineStr">
         <is>
@@ -5355,10 +5357,10 @@
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>0.368</v>
+        <v>0.46</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>0.386</v>
+        <v>0.419</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5371,28 +5373,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E109" s="17" t="n">
-        <v>-0.0132</v>
+        <v>0.645</v>
+      </c>
+      <c r="E109" s="10" t="n">
+        <v>0.0238</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1335100</v>
+        <v>1738700</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.16</v>
+        <v>0.47</v>
       </c>
       <c r="H109" t="n">
-        <v>68.06</v>
+        <v>87.43000000000001</v>
       </c>
       <c r="I109" s="13" t="inlineStr">
         <is>
@@ -5400,10 +5402,10 @@
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>0.349</v>
+        <v>0.483</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>0.318</v>
+        <v>0.433</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5416,39 +5418,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>MFLOUR</t>
+          <t>ALPHA</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E110" s="17" t="n">
-        <v>-0.008199999999999999</v>
+        <v>0.275</v>
+      </c>
+      <c r="E110" s="15" t="n">
+        <v>-0.0351</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1330000</v>
+        <v>1721000</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.61</v>
+        <v>0.8</v>
       </c>
       <c r="H110" t="n">
-        <v>38.29</v>
-      </c>
-      <c r="I110" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.26000000000001</v>
+      </c>
+      <c r="I110" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>0.623</v>
+        <v>0.255</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>0.638</v>
+        <v>0.257</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5461,28 +5463,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E111" s="17" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.265</v>
+      </c>
+      <c r="E111" s="10" t="n">
+        <v>0.0192</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1327300</v>
+        <v>1702600</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.21</v>
+        <v>1.81</v>
       </c>
       <c r="H111" t="n">
-        <v>46.42</v>
+        <v>57.12</v>
       </c>
       <c r="I111" s="16" t="inlineStr">
         <is>
@@ -5490,10 +5492,10 @@
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>1.149</v>
+        <v>0.261</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>1.164</v>
+        <v>0.264</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5506,39 +5508,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="E112" s="17" t="n">
-        <v>-0.0329</v>
+        <v>1.82</v>
+      </c>
+      <c r="E112" s="15" t="n">
+        <v>-0.0109</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>1318400</v>
+        <v>1687700</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="H112" t="n">
-        <v>63.31</v>
-      </c>
-      <c r="I112" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.93</v>
+      </c>
+      <c r="I112" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>5.379</v>
+        <v>1.908</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>5.327</v>
+        <v>2.035</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5551,36 +5553,40 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E113" s="17" t="n">
-        <v>-0.0357</v>
+        <v>0.615</v>
+      </c>
+      <c r="E113" s="10" t="n">
+        <v>0.008199999999999999</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>1311200</v>
+        <v>1664100</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H113" t="n">
-        <v>31.12</v>
+        <v>58.78</v>
       </c>
       <c r="I113" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J113" s="9" t="n"/>
-      <c r="K113" s="9" t="n"/>
+      <c r="J113" s="9" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="K113" s="9" t="n">
+        <v>0.597</v>
+      </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
     </row>
@@ -5592,28 +5598,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>3417</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>E&amp;O</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="E114" s="17" t="n">
-        <v>-0.013</v>
+        <v>0.325</v>
+      </c>
+      <c r="E114" s="15" t="n">
+        <v>-0.0152</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>1304100</v>
+        <v>1662500</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.91</v>
+        <v>0.27</v>
       </c>
       <c r="H114" t="n">
-        <v>44.8</v>
+        <v>28.35</v>
       </c>
       <c r="I114" s="16" t="inlineStr">
         <is>
@@ -5621,10 +5627,10 @@
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>0.771</v>
+        <v>0.341</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>0.767</v>
+        <v>0.346</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5637,39 +5643,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0337</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>0.24</v>
+        <v>0.52</v>
       </c>
       <c r="E115" s="15" t="n">
-        <v>0</v>
+        <v>-0.0095</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>1297400</v>
+        <v>1661800</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.74</v>
+        <v>0.43</v>
       </c>
       <c r="H115" t="n">
-        <v>52.31</v>
-      </c>
-      <c r="I115" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.04000000000001</v>
+      </c>
+      <c r="I115" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>0.236</v>
+        <v>0.462</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>0.243</v>
+        <v>0.447</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5682,28 +5688,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0172</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>OCK</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E116" s="15" t="n">
-        <v>0</v>
+        <v>2.49</v>
+      </c>
+      <c r="E116" s="10" t="n">
+        <v>0.004</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>1282200</v>
+        <v>1661000</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.39</v>
+        <v>0.11</v>
       </c>
       <c r="H116" t="n">
-        <v>61.26</v>
+        <v>57.34</v>
       </c>
       <c r="I116" s="16" t="inlineStr">
         <is>
@@ -5711,10 +5717,10 @@
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>0.461</v>
+        <v>2.459</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>0.419</v>
+        <v>2.342</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5727,28 +5733,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="E117" s="10" t="n">
-        <v>0.0146</v>
+        <v>0.275</v>
+      </c>
+      <c r="E117" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>1264900</v>
+        <v>1649800</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.47</v>
+        <v>0.41</v>
       </c>
       <c r="H117" t="n">
-        <v>57.34</v>
+        <v>69.5</v>
       </c>
       <c r="I117" s="16" t="inlineStr">
         <is>
@@ -5756,10 +5762,10 @@
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>1.358</v>
+        <v>0.246</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>1.223</v>
+        <v>0.217</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5772,39 +5778,39 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>1.83</v>
+        <v>1.2</v>
       </c>
       <c r="E118" s="17" t="n">
-        <v>-0.0054</v>
+        <v>0</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>1264700</v>
+        <v>1550700</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.28</v>
+        <v>0.36</v>
       </c>
       <c r="H118" t="n">
-        <v>31.91</v>
-      </c>
-      <c r="I118" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.7</v>
+      </c>
+      <c r="I118" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>1.909</v>
+        <v>1.148</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>2.036</v>
+        <v>1.057</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5817,39 +5823,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>2.48</v>
+        <v>0.37</v>
       </c>
       <c r="E119" s="15" t="n">
-        <v>0</v>
+        <v>-0.0263</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>1259000</v>
+        <v>1525200</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="H119" t="n">
-        <v>56.21</v>
-      </c>
-      <c r="I119" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.84999999999999</v>
+      </c>
+      <c r="I119" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>2.458</v>
+        <v>0.348</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>2.342</v>
+        <v>0.318</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5862,39 +5868,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E120" s="17" t="n">
-        <v>-0.0128</v>
+        <v>1.64</v>
+      </c>
+      <c r="E120" s="10" t="n">
+        <v>0.0061</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>1254100</v>
+        <v>1491700</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.41</v>
+        <v>0.22</v>
       </c>
       <c r="H120" t="n">
-        <v>51.63</v>
-      </c>
-      <c r="I120" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.15</v>
+      </c>
+      <c r="I120" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>0.767</v>
+        <v>1.684</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>0.746</v>
+        <v>1.798</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5907,39 +5913,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="E121" s="10" t="n">
-        <v>0.0115</v>
+        <v>0.775</v>
+      </c>
+      <c r="E121" s="15" t="n">
+        <v>-0.0064</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>1222500</v>
+        <v>1478700</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.24</v>
+        <v>0.49</v>
       </c>
       <c r="H121" t="n">
-        <v>50.13</v>
-      </c>
-      <c r="I121" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.74</v>
+      </c>
+      <c r="I121" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>1.753</v>
+        <v>0.767</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>1.782</v>
+        <v>0.746</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5952,28 +5958,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>FFB</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="E122" s="17" t="n">
-        <v>-0.0068</v>
+        <v>1.79</v>
+      </c>
+      <c r="E122" s="15" t="n">
+        <v>-0.005600000000000001</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>1203300</v>
+        <v>1478500</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.24</v>
+        <v>0.53</v>
       </c>
       <c r="H122" t="n">
-        <v>44.42</v>
+        <v>24.01</v>
       </c>
       <c r="I122" s="16" t="inlineStr">
         <is>
@@ -5981,10 +5987,10 @@
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>1.465</v>
+        <v>1.904</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>1.469</v>
+        <v>2.032</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -5997,39 +6003,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>5127</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>ARREIT</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="E123" s="15" t="n">
-        <v>0</v>
+        <v>0.39</v>
+      </c>
+      <c r="E123" s="10" t="n">
+        <v>0.0263</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>1198100</v>
+        <v>1441200</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.18</v>
+        <v>7.87</v>
       </c>
       <c r="H123" t="n">
-        <v>37.31</v>
-      </c>
-      <c r="I123" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.43000000000001</v>
+      </c>
+      <c r="I123" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>1.683</v>
+        <v>0.369</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>1.798</v>
+        <v>0.372</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6042,28 +6048,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>1.42</v>
+        <v>12.96</v>
       </c>
       <c r="E124" s="10" t="n">
-        <v>0.0365</v>
+        <v>0.004699999999999999</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1194400</v>
+        <v>1432000</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.29</v>
+        <v>0.17</v>
       </c>
       <c r="H124" t="n">
-        <v>65.15000000000001</v>
+        <v>41.33</v>
       </c>
       <c r="I124" s="13" t="inlineStr">
         <is>
@@ -6071,10 +6077,10 @@
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>1.286</v>
+        <v>13.066</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>1.185</v>
+        <v>13.615</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6087,39 +6093,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E125" s="10" t="n">
-        <v>0.0159</v>
+        <v>1.37</v>
+      </c>
+      <c r="E125" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>1190200</v>
+        <v>1396600</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.32</v>
+        <v>0.52</v>
       </c>
       <c r="H125" t="n">
-        <v>87.18000000000001</v>
-      </c>
-      <c r="I125" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.2</v>
+      </c>
+      <c r="I125" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>0.482</v>
+        <v>1.356</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>0.433</v>
+        <v>1.222</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6132,32 +6138,37 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0475</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>GBBOND</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E126" s="15" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="E126" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>1149600</v>
+        <v>1381100</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
+      </c>
+      <c r="H126" t="n">
+        <v>18.18</v>
       </c>
       <c r="I126" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J126" s="9" t="n"/>
+      <c r="J126" s="9" t="n">
+        <v>0.293</v>
+      </c>
       <c r="K126" s="9" t="n"/>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6170,28 +6181,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E127" s="17" t="n">
-        <v>-0.0064</v>
+        <v>4.31</v>
+      </c>
+      <c r="E127" s="15" t="n">
+        <v>-0.0137</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>1133700</v>
+        <v>1371100</v>
       </c>
       <c r="G127" s="12" t="n">
         <v>0.16</v>
       </c>
       <c r="H127" t="n">
-        <v>67.56999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="I127" s="13" t="inlineStr">
         <is>
@@ -6199,10 +6210,10 @@
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>0.719</v>
+        <v>3.921</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>0.642</v>
+        <v>3.398</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6215,39 +6226,39 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>4.31</v>
+        <v>0.355</v>
       </c>
       <c r="E128" s="17" t="n">
-        <v>-0.0137</v>
+        <v>0</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>1128800</v>
+        <v>1371000</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.13</v>
+        <v>0.37</v>
       </c>
       <c r="H128" t="n">
-        <v>69.2</v>
-      </c>
-      <c r="I128" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.26</v>
+      </c>
+      <c r="I128" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>3.921</v>
+        <v>0.368</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>3.398</v>
+        <v>0.386</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6260,28 +6271,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E129" s="17" t="n">
-        <v>-0.0083</v>
+        <v>3.12</v>
+      </c>
+      <c r="E129" s="15" t="n">
+        <v>-0.0032</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>1080200</v>
+        <v>1350700</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="H129" t="n">
-        <v>63.19</v>
+        <v>59.87</v>
       </c>
       <c r="I129" s="13" t="inlineStr">
         <is>
@@ -6289,10 +6300,10 @@
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>1.147</v>
+        <v>2.985</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>1.057</v>
+        <v>2.805</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6305,40 +6316,36 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E130" s="17" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.265</v>
+      </c>
+      <c r="E130" s="15" t="n">
+        <v>-0.0536</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>1078000</v>
+        <v>1319100</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.35</v>
+        <v>0.11</v>
       </c>
       <c r="H130" t="n">
-        <v>53.32</v>
-      </c>
-      <c r="I130" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J130" s="9" t="n">
-        <v>0.864</v>
-      </c>
-      <c r="K130" s="9" t="n">
-        <v>0.858</v>
-      </c>
+        <v>30.32</v>
+      </c>
+      <c r="I130" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J130" s="9" t="n"/>
+      <c r="K130" s="9" t="n"/>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
     </row>
@@ -6350,28 +6357,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>E&amp;O</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>0.415</v>
+        <v>0.765</v>
       </c>
       <c r="E131" s="15" t="n">
-        <v>0</v>
+        <v>-0.006500000000000001</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1061800</v>
+        <v>1314900</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="H131" t="n">
-        <v>39.02</v>
+        <v>47.11</v>
       </c>
       <c r="I131" s="16" t="inlineStr">
         <is>
@@ -6379,10 +6386,10 @@
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>0.424</v>
+        <v>0.771</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>0.443</v>
+        <v>0.768</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6395,28 +6402,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>HEXRTL</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E132" s="10" t="n">
-        <v>0.0959</v>
+        <v>0.785</v>
+      </c>
+      <c r="E132" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1002700</v>
+        <v>1300900</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>3.08</v>
+        <v>0.18</v>
       </c>
       <c r="H132" t="n">
-        <v>45.96</v>
+        <v>68.98</v>
       </c>
       <c r="I132" s="13" t="inlineStr">
         <is>
@@ -6424,10 +6431,10 @@
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>0.406</v>
+        <v>0.72</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>0.411</v>
+        <v>0.642</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6440,28 +6447,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>2.51</v>
+        <v>0.24</v>
       </c>
       <c r="E133" s="17" t="n">
-        <v>-0.0233</v>
+        <v>0</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>997700</v>
+        <v>1297400</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.15</v>
+        <v>0.74</v>
       </c>
       <c r="H133" t="n">
-        <v>34.18</v>
+        <v>52.31</v>
       </c>
       <c r="I133" s="16" t="inlineStr">
         <is>
@@ -6469,10 +6476,10 @@
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>2.633</v>
+        <v>0.236</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>2.799</v>
+        <v>0.243</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6485,28 +6492,28 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="E134" s="17" t="n">
-        <v>-0.0313</v>
+        <v>1.43</v>
+      </c>
+      <c r="E134" s="10" t="n">
+        <v>0.0438</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>986400</v>
+        <v>1274100</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.13</v>
+        <v>0.31</v>
       </c>
       <c r="H134" t="n">
-        <v>72.16</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="I134" s="13" t="inlineStr">
         <is>
@@ -6514,10 +6521,10 @@
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>1.059</v>
+        <v>1.287</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.185</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6530,28 +6537,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>4.31</v>
+        <v>1.89</v>
       </c>
       <c r="E135" s="10" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.0107</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>985500</v>
+        <v>1252100</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="H135" t="n">
-        <v>28.42</v>
+        <v>41.41</v>
       </c>
       <c r="I135" s="16" t="inlineStr">
         <is>
@@ -6559,10 +6566,10 @@
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>4.524</v>
+        <v>1.934</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>4.871</v>
+        <v>1.96</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6575,39 +6582,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>12.92</v>
-      </c>
-      <c r="E136" s="10" t="n">
-        <v>0.0016</v>
+        <v>1.45</v>
+      </c>
+      <c r="E136" s="15" t="n">
+        <v>-0.0068</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>961900</v>
+        <v>1238400</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.11</v>
+        <v>0.24</v>
       </c>
       <c r="H136" t="n">
-        <v>39.45</v>
-      </c>
-      <c r="I136" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.42</v>
+      </c>
+      <c r="I136" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>13.062</v>
+        <v>1.465</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>13.615</v>
+        <v>1.469</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6620,40 +6627,33 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>0475</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>FFB</t>
+          <t>GBBOND</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="E137" s="17" t="n">
-        <v>-0.005600000000000001</v>
+        <v>0.23</v>
+      </c>
+      <c r="E137" s="10" t="n">
+        <v>0.0222</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>934800</v>
+        <v>1195400</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="H137" t="n">
-        <v>24.01</v>
+        <v>0.04</v>
       </c>
       <c r="I137" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J137" s="9" t="n">
-        <v>1.904</v>
-      </c>
-      <c r="K137" s="9" t="n">
-        <v>2.032</v>
-      </c>
+      <c r="J137" s="9" t="n"/>
+      <c r="K137" s="9" t="n"/>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
     </row>
@@ -6665,39 +6665,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="E138" s="17" t="n">
-        <v>-0.0032</v>
+        <v>2.07</v>
+      </c>
+      <c r="E138" s="10" t="n">
+        <v>0.0147</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>924700</v>
+        <v>1174800</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.21</v>
+        <v>0.38</v>
       </c>
       <c r="H138" t="n">
-        <v>59.87</v>
-      </c>
-      <c r="I138" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.02</v>
+      </c>
+      <c r="I138" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>2.985</v>
+        <v>2.054</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>2.805</v>
+        <v>2.088</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6710,28 +6710,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>OSK</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="E139" s="17" t="n">
-        <v>-0.0235</v>
+        <v>3</v>
+      </c>
+      <c r="E139" s="15" t="n">
+        <v>-0.0132</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>922000</v>
+        <v>1159100</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.67</v>
+        <v>0.39</v>
       </c>
       <c r="H139" t="n">
-        <v>21.7</v>
+        <v>50.88</v>
       </c>
       <c r="I139" s="16" t="inlineStr">
         <is>
@@ -6739,10 +6739,10 @@
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>1.82</v>
+        <v>2.986</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>1.935</v>
+        <v>3.037</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6755,28 +6755,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E140" s="17" t="n">
-        <v>-0.0132</v>
+        <v>4.3</v>
+      </c>
+      <c r="E140" s="10" t="n">
+        <v>0.0023</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>905000</v>
+        <v>1154000</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.3</v>
+        <v>0.22</v>
       </c>
       <c r="H140" t="n">
-        <v>50.88</v>
+        <v>27.41</v>
       </c>
       <c r="I140" s="16" t="inlineStr">
         <is>
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>2.986</v>
+        <v>4.523</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>3.037</v>
+        <v>4.871</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6800,39 +6800,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.44</v>
       </c>
       <c r="E141" s="10" t="n">
-        <v>0.0053</v>
+        <v>0.0141</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>891900</v>
+        <v>1146700</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.52</v>
+        <v>0.39</v>
       </c>
       <c r="H141" t="n">
-        <v>34.76</v>
-      </c>
-      <c r="I141" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>79.86</v>
+      </c>
+      <c r="I141" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>0.971</v>
+        <v>1.18</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>0.997</v>
+        <v>1.139</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6845,39 +6845,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0466</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>SRKKAI</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E142" s="17" t="n">
-        <v>-0.0185</v>
+        <v>3.33</v>
+      </c>
+      <c r="E142" s="10" t="n">
+        <v>0.003</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>883100</v>
+        <v>1135700</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>0.82</v>
+        <v>0.18</v>
       </c>
       <c r="H142" t="n">
-        <v>50.33</v>
-      </c>
-      <c r="I142" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.28</v>
+      </c>
+      <c r="I142" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>0.527</v>
+        <v>3.494</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>0.533</v>
+        <v>3.667</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6890,39 +6890,39 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>OSK</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E143" s="17" t="n">
-        <v>-0.0216</v>
+        <v>1.67</v>
+      </c>
+      <c r="E143" s="15" t="n">
+        <v>-0.0176</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>879100</v>
+        <v>1123300</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>0.4</v>
+        <v>0.82</v>
       </c>
       <c r="H143" t="n">
-        <v>69.78</v>
-      </c>
-      <c r="I143" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>22.33</v>
+      </c>
+      <c r="I143" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>0.619</v>
+        <v>1.821</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>0.523</v>
+        <v>1.935</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6935,28 +6935,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>0.995</v>
-      </c>
-      <c r="E144" s="17" t="n">
-        <v>-0.0149</v>
+        <v>2.52</v>
+      </c>
+      <c r="E144" s="15" t="n">
+        <v>-0.0195</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>865300</v>
+        <v>1119300</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>0.1</v>
+        <v>0.17</v>
       </c>
       <c r="H144" t="n">
-        <v>60.39</v>
+        <v>34.84</v>
       </c>
       <c r="I144" s="16" t="inlineStr">
         <is>
@@ -6964,10 +6964,10 @@
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>0.96</v>
+        <v>2.634</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>0.8090000000000001</v>
+        <v>2.799</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -6980,39 +6980,39 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="E145" s="15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="E145" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>864600</v>
+        <v>1114100</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>0.14</v>
+        <v>0.23</v>
       </c>
       <c r="H145" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="I145" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.57</v>
+      </c>
+      <c r="I145" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>3.493</v>
+        <v>5.042</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>3.667</v>
+        <v>5.058</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7025,28 +7025,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="E146" s="10" t="n">
-        <v>0.0052</v>
+        <v>0.465</v>
+      </c>
+      <c r="E146" s="15" t="n">
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>820500</v>
+        <v>1104200</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>0.19</v>
+        <v>1.02</v>
       </c>
       <c r="H146" t="n">
-        <v>29.5</v>
+        <v>6.4</v>
       </c>
       <c r="I146" s="16" t="inlineStr">
         <is>
@@ -7054,10 +7054,10 @@
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>1.007</v>
+        <v>0.592</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>1.075</v>
+        <v>0.626</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -7070,39 +7070,39 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="E147" s="10" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.865</v>
+      </c>
+      <c r="E147" s="15" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>819600</v>
+        <v>1078000</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>0.28</v>
+        <v>0.35</v>
       </c>
       <c r="H147" t="n">
-        <v>79.45</v>
-      </c>
-      <c r="I147" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.32</v>
+      </c>
+      <c r="I147" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>1.179</v>
+        <v>0.864</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>1.139</v>
+        <v>0.858</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
@@ -7115,28 +7115,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>UNISEM</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D148" s="9" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="E148" s="10" t="n">
-        <v>0.0114</v>
+        <v>0.415</v>
+      </c>
+      <c r="E148" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>801100</v>
+        <v>1067700</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>0.3</v>
+        <v>0.91</v>
       </c>
       <c r="H148" t="n">
-        <v>53.2</v>
+        <v>39.02</v>
       </c>
       <c r="I148" s="16" t="inlineStr">
         <is>
@@ -7144,10 +7144,10 @@
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>4.349</v>
+        <v>0.424</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>4.369</v>
+        <v>0.443</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -7160,28 +7160,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D149" s="9" t="n">
-        <v>7.97</v>
-      </c>
-      <c r="E149" s="17" t="n">
-        <v>-0.0038</v>
+        <v>1.24</v>
+      </c>
+      <c r="E149" s="15" t="n">
+        <v>-0.0313</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>764500</v>
+        <v>1058100</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="H149" t="n">
-        <v>73.97</v>
+        <v>72.16</v>
       </c>
       <c r="I149" s="13" t="inlineStr">
         <is>
@@ -7189,10 +7189,10 @@
         </is>
       </c>
       <c r="J149" s="9" t="n">
-        <v>7.077</v>
+        <v>1.059</v>
       </c>
       <c r="K149" s="9" t="n">
-        <v>6.693</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="14" t="inlineStr"/>
@@ -7205,28 +7205,28 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0466</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>SRKKAI</t>
         </is>
       </c>
       <c r="D150" s="9" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="E150" s="10" t="n">
-        <v>0.0075</v>
+        <v>0.53</v>
+      </c>
+      <c r="E150" s="15" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>749100</v>
+        <v>1013900</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>0.24</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H150" t="n">
-        <v>63.01</v>
+        <v>50.33</v>
       </c>
       <c r="I150" s="13" t="inlineStr">
         <is>
@@ -7234,10 +7234,10 @@
         </is>
       </c>
       <c r="J150" s="9" t="n">
-        <v>3.854</v>
+        <v>0.527</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>3.542</v>
+        <v>0.533</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -7250,28 +7250,28 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>7202</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>HEXRTL</t>
         </is>
       </c>
       <c r="D151" s="9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="E151" s="15" t="n">
-        <v>0</v>
+        <v>0.4</v>
+      </c>
+      <c r="E151" s="10" t="n">
+        <v>0.0959</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>733900</v>
+        <v>1002700</v>
       </c>
       <c r="G151" s="12" t="n">
-        <v>0.15</v>
+        <v>3.08</v>
       </c>
       <c r="H151" t="n">
-        <v>61.57</v>
+        <v>45.96</v>
       </c>
       <c r="I151" s="13" t="inlineStr">
         <is>
@@ -7279,10 +7279,10 @@
         </is>
       </c>
       <c r="J151" s="9" t="n">
-        <v>5.042</v>
+        <v>0.406</v>
       </c>
       <c r="K151" s="9" t="n">
-        <v>5.058</v>
+        <v>0.411</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="14" t="inlineStr"/>
@@ -7295,28 +7295,28 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>1562</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>SPTOTO</t>
         </is>
       </c>
       <c r="D152" s="9" t="n">
-        <v>0.95</v>
+        <v>1.35</v>
       </c>
       <c r="E152" s="10" t="n">
-        <v>0.0215</v>
+        <v>0.0227</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>732800</v>
+        <v>995900</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>0.39</v>
+        <v>1.68</v>
       </c>
       <c r="H152" t="n">
-        <v>56.93</v>
+        <v>67.39</v>
       </c>
       <c r="I152" s="13" t="inlineStr">
         <is>
@@ -7324,10 +7324,10 @@
         </is>
       </c>
       <c r="J152" s="9" t="n">
-        <v>0.922</v>
+        <v>1.282</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>0.842</v>
+        <v>1.293</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
@@ -7340,28 +7340,28 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D153" s="9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E153" s="17" t="n">
-        <v>-0.0141</v>
+        <v>0.96</v>
+      </c>
+      <c r="E153" s="10" t="n">
+        <v>0.0052</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>723500</v>
+        <v>979600</v>
       </c>
       <c r="G153" s="12" t="n">
-        <v>0.77</v>
+        <v>0.23</v>
       </c>
       <c r="H153" t="n">
-        <v>37.67</v>
+        <v>29.5</v>
       </c>
       <c r="I153" s="16" t="inlineStr">
         <is>
@@ -7369,10 +7369,10 @@
         </is>
       </c>
       <c r="J153" s="9" t="n">
-        <v>2.244</v>
+        <v>1.007</v>
       </c>
       <c r="K153" s="9" t="n">
-        <v>2.323</v>
+        <v>1.075</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="14" t="inlineStr"/>
@@ -7385,28 +7385,28 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>7174</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>CAB</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D154" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E154" s="17" t="n">
-        <v>-0.007800000000000001</v>
+        <v>7.99</v>
+      </c>
+      <c r="E154" s="15" t="n">
+        <v>-0.0012</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>718500</v>
+        <v>978300</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>0.59</v>
+        <v>0.24</v>
       </c>
       <c r="H154" t="n">
-        <v>85.22</v>
+        <v>74.63</v>
       </c>
       <c r="I154" s="13" t="inlineStr">
         <is>
@@ -7414,10 +7414,10 @@
         </is>
       </c>
       <c r="J154" s="9" t="n">
-        <v>0.57</v>
+        <v>7.079</v>
       </c>
       <c r="K154" s="9" t="n">
-        <v>0.538</v>
+        <v>6.694</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="14" t="inlineStr"/>
@@ -7430,28 +7430,28 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>0263</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D155" s="9" t="n">
-        <v>0.68</v>
+        <v>7.23</v>
       </c>
       <c r="E155" s="10" t="n">
-        <v>0.05429999999999999</v>
+        <v>0.005600000000000001</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>701600</v>
+        <v>972100</v>
       </c>
       <c r="G155" s="12" t="n">
-        <v>1.27</v>
+        <v>0.13</v>
       </c>
       <c r="H155" t="n">
-        <v>48.64</v>
+        <v>33.8</v>
       </c>
       <c r="I155" s="16" t="inlineStr">
         <is>
@@ -7459,10 +7459,10 @@
         </is>
       </c>
       <c r="J155" s="9" t="n">
-        <v>0.681</v>
+        <v>7.467</v>
       </c>
       <c r="K155" s="9" t="n">
-        <v>0.712</v>
+        <v>7.755</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="14" t="inlineStr"/>
@@ -7475,28 +7475,28 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D156" s="9" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E156" s="10" t="n">
+        <v>0.0053</v>
+      </c>
+      <c r="F156" s="11" t="n">
+        <v>964000</v>
+      </c>
+      <c r="G156" s="12" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="E156" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F156" s="11" t="n">
-        <v>693300</v>
-      </c>
-      <c r="G156" s="12" t="n">
-        <v>0.31</v>
-      </c>
       <c r="H156" t="n">
-        <v>48.46</v>
+        <v>34.76</v>
       </c>
       <c r="I156" s="16" t="inlineStr">
         <is>
@@ -7504,10 +7504,10 @@
         </is>
       </c>
       <c r="J156" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.971</v>
       </c>
       <c r="K156" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.997</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="14" t="inlineStr"/>
@@ -7520,39 +7520,39 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D157" s="9" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="E157" s="10" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.995</v>
+      </c>
+      <c r="E157" s="15" t="n">
+        <v>-0.0149</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>675700</v>
+        <v>930400</v>
       </c>
       <c r="G157" s="12" t="n">
-        <v>0.27</v>
+        <v>0.11</v>
       </c>
       <c r="H157" t="n">
-        <v>56.83</v>
-      </c>
-      <c r="I157" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.39</v>
+      </c>
+      <c r="I157" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J157" s="9" t="n">
-        <v>2.082</v>
+        <v>0.96</v>
       </c>
       <c r="K157" s="9" t="n">
-        <v>2.035</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="14" t="inlineStr"/>
@@ -7565,28 +7565,28 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>KOBAY</t>
         </is>
       </c>
       <c r="D158" s="9" t="n">
-        <v>1.29</v>
+        <v>2.1</v>
       </c>
       <c r="E158" s="15" t="n">
-        <v>0</v>
+        <v>-0.0141</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>673500</v>
+        <v>908900</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>0.05</v>
+        <v>0.97</v>
       </c>
       <c r="H158" t="n">
-        <v>43.85</v>
+        <v>37.67</v>
       </c>
       <c r="I158" s="16" t="inlineStr">
         <is>
@@ -7594,10 +7594,10 @@
         </is>
       </c>
       <c r="J158" s="9" t="n">
-        <v>1.334</v>
+        <v>2.244</v>
       </c>
       <c r="K158" s="9" t="n">
-        <v>1.307</v>
+        <v>2.323</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="14" t="inlineStr"/>
@@ -7610,28 +7610,28 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>CAB</t>
         </is>
       </c>
       <c r="D159" s="9" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="E159" s="17" t="n">
-        <v>-0.0083</v>
+        <v>0.64</v>
+      </c>
+      <c r="E159" s="15" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>671500</v>
+        <v>890800</v>
       </c>
       <c r="G159" s="12" t="n">
-        <v>0.3</v>
+        <v>0.73</v>
       </c>
       <c r="H159" t="n">
-        <v>72.08</v>
+        <v>85.22</v>
       </c>
       <c r="I159" s="13" t="inlineStr">
         <is>
@@ -7639,10 +7639,10 @@
         </is>
       </c>
       <c r="J159" s="9" t="n">
-        <v>2.084</v>
+        <v>0.57</v>
       </c>
       <c r="K159" s="9" t="n">
-        <v>1.944</v>
+        <v>0.538</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="14" t="inlineStr"/>
@@ -7655,28 +7655,28 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D160" s="9" t="n">
-        <v>0.9</v>
+        <v>0.68</v>
       </c>
       <c r="E160" s="15" t="n">
-        <v>0</v>
+        <v>-0.0216</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>663900</v>
+        <v>888900</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>0.23</v>
+        <v>0.4</v>
       </c>
       <c r="H160" t="n">
-        <v>39.1</v>
+        <v>69.78</v>
       </c>
       <c r="I160" s="13" t="inlineStr">
         <is>
@@ -7684,10 +7684,10 @@
         </is>
       </c>
       <c r="J160" s="9" t="n">
-        <v>0.915</v>
+        <v>0.619</v>
       </c>
       <c r="K160" s="9" t="n">
-        <v>0.968</v>
+        <v>0.523</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="14" t="inlineStr"/>
@@ -7700,28 +7700,28 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>HI</t>
         </is>
       </c>
       <c r="D161" s="9" t="n">
-        <v>7.21</v>
-      </c>
-      <c r="E161" s="10" t="n">
-        <v>0.0028</v>
+        <v>1.79</v>
+      </c>
+      <c r="E161" s="15" t="n">
+        <v>-0.0165</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>656600</v>
+        <v>882600</v>
       </c>
       <c r="G161" s="12" t="n">
-        <v>0.09</v>
+        <v>0.95</v>
       </c>
       <c r="H161" t="n">
-        <v>32.48</v>
+        <v>42.96</v>
       </c>
       <c r="I161" s="16" t="inlineStr">
         <is>
@@ -7729,10 +7729,10 @@
         </is>
       </c>
       <c r="J161" s="9" t="n">
-        <v>7.465</v>
+        <v>1.822</v>
       </c>
       <c r="K161" s="9" t="n">
-        <v>7.754</v>
+        <v>1.841</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="14" t="inlineStr"/>
@@ -7745,28 +7745,28 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D162" s="9" t="n">
-        <v>1.89</v>
+        <v>1.3</v>
       </c>
       <c r="E162" s="10" t="n">
-        <v>0.0107</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>650300</v>
+        <v>880600</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H162" t="n">
-        <v>41.41</v>
+        <v>45.35</v>
       </c>
       <c r="I162" s="16" t="inlineStr">
         <is>
@@ -7774,10 +7774,10 @@
         </is>
       </c>
       <c r="J162" s="9" t="n">
-        <v>1.934</v>
+        <v>1.335</v>
       </c>
       <c r="K162" s="9" t="n">
-        <v>1.96</v>
+        <v>1.307</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="14" t="inlineStr"/>
@@ -7790,28 +7790,28 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>0351</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>LSH</t>
+          <t>THMY</t>
         </is>
       </c>
       <c r="D163" s="9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="E163" s="10" t="n">
-        <v>0.0355</v>
+        <v>2.4</v>
+      </c>
+      <c r="E163" s="15" t="n">
+        <v>-0.004099999999999999</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>640300</v>
+        <v>862700</v>
       </c>
       <c r="G163" s="12" t="n">
-        <v>1.19</v>
+        <v>0.39</v>
       </c>
       <c r="H163" t="n">
-        <v>76.36</v>
+        <v>72.94</v>
       </c>
       <c r="I163" s="13" t="inlineStr">
         <is>
@@ -7819,10 +7819,10 @@
         </is>
       </c>
       <c r="J163" s="9" t="n">
-        <v>1.63</v>
+        <v>2.085</v>
       </c>
       <c r="K163" s="9" t="n">
-        <v>1.606</v>
+        <v>1.944</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="14" t="inlineStr"/>
@@ -7835,28 +7835,28 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D164" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E164" s="17" t="n">
-        <v>-0.007800000000000001</v>
+        <v>4.04</v>
+      </c>
+      <c r="E164" s="10" t="n">
+        <v>0.01</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>631500</v>
+        <v>852700</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>0.17</v>
+        <v>0.27</v>
       </c>
       <c r="H164" t="n">
-        <v>55.69</v>
+        <v>63.38</v>
       </c>
       <c r="I164" s="13" t="inlineStr">
         <is>
@@ -7864,10 +7864,10 @@
         </is>
       </c>
       <c r="J164" s="9" t="n">
-        <v>0.63</v>
+        <v>3.855</v>
       </c>
       <c r="K164" s="9" t="n">
-        <v>0.598</v>
+        <v>3.542</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="14" t="inlineStr"/>
@@ -7889,19 +7889,19 @@
         </is>
       </c>
       <c r="D165" s="9" t="n">
-        <v>0.87</v>
+        <v>0.865</v>
       </c>
       <c r="E165" s="10" t="n">
-        <v>0.0675</v>
+        <v>0.0613</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>625000</v>
+        <v>839700</v>
       </c>
       <c r="G165" s="12" t="n">
-        <v>0.33</v>
+        <v>0.44</v>
       </c>
       <c r="H165" t="n">
-        <v>49.39</v>
+        <v>48.05</v>
       </c>
       <c r="I165" s="13" t="inlineStr">
         <is>
@@ -7909,7 +7909,7 @@
         </is>
       </c>
       <c r="J165" s="9" t="n">
-        <v>0.859</v>
+        <v>0.858</v>
       </c>
       <c r="K165" s="9" t="n">
         <v>0.928</v>
@@ -7925,28 +7925,28 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>PADINI</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D166" s="9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E166" s="10" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.9</v>
+      </c>
+      <c r="E166" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>602500</v>
+        <v>838500</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="H166" t="n">
-        <v>46.04</v>
+        <v>39.1</v>
       </c>
       <c r="I166" s="13" t="inlineStr">
         <is>
@@ -7954,10 +7954,10 @@
         </is>
       </c>
       <c r="J166" s="9" t="n">
-        <v>1.062</v>
+        <v>0.915</v>
       </c>
       <c r="K166" s="9" t="n">
-        <v>1.207</v>
+        <v>0.968</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="14" t="inlineStr"/>
@@ -7970,39 +7970,39 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D167" s="9" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="E167" s="15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="E167" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>600800</v>
+        <v>833800</v>
       </c>
       <c r="G167" s="12" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="H167" t="n">
-        <v>31.04</v>
-      </c>
-      <c r="I167" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.89</v>
+      </c>
+      <c r="I167" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J167" s="9" t="n">
-        <v>1.517</v>
+        <v>2.081</v>
       </c>
       <c r="K167" s="9" t="n">
-        <v>1.631</v>
+        <v>2.035</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="14" t="inlineStr"/>
@@ -8015,39 +8015,39 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D168" s="9" t="n">
-        <v>2.17</v>
+        <v>0.945</v>
       </c>
       <c r="E168" s="10" t="n">
-        <v>0.014</v>
+        <v>0.0161</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>599000</v>
+        <v>808600</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>0.1</v>
+        <v>0.43</v>
       </c>
       <c r="H168" t="n">
-        <v>48.99</v>
-      </c>
-      <c r="I168" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.31</v>
+      </c>
+      <c r="I168" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J168" s="9" t="n">
-        <v>2.188</v>
+        <v>0.921</v>
       </c>
       <c r="K168" s="9" t="n">
-        <v>2.119</v>
+        <v>0.842</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="14" t="inlineStr"/>
@@ -8060,39 +8060,39 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>HI</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D169" s="9" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="E169" s="17" t="n">
-        <v>-0.0275</v>
+        <v>0.64</v>
+      </c>
+      <c r="E169" s="15" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>592700</v>
+        <v>739400</v>
       </c>
       <c r="G169" s="12" t="n">
-        <v>0.64</v>
+        <v>0.2</v>
       </c>
       <c r="H169" t="n">
-        <v>40.19</v>
-      </c>
-      <c r="I169" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.69</v>
+      </c>
+      <c r="I169" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J169" s="9" t="n">
-        <v>1.82</v>
+        <v>0.63</v>
       </c>
       <c r="K169" s="9" t="n">
-        <v>1.841</v>
+        <v>0.598</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="14" t="inlineStr"/>
@@ -8105,28 +8105,28 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>0263</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="D170" s="9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E170" s="15" t="n">
-        <v>0</v>
+        <v>0.675</v>
+      </c>
+      <c r="E170" s="10" t="n">
+        <v>0.04650000000000001</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>576000</v>
+        <v>711700</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>0.36</v>
+        <v>1.29</v>
       </c>
       <c r="H170" t="n">
-        <v>46.29</v>
+        <v>47.19</v>
       </c>
       <c r="I170" s="16" t="inlineStr">
         <is>
@@ -8134,10 +8134,10 @@
         </is>
       </c>
       <c r="J170" s="9" t="n">
-        <v>1.263</v>
+        <v>0.681</v>
       </c>
       <c r="K170" s="9" t="n">
-        <v>1.319</v>
+        <v>0.712</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="14" t="inlineStr"/>
@@ -8150,39 +8150,39 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D171" s="9" t="n">
-        <v>1.18</v>
+        <v>1.47</v>
       </c>
       <c r="E171" s="17" t="n">
-        <v>-0.0167</v>
+        <v>0</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>549800</v>
+        <v>699600</v>
       </c>
       <c r="G171" s="12" t="n">
-        <v>0.16</v>
+        <v>0.31</v>
       </c>
       <c r="H171" t="n">
-        <v>74.95999999999999</v>
-      </c>
-      <c r="I171" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.04</v>
+      </c>
+      <c r="I171" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J171" s="9" t="n">
-        <v>0.982</v>
+        <v>1.517</v>
       </c>
       <c r="K171" s="9" t="n">
-        <v>0.841</v>
+        <v>1.631</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="14" t="inlineStr"/>
@@ -8195,39 +8195,39 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>7052</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>PADINI</t>
         </is>
       </c>
       <c r="D172" s="9" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E172" s="17" t="n">
-        <v>-0.0118</v>
+        <v>1.07</v>
+      </c>
+      <c r="E172" s="10" t="n">
+        <v>0.009399999999999999</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>520400</v>
+        <v>698500</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>0.17</v>
+        <v>0.36</v>
       </c>
       <c r="H172" t="n">
-        <v>58.33</v>
-      </c>
-      <c r="I172" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.04</v>
+      </c>
+      <c r="I172" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J172" s="9" t="n">
-        <v>0.8159999999999999</v>
+        <v>1.062</v>
       </c>
       <c r="K172" s="9" t="n">
-        <v>0.75</v>
+        <v>1.207</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="14" t="inlineStr"/>
@@ -8240,28 +8240,28 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D173" s="9" t="n">
-        <v>2.51</v>
+        <v>1.24</v>
       </c>
       <c r="E173" s="17" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>512800</v>
+        <v>691400</v>
       </c>
       <c r="G173" s="12" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="H173" t="n">
-        <v>31.43</v>
+        <v>45.41</v>
       </c>
       <c r="I173" s="13" t="inlineStr">
         <is>
@@ -8269,16 +8269,646 @@
         </is>
       </c>
       <c r="J173" s="9" t="n">
-        <v>2.601</v>
+        <v>1.252</v>
       </c>
       <c r="K173" s="9" t="n">
-        <v>2.743</v>
+        <v>1.289</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="14" t="inlineStr"/>
     </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>0351</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>LSH</t>
+        </is>
+      </c>
+      <c r="D174" s="9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="E174" s="10" t="n">
+        <v>0.0355</v>
+      </c>
+      <c r="F174" s="11" t="n">
+        <v>683900</v>
+      </c>
+      <c r="G174" s="12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="H174" t="n">
+        <v>76.36</v>
+      </c>
+      <c r="I174" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J174" s="9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="K174" s="9" t="n">
+        <v>1.606</v>
+      </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" s="14" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>6947</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="D175" s="9" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="E175" s="15" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F175" s="11" t="n">
+        <v>667400</v>
+      </c>
+      <c r="G175" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H175" t="n">
+        <v>31.43</v>
+      </c>
+      <c r="I175" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J175" s="9" t="n">
+        <v>2.601</v>
+      </c>
+      <c r="K175" s="9" t="n">
+        <v>2.743</v>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" s="14" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>5341</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>LACMED</t>
+        </is>
+      </c>
+      <c r="D176" s="9" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="E176" s="10" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="F176" s="11" t="n">
+        <v>636900</v>
+      </c>
+      <c r="G176" s="12" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="H176" t="n">
+        <v>42.26</v>
+      </c>
+      <c r="I176" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J176" s="9" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="K176" s="9" t="n">
+        <v>0.754</v>
+      </c>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" s="14" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>0376</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>IAB</t>
+        </is>
+      </c>
+      <c r="D177" s="9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E177" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F177" s="11" t="n">
+        <v>620600</v>
+      </c>
+      <c r="G177" s="12" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H177" t="n">
+        <v>46.29</v>
+      </c>
+      <c r="I177" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J177" s="9" t="n">
+        <v>1.263</v>
+      </c>
+      <c r="K177" s="9" t="n">
+        <v>1.319</v>
+      </c>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" s="14" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>HIBISCS</t>
+        </is>
+      </c>
+      <c r="D178" s="9" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="E178" s="10" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="F178" s="11" t="n">
+        <v>611600</v>
+      </c>
+      <c r="G178" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H178" t="n">
+        <v>48.99</v>
+      </c>
+      <c r="I178" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J178" s="9" t="n">
+        <v>2.188</v>
+      </c>
+      <c r="K178" s="9" t="n">
+        <v>2.119</v>
+      </c>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" s="14" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>5263</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>SUNCON</t>
+        </is>
+      </c>
+      <c r="D179" s="9" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="E179" s="15" t="n">
+        <v>-0.0013</v>
+      </c>
+      <c r="F179" s="11" t="n">
+        <v>606900</v>
+      </c>
+      <c r="G179" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H179" t="n">
+        <v>45.16</v>
+      </c>
+      <c r="I179" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J179" s="9" t="n">
+        <v>7.622</v>
+      </c>
+      <c r="K179" s="9" t="n">
+        <v>7.814</v>
+      </c>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" s="14" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>5246</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>WPRTS</t>
+        </is>
+      </c>
+      <c r="D180" s="9" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="E180" s="10" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="F180" s="11" t="n">
+        <v>590700</v>
+      </c>
+      <c r="G180" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H180" t="n">
+        <v>55.06</v>
+      </c>
+      <c r="I180" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J180" s="9" t="n">
+        <v>6.783</v>
+      </c>
+      <c r="K180" s="9" t="n">
+        <v>6.849</v>
+      </c>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" s="14" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>0246</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>CNERGEN</t>
+        </is>
+      </c>
+      <c r="D181" s="9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="E181" s="15" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="F181" s="11" t="n">
+        <v>584000</v>
+      </c>
+      <c r="G181" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H181" t="n">
+        <v>73.48</v>
+      </c>
+      <c r="I181" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J181" s="9" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="K181" s="9" t="n">
+        <v>0.841</v>
+      </c>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" s="14" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>0097</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>VITROX</t>
+        </is>
+      </c>
+      <c r="D182" s="9" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="E182" s="10" t="n">
+        <v>0.0162</v>
+      </c>
+      <c r="F182" s="11" t="n">
+        <v>570600</v>
+      </c>
+      <c r="G182" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H182" t="n">
+        <v>81.56999999999999</v>
+      </c>
+      <c r="I182" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J182" s="9" t="n">
+        <v>10.072</v>
+      </c>
+      <c r="K182" s="9" t="n">
+        <v>9.428000000000001</v>
+      </c>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" s="14" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>5301</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>CTOS</t>
+        </is>
+      </c>
+      <c r="D183" s="9" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="E183" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F183" s="11" t="n">
+        <v>568200</v>
+      </c>
+      <c r="G183" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H183" t="n">
+        <v>32.41</v>
+      </c>
+      <c r="I183" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J183" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K183" s="9" t="n">
+        <v>0.646</v>
+      </c>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" s="14" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D184" s="9" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E184" s="15" t="n">
+        <v>-0.0178</v>
+      </c>
+      <c r="F184" s="11" t="n">
+        <v>558600</v>
+      </c>
+      <c r="G184" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H184" t="n">
+        <v>56.99</v>
+      </c>
+      <c r="I184" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J184" s="9" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="K184" s="9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" s="14" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>5302</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>ATECH</t>
+        </is>
+      </c>
+      <c r="D185" s="9" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E185" s="10" t="n">
+        <v>0.0197</v>
+      </c>
+      <c r="F185" s="11" t="n">
+        <v>554200</v>
+      </c>
+      <c r="G185" s="12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H185" t="n">
+        <v>53.12</v>
+      </c>
+      <c r="I185" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J185" s="9" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="K185" s="9" t="n">
+        <v>0.759</v>
+      </c>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" s="14" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>7133</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>ULICORP</t>
+        </is>
+      </c>
+      <c r="D186" s="9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E186" s="15" t="n">
+        <v>-0.0072</v>
+      </c>
+      <c r="F186" s="11" t="n">
+        <v>515600</v>
+      </c>
+      <c r="G186" s="12" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H186" t="n">
+        <v>53.48</v>
+      </c>
+      <c r="I186" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J186" s="9" t="n">
+        <v>1.363</v>
+      </c>
+      <c r="K186" s="9" t="n">
+        <v>1.356</v>
+      </c>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" s="14" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>7148</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>DPHARMA</t>
+        </is>
+      </c>
+      <c r="D187" s="9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="E187" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" s="11" t="n">
+        <v>514700</v>
+      </c>
+      <c r="G187" s="12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H187" t="n">
+        <v>41.62</v>
+      </c>
+      <c r="I187" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J187" s="9" t="n">
+        <v>1.178</v>
+      </c>
+      <c r="K187" s="9" t="n">
+        <v>1.211</v>
+      </c>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M173"/>
+  <autoFilter ref="A1:M187"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>